--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -619,15 +619,15 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,1,TRAMOS!$E$5:$E$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,1,TRAMOS!$E$5:$E$66)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,1,TRAMOS!$N$5:$N$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,1,TRAMOS!$N$5:$N$66)</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,1,TRAMOS!$M$5:$M$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,1,TRAMOS!$M$5:$M$66)</f>
         <v/>
       </c>
       <c r="E5" s="6" t="n">
@@ -635,7 +635,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>D1: Esquina oeste: al terreno natural (quebrada al oeste / nor-oeste)</t>
+          <t>D1: Cerco sur-oeste (lado C22-C1, x = 820.7): al talud natural que baja a la quebrada del oeste</t>
         </is>
       </c>
     </row>
@@ -646,23 +646,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,2,TRAMOS!$E$5:$E$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,2,TRAMOS!$E$5:$E$66)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,2,TRAMOS!$N$5:$N$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,2,TRAMOS!$N$5:$N$66)</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,2,TRAMOS!$M$5:$M$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,2,TRAMOS!$M$5:$M$66)</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.782</v>
+        <v>0.834</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>D3: Frente sur, punto bajo (x = 925.0): al Jr. Alfonso Ugarte en su punto bajo (183.00) - confirmar evacuacion de la calle</t>
+          <t>D3: Cerco sur junto a C14 (x = 935.5): al terreno exterior que baja al Jr. Alfonso Ugarte (183.00)</t>
         </is>
       </c>
     </row>
@@ -673,15 +673,15 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,3,TRAMOS!$E$5:$E$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,3,TRAMOS!$E$5:$E$66)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,3,TRAMOS!$N$5:$N$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,3,TRAMOS!$N$5:$N$66)</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,3,TRAMOS!$M$5:$M$65)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$66,3,TRAMOS!$M$5:$M$66)</f>
         <v/>
       </c>
       <c r="E7" s="6" t="n">
@@ -689,53 +689,26 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>D2: Perimetral este, punto bajo (y = 860.5): a la cabecera de la quebrada del norte</t>
+          <t>D2: Cerco norte (x = 965.5): poza de salida que rebalsa a nivel del fondo de la hondonada natural (baja a la quebrada del norte)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SISTEMA 4 - INGRESO SUR-ESTE (descarga D4)</t>
-        </is>
-      </c>
-      <c r="B8" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,4,TRAMOS!$E$5:$E$65)</f>
-        <v/>
-      </c>
-      <c r="C8" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,4,TRAMOS!$N$5:$N$65)</f>
-        <v/>
-      </c>
-      <c r="D8" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$65,4,TRAMOS!$M$5:$M$65)</f>
-        <v/>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>D4: Ingreso sur-este: a la calzada del Jr. Alfonso Ugarte, que baja hacia su punto bajo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <f>SUM(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="8">
-        <f>SUM(C5:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="8">
-        <f>SUM(D5:D8)</f>
+      <c r="B8" s="8">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>SUM(D5:D7)</f>
         <v/>
       </c>
     </row>
@@ -763,28 +736,35 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>3. Rasante: NTN +184.50 en la plataforma de los bloques; terreno de las curvas en el resto (monticulo de 185.5 recortado a +184.50).</t>
+          <t>3. Area de intervencion = interior del cerco perimetrico: todas las cunetas quedan dentro del cerco (las perimetrales a 0.60 m de su eje).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>4. D1, D2 y D4 salen a la superficie del terreno por gravedad; D3 entrega al punto bajo del Jr. Alfonso Ugarte (183.00): confirmar su evacuacion.</t>
+          <t>4. Rasante: NTN +184.50 en la plataforma; en el resto del area dentro del cerco, el terreno de las curvas recortado a +184.50.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>5. Tramos de fuerte pendiente con V &gt; 3.0 m/s: gradas de concreto (hoja HIDRAULICA). Verificacion completa en la hoja VERIFICACION.</t>
+          <t>5. D1 y D3 salen por un pase en el cimiento del cerco; D2 por una poza de salida (0.80 x 0.80 m) que rebalsa a nivel del terreno. Fuera del cerco no hay obra.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>6. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta, DC-02 cuadro y secciones, DC-03 a DC-06 perfiles, DC-07 y DC-08 isometricos, DC-09 y DC-10 cortes.</t>
+          <t>6. Tramos de fuerte pendiente con V &gt; 3.0 m/s: gradas de concreto (hoja HIDRAULICA). Verificacion completa en la hoja VERIFICACION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta, DC-02 cuadro y secciones, DC-03 a DC-05 perfiles, DC-06 y DC-07 isometricos, DC-08 y DC-09 cortes, DC-10 detalle de descargas.</t>
         </is>
       </c>
     </row>
@@ -816,7 +796,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VERIFICACION DEL PLANTEAMIENTO (10 COMPROBACIONES)</t>
+          <t>VERIFICACION DEL PLANTEAMIENTO (11 COMPROBACIONES)</t>
         </is>
       </c>
     </row>
@@ -865,7 +845,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>22 ramales: R-01-&gt;D1, R-02-&gt;D1, R-03-&gt;D1, R-04-&gt;D1, R-05-&gt;D1, R-06-&gt;D1, R-07-&gt;D3, R-23-&gt;D3, R-08-&gt;D3, R-09-&gt;D3, R-10-&gt;D3, R-11-&gt;D3, R-12-&gt;D3, R-13-&gt;D2, R-22-&gt;D2, R-14-&gt;D2, R-15-&gt;D2, R-16-&gt;D2, R-17-&gt;D2, R-18-&gt;D2, R-19-&gt;D2, R-20-&gt;D2, R-21-&gt;D4</t>
+          <t>19 ramales: R-01-&gt;D1, R-02-&gt;D1, R-03-&gt;D1, R-04-&gt;D1, R-05-&gt;D1, R-06-&gt;D1, R-07-&gt;D3, R-08-&gt;D3, R-09-&gt;D3, R-10-&gt;D3, R-11-&gt;D3, R-12-&gt;D2, R-13-&gt;D2, R-14-&gt;D2, R-15-&gt;D2, R-16-&gt;D2, R-17-&gt;D2, R-18-&gt;D2, R-19-&gt;D2</t>
         </is>
       </c>
     </row>
@@ -905,7 +885,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>minima 0.50 % (R-01 P-01-P-02); maxima 20.71 %</t>
+          <t>minima 0.50 % (R-01 P-01-P-02); maxima 44.02 %</t>
         </is>
       </c>
     </row>
@@ -925,7 +905,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>inicio 0.30 a 0.30; minima 0.25 (R-01); maxima 0.83 (R-02, prog 30.7)</t>
+          <t>inicio 0.30 a 0.30; minima 0.25 (R-07); maxima 0.83 (R-07, prog 82.5)</t>
         </is>
       </c>
     </row>
@@ -945,7 +925,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>16 empalmes; caida maxima 0.18 m (R-17 en P-46)</t>
+          <t>16 empalmes; caida maxima 0.32 m (R-11 en P-27)</t>
         </is>
       </c>
     </row>
@@ -955,17 +935,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Descargas por gravedad: el canal de salida (0.5 %) sale a la superficie del terreno</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>CUMPLE CON CONDICION</t>
+          <t>Descargas por el cerco: el agua sale por gravedad al terreno exterior sin obras fuera del cerco</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>D1 CF 181.588: sale a la superficie a 1.5 m (corte max 0.16); D2 CF 181.495: sale a la superficie a 5.5 m (corte max 0.17); D3 CF 182.992: terreno plano a 183.24: requiere receptor (Jr. Alfonso Ugarte, punto bajo de la calle (183.00)); D4 CF 183.741: sale a la superficie a 7.0 m (corte max 0.24)</t>
+          <t>D1 C.F. 183.557: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 1.0 m del cerco; D2 C.F. 180.175: poza de salida: rebalsa a 180.62 (fondo de la hondonada); afuera el fondo no sube y baja 0.25 m a 10.8 m; D3 C.F. 183.431: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 2.0 m del cerco</t>
         </is>
       </c>
     </row>
@@ -1005,7 +985,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 211 mm/h, C = 0.80, area total 10242 m2; menor borde libre 0.117 m en R-01 P-03-D1 (Q 189.7 l/s, y 0.133, h 0.25)</t>
+          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.055 m en R-12 P-43-P-44 (Q 154.7 l/s, y 0.228, h 0.28)</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1005,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-03-D1 (S 8.2 %, V 3.94), R-02 P-07-P-03 (S 7.1 %, V 3.51), R-08 P-25-D3 (S 7.5 %, V 3.53), R-13 P-37-P-38 (S 10.6 %, V 3.09), R-13 P-38-D2 (S 8.5 %, V 3.79), R-16 P-49-P-38 (S 20.7 %, V 4.25) -&gt; gradas (escalones) de concreto</t>
+          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-06-D1 (S 6.0 %, V 3.51), R-12 P-41-P-42 (S 5.6 %, V 3.15), R-12 P-42-P-43 (S 6.8 %, V 3.42), R-15 P-52-P-41 (S 44.0 %, V 5.24) -&gt; gradas (escalones) de concreto</t>
         </is>
       </c>
     </row>
@@ -1045,48 +1025,52 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>distancia minima eje-muro 1.11 m en 1847 puntos revisados</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+          <t>distancia minima eje-muro 0.55 m en 1696 puntos revisados</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Toda la red dentro del cerco perimetrico (limite de intervencion)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>CUMPLE</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>ningun borde de cuneta pasa el cerco; solo las 3 salidas lo atraviesan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>DESCARGAS</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DESCARGA</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>COTA DE FONDO</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>SALIDA POR GRAVEDAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>181.588</v>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>sale a la superficie del terreno a 1.5 m (corte maximo 0.16 m)</t>
         </is>
       </c>
     </row>
@@ -1094,15 +1078,15 @@
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>181.495</v>
+        <v>183.557</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>sale a la superficie del terreno a 5.5 m (corte maximo 0.17 m)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 1.0 m (perfilado maximo 0.31 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1110,15 +1094,15 @@
       <c r="A20" s="4" t="inlineStr"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>182.992</v>
+        <v>180.175</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>terreno plano: entrega al Jr. Alfonso Ugarte, punto bajo de la calle (183.00)</t>
+          <t>poza de salida: rebalsa a 180.62; el fondo exterior no sube y baja 0.25 m a 10.8 m</t>
         </is>
       </c>
     </row>
@@ -1126,15 +1110,15 @@
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>183.741</v>
+        <v>183.431</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>sale a la superficie del terreno a 7.0 m (corte maximo 0.24 m)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 2.0 m (perfilado maximo 0.32 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1562,7 +1546,7 @@
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E11" s="5">
         <f>1000*$B$4*$B$5*D11/3600000*$B$6</f>
@@ -1572,7 +1556,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>0.3</v>
@@ -1582,7 +1566,7 @@
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="K11" s="21">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1611,27 +1595,27 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>482</v>
+        <v>225</v>
       </c>
       <c r="E12" s="5">
         <f>1000*$B$4*$B$5*D12/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F12" s="18" t="n">
-        <v>1.83</v>
+        <v>0.5</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="I12" s="20">
         <f>H12-G12</f>
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>1.24</v>
+        <v>0.63</v>
       </c>
       <c r="K12" s="21">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1656,31 +1640,31 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>3519</v>
+        <v>370</v>
       </c>
       <c r="E13" s="5">
         <f>1000*$B$4*$B$5*D13/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F13" s="18" t="n">
-        <v>8.24</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.133</v>
+        <v>0.074</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="I13" s="20">
         <f>H13-G13</f>
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>3.94</v>
+        <v>0.74</v>
       </c>
       <c r="K13" s="21">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1690,16 +1674,12 @@
         <f>IF(J13&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M13" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M13" s="22" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
@@ -1713,27 +1693,27 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>440</v>
+        <v>651</v>
       </c>
       <c r="E14" s="5">
         <f>1000*$B$4*$B$5*D14/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>0.059</v>
+        <v>0.097</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="I14" s="20">
         <f>H14-G14</f>
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="K14" s="21">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1748,7 +1728,7 @@
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
@@ -1762,27 +1742,27 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1017</v>
+        <v>3533</v>
       </c>
       <c r="E15" s="5">
         <f>1000*$B$4*$B$5*D15/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F15" s="18" t="n">
-        <v>3.6</v>
+        <v>0.57</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.075</v>
+        <v>0.368</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I15" s="20">
         <f>H15-G15</f>
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>2.01</v>
+        <v>1.45</v>
       </c>
       <c r="K15" s="21">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1797,7 +1777,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -1807,31 +1787,31 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>2807</v>
+        <v>3540</v>
       </c>
       <c r="E16" s="5">
         <f>1000*$B$4*$B$5*D16/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F16" s="18" t="n">
-        <v>0.5</v>
+        <v>5.96</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.323</v>
+        <v>0.151</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="I16" s="20">
         <f>H16-G16</f>
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.31</v>
+        <v>3.51</v>
       </c>
       <c r="K16" s="21">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1841,7 +1821,11 @@
         <f>IF(J16&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M16" s="22" t="inlineStr"/>
+      <c r="M16" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
@@ -1856,31 +1840,31 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>2831</v>
+        <v>454</v>
       </c>
       <c r="E17" s="5">
         <f>1000*$B$4*$B$5*D17/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F17" s="18" t="n">
-        <v>7.14</v>
+        <v>1.4</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I17" s="20">
         <f>H17-G17</f>
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.51</v>
+        <v>1.12</v>
       </c>
       <c r="K17" s="21">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1890,16 +1874,12 @@
         <f>IF(J17&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M17" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M17" s="22" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -1909,31 +1889,31 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>388</v>
+        <v>1030</v>
       </c>
       <c r="E18" s="5">
         <f>1000*$B$4*$B$5*D18/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F18" s="18" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="G18" s="19" t="n">
         <v>0.076</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="I18" s="20">
         <f>H18-G18</f>
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.75</v>
+        <v>2.01</v>
       </c>
       <c r="K18" s="21">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1948,7 +1928,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -1958,11 +1938,11 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>249</v>
+        <v>2668</v>
       </c>
       <c r="E19" s="5">
         <f>1000*$B$4*$B$5*D19/3600000*$B$6</f>
@@ -1972,17 +1952,17 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.057</v>
+        <v>0.311</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>0.3</v>
+        <v>0.77</v>
       </c>
       <c r="I19" s="20">
         <f>H19-G19</f>
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.65</v>
+        <v>1.3</v>
       </c>
       <c r="K19" s="21">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1997,41 +1977,41 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>308</v>
+        <v>2672</v>
       </c>
       <c r="E20" s="5">
         <f>1000*$B$4*$B$5*D20/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F20" s="18" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>0.037</v>
+        <v>0.311</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>0.36</v>
+        <v>0.79</v>
       </c>
       <c r="I20" s="20">
         <f>H20-G20</f>
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="K20" s="21">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2046,21 +2026,21 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1604</v>
+        <v>393</v>
       </c>
       <c r="E21" s="5">
         <f>1000*$B$4*$B$5*D21/3600000*$B$6</f>
@@ -2070,17 +2050,17 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.21</v>
+        <v>0.077</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="I21" s="20">
         <f>H21-G21</f>
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.15</v>
+        <v>0.76</v>
       </c>
       <c r="K21" s="21">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2095,21 +2075,21 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
+          <t>P-12</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
           <t>P-11</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>P-12</t>
-        </is>
-      </c>
       <c r="D22" s="18" t="n">
-        <v>409</v>
+        <v>248</v>
       </c>
       <c r="E22" s="5">
         <f>1000*$B$4*$B$5*D22/3600000*$B$6</f>
@@ -2119,7 +2099,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0.079</v>
+        <v>0.057</v>
       </c>
       <c r="H22" s="18" t="n">
         <v>0.3</v>
@@ -2129,7 +2109,7 @@
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="K22" s="21">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2144,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -2158,27 +2138,27 @@
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>486</v>
+        <v>307</v>
       </c>
       <c r="E23" s="5">
         <f>1000*$B$4*$B$5*D23/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.089</v>
+        <v>0.037</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
       <c r="I23" s="20">
         <f>H23-G23</f>
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.23</v>
       </c>
       <c r="K23" s="21">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2193,7 +2173,7 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -2203,11 +2183,11 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>650</v>
+        <v>1497</v>
       </c>
       <c r="E24" s="5">
         <f>1000*$B$4*$B$5*D24/3600000*$B$6</f>
@@ -2217,17 +2197,17 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>0.109</v>
+        <v>0.199</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="I24" s="20">
         <f>H24-G24</f>
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="K24" s="21">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2256,7 +2236,7 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>882</v>
+        <v>390</v>
       </c>
       <c r="E25" s="5">
         <f>1000*$B$4*$B$5*D25/3600000*$B$6</f>
@@ -2266,17 +2246,17 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0.135</v>
+        <v>0.077</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I25" s="20">
         <f>H25-G25</f>
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.97</v>
+        <v>0.75</v>
       </c>
       <c r="K25" s="21">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2301,11 +2281,11 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>954</v>
+        <v>463</v>
       </c>
       <c r="E26" s="5">
         <f>1000*$B$4*$B$5*D26/3600000*$B$6</f>
@@ -2315,17 +2295,17 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>0.143</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="I26" s="20">
         <f>H26-G26</f>
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K26" s="21">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2340,7 +2320,7 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -2350,11 +2330,11 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>130</v>
+        <v>595</v>
       </c>
       <c r="E27" s="5">
         <f>1000*$B$4*$B$5*D27/3600000*$B$6</f>
@@ -2364,17 +2344,17 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.037</v>
+        <v>0.102</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="I27" s="20">
         <f>H27-G27</f>
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="K27" s="21">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2389,41 +2369,41 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>286</v>
+        <v>805</v>
       </c>
       <c r="E28" s="5">
         <f>1000*$B$4*$B$5*D28/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F28" s="18" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>0.035</v>
+        <v>0.127</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I28" s="20">
         <f>H28-G28</f>
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1.21</v>
+        <v>0.95</v>
       </c>
       <c r="K28" s="21">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2438,41 +2418,41 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
-        <v>334</v>
+        <v>868</v>
       </c>
       <c r="E29" s="5">
         <f>1000*$B$4*$B$5*D29/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1.51</v>
+        <v>0.5</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.048</v>
+        <v>0.134</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="I29" s="20">
         <f>H29-G29</f>
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="K29" s="21">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2487,41 +2467,41 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="E30" s="5">
         <f>1000*$B$4*$B$5*D30/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F30" s="18" t="n">
-        <v>1.96</v>
+        <v>0.5</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>0.045</v>
+        <v>0.032</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I30" s="20">
         <f>H30-G30</f>
         <v/>
       </c>
       <c r="J30" s="6" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="K30" s="21">
         <f>IF(I30&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2536,41 +2516,41 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>R-23</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="E31" s="5">
         <f>1000*$B$4*$B$5*D31/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.5</v>
+        <v>1.55</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>0.018</v>
+        <v>0.033</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="I31" s="20">
         <f>H31-G31</f>
         <v/>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.34</v>
+        <v>0.85</v>
       </c>
       <c r="K31" s="21">
         <f>IF(I31&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2585,41 +2565,41 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>R-23</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>425</v>
+        <v>860</v>
       </c>
       <c r="E32" s="5">
         <f>1000*$B$4*$B$5*D32/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F32" s="18" t="n">
-        <v>1.44</v>
+        <v>0.5</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>0.057</v>
+        <v>0.133</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
       <c r="I32" s="20">
         <f>H32-G32</f>
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="K32" s="21">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2634,41 +2614,41 @@
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
-        <v>205</v>
+        <v>1229</v>
       </c>
       <c r="E33" s="5">
         <f>1000*$B$4*$B$5*D33/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F33" s="18" t="n">
-        <v>1.55</v>
+        <v>0.5</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>0.035</v>
+        <v>0.172</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.3</v>
+        <v>0.57</v>
       </c>
       <c r="I33" s="20">
         <f>H33-G33</f>
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.87</v>
+        <v>1.07</v>
       </c>
       <c r="K33" s="21">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2683,12 +2663,12 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
@@ -2697,7 +2677,7 @@
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>876</v>
+        <v>1416</v>
       </c>
       <c r="E34" s="5">
         <f>1000*$B$4*$B$5*D34/3600000*$B$6</f>
@@ -2707,17 +2687,17 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>0.134</v>
+        <v>0.191</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="I34" s="20">
         <f>H34-G34</f>
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.97</v>
+        <v>1.11</v>
       </c>
       <c r="K34" s="21">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2732,7 +2712,7 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -2742,11 +2722,11 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1245</v>
+        <v>2577</v>
       </c>
       <c r="E35" s="5">
         <f>1000*$B$4*$B$5*D35/3600000*$B$6</f>
@@ -2756,17 +2736,17 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>0.174</v>
+        <v>0.302</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="I35" s="20">
         <f>H35-G35</f>
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="K35" s="21">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2781,21 +2761,21 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>1479</v>
+        <v>2638</v>
       </c>
       <c r="E36" s="5">
         <f>1000*$B$4*$B$5*D36/3600000*$B$6</f>
@@ -2805,17 +2785,17 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0.197</v>
+        <v>0.308</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I36" s="20">
         <f>H36-G36</f>
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="K36" s="21">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2830,41 +2810,41 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
-        <v>2675</v>
+        <v>2663</v>
       </c>
       <c r="E37" s="5">
         <f>1000*$B$4*$B$5*D37/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F37" s="18" t="n">
-        <v>0.5</v>
+        <v>1.61</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>0.311</v>
+        <v>0.198</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.63</v>
+        <v>0.29</v>
       </c>
       <c r="I37" s="20">
         <f>H37-G37</f>
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="K37" s="21">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2879,41 +2859,41 @@
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>2748</v>
+        <v>2684</v>
       </c>
       <c r="E38" s="5">
         <f>1000*$B$4*$B$5*D38/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F38" s="18" t="n">
-        <v>7.46</v>
+        <v>1.6</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>0.116</v>
+        <v>0.199</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="I38" s="20">
         <f>H38-G38</f>
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>3.53</v>
+        <v>2.02</v>
       </c>
       <c r="K38" s="21">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,30 +2903,26 @@
         <f>IF(J38&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M38" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M38" s="22" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
-        <v>491</v>
+        <v>2966</v>
       </c>
       <c r="E39" s="5">
         <f>1000*$B$4*$B$5*D39/3600000*$B$6</f>
@@ -2956,17 +2932,17 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.09</v>
+        <v>0.338</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="I39" s="20">
         <f>H39-G39</f>
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="K39" s="21">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2981,21 +2957,21 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>342</v>
+        <v>491</v>
       </c>
       <c r="E40" s="5">
         <f>1000*$B$4*$B$5*D40/3600000*$B$6</f>
@@ -3005,7 +2981,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H40" s="18" t="n">
         <v>0.3</v>
@@ -3015,7 +2991,7 @@
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K40" s="21">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3030,21 +3006,21 @@
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
-        <v>520</v>
+        <v>342</v>
       </c>
       <c r="E41" s="5">
         <f>1000*$B$4*$B$5*D41/3600000*$B$6</f>
@@ -3054,7 +3030,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>0.093</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H41" s="18" t="n">
         <v>0.3</v>
@@ -3064,7 +3040,7 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="K41" s="21">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3079,21 +3055,21 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>655</v>
+        <v>547</v>
       </c>
       <c r="E42" s="5">
         <f>1000*$B$4*$B$5*D42/3600000*$B$6</f>
@@ -3103,17 +3079,17 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>0.109</v>
+        <v>0.097</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="I42" s="20">
         <f>H42-G42</f>
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="K42" s="21">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3128,21 +3104,21 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="E43" s="5">
         <f>1000*$B$4*$B$5*D43/3600000*$B$6</f>
@@ -3152,10 +3128,10 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="I43" s="20">
         <f>H43-G43</f>
@@ -3177,21 +3153,21 @@
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>876</v>
+        <v>698</v>
       </c>
       <c r="E44" s="5">
         <f>1000*$B$4*$B$5*D44/3600000*$B$6</f>
@@ -3201,17 +3177,17 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="19" t="n">
-        <v>0.134</v>
+        <v>0.114</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I44" s="20">
         <f>H44-G44</f>
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="K44" s="21">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3226,21 +3202,21 @@
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="E45" s="5">
         <f>1000*$B$4*$B$5*D45/3600000*$B$6</f>
@@ -3250,10 +3226,10 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="I45" s="20">
         <f>H45-G45</f>
@@ -3275,21 +3251,21 @@
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1012</v>
+        <v>935</v>
       </c>
       <c r="E46" s="5">
         <f>1000*$B$4*$B$5*D46/3600000*$B$6</f>
@@ -3299,17 +3275,17 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>0.149</v>
+        <v>0.141</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I46" s="20">
         <f>H46-G46</f>
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="K46" s="21">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3324,21 +3300,21 @@
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>141</v>
+        <v>1036</v>
       </c>
       <c r="E47" s="5">
         <f>1000*$B$4*$B$5*D47/3600000*$B$6</f>
@@ -3348,17 +3324,17 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>0.039</v>
+        <v>0.152</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I47" s="20">
         <f>H47-G47</f>
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0.53</v>
+        <v>1.02</v>
       </c>
       <c r="K47" s="21">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3373,41 +3349,41 @@
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>331</v>
+        <v>130</v>
       </c>
       <c r="E48" s="5">
         <f>1000*$B$4*$B$5*D48/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F48" s="18" t="n">
-        <v>6.49</v>
+        <v>0.5</v>
       </c>
       <c r="G48" s="19" t="n">
-        <v>0.03</v>
+        <v>0.037</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I48" s="20">
         <f>H48-G48</f>
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.63</v>
+        <v>0.51</v>
       </c>
       <c r="K48" s="21">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3422,41 +3398,41 @@
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>P-34</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>120</v>
+        <v>264</v>
       </c>
       <c r="E49" s="5">
         <f>1000*$B$4*$B$5*D49/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F49" s="18" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>0.033</v>
+        <v>0.059</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="I49" s="20">
         <f>H49-G49</f>
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="K49" s="21">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3471,21 +3447,21 @@
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1197</v>
+        <v>276</v>
       </c>
       <c r="E50" s="5">
         <f>1000*$B$4*$B$5*D50/3600000*$B$6</f>
@@ -3495,17 +3471,17 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>0.169</v>
+        <v>0.061</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="I50" s="20">
         <f>H50-G50</f>
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="K50" s="21">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3520,31 +3496,31 @@
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
-        <v>1216</v>
+        <v>280</v>
       </c>
       <c r="E51" s="5">
         <f>1000*$B$4*$B$5*D51/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F51" s="18" t="n">
-        <v>4.34</v>
+        <v>14.89</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.08</v>
+        <v>0.021</v>
       </c>
       <c r="H51" s="18" t="n">
         <v>0.25</v>
@@ -3554,7 +3530,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="K51" s="21">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3569,41 +3545,41 @@
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>1267</v>
+        <v>70</v>
       </c>
       <c r="E52" s="5">
         <f>1000*$B$4*$B$5*D52/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F52" s="18" t="n">
-        <v>10.57</v>
+        <v>1.08</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>0.061</v>
+        <v>0.02</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I52" s="20">
         <f>H52-G52</f>
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>3.09</v>
+        <v>0.52</v>
       </c>
       <c r="K52" s="21">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3613,50 +3589,46 @@
         <f>IF(J52&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M52" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M52" s="22" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>3000</v>
+        <v>753</v>
       </c>
       <c r="E53" s="5">
         <f>1000*$B$4*$B$5*D53/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F53" s="18" t="n">
-        <v>8.460000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G53" s="19" t="n">
-        <v>0.118</v>
+        <v>0.121</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="I53" s="20">
         <f>H53-G53</f>
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>3.79</v>
+        <v>0.93</v>
       </c>
       <c r="K53" s="21">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3666,50 +3638,46 @@
         <f>IF(J53&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M53" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M53" s="22" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>R-22</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>108</v>
+        <v>1071</v>
       </c>
       <c r="E54" s="5">
         <f>1000*$B$4*$B$5*D54/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F54" s="18" t="n">
-        <v>11.11</v>
+        <v>11.49</v>
       </c>
       <c r="G54" s="19" t="n">
-        <v>0.013</v>
+        <v>0.053</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="I54" s="20">
         <f>H54-G54</f>
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>1.26</v>
+        <v>2.99</v>
       </c>
       <c r="K54" s="21">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3724,41 +3692,41 @@
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>487</v>
+        <v>2641</v>
       </c>
       <c r="E55" s="5">
         <f>1000*$B$4*$B$5*D55/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0.5</v>
+        <v>5.59</v>
       </c>
       <c r="G55" s="19" t="n">
-        <v>0.089</v>
+        <v>0.125</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I55" s="20">
         <f>H55-G55</f>
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="K55" s="21">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3768,46 +3736,50 @@
         <f>IF(J55&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M55" s="22" t="inlineStr"/>
+      <c r="M55" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>816</v>
+        <v>2767</v>
       </c>
       <c r="E56" s="5">
         <f>1000*$B$4*$B$5*D56/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F56" s="18" t="n">
-        <v>0.5</v>
+        <v>6.76</v>
       </c>
       <c r="G56" s="19" t="n">
-        <v>0.128</v>
+        <v>0.121</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="I56" s="20">
         <f>H56-G56</f>
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.95</v>
+        <v>3.42</v>
       </c>
       <c r="K56" s="21">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3817,46 +3789,50 @@
         <f>IF(J56&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M56" s="22" t="inlineStr"/>
+      <c r="M56" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1071</v>
+        <v>2870</v>
       </c>
       <c r="E57" s="5">
         <f>1000*$B$4*$B$5*D57/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F57" s="18" t="n">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="G57" s="19" t="n">
-        <v>0.155</v>
+        <v>0.228</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
       <c r="I57" s="20">
         <f>H57-G57</f>
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="K57" s="21">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3871,41 +3847,41 @@
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>251</v>
+        <v>2887</v>
       </c>
       <c r="E58" s="5">
         <f>1000*$B$4*$B$5*D58/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F58" s="18" t="n">
-        <v>0.5</v>
+        <v>5.27</v>
       </c>
       <c r="G58" s="19" t="n">
-        <v>0.057</v>
+        <v>0.136</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="I58" s="20">
         <f>H58-G58</f>
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.65</v>
+        <v>3.17</v>
       </c>
       <c r="K58" s="21">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3920,21 +3896,21 @@
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>P-45</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="E59" s="5">
         <f>1000*$B$4*$B$5*D59/3600000*$B$6</f>
@@ -3944,7 +3920,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="19" t="n">
-        <v>0.066</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H59" s="18" t="n">
         <v>0.3</v>
@@ -3954,7 +3930,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="K59" s="21">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3969,21 +3945,21 @@
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-46</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
-        <v>579</v>
+        <v>244</v>
       </c>
       <c r="E60" s="5">
         <f>1000*$B$4*$B$5*D60/3600000*$B$6</f>
@@ -3993,17 +3969,17 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="19" t="n">
-        <v>0.1</v>
+        <v>0.056</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="I60" s="20">
         <f>H60-G60</f>
         <v/>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="K60" s="21">
         <f>IF(I60&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4018,21 +3994,21 @@
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>637</v>
+        <v>313</v>
       </c>
       <c r="E61" s="5">
         <f>1000*$B$4*$B$5*D61/3600000*$B$6</f>
@@ -4042,17 +4018,17 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="19" t="n">
-        <v>0.107</v>
+        <v>0.066</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I61" s="20">
         <f>H61-G61</f>
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="K61" s="21">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4067,21 +4043,21 @@
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>816</v>
+        <v>579</v>
       </c>
       <c r="E62" s="5">
         <f>1000*$B$4*$B$5*D62/3600000*$B$6</f>
@@ -4091,17 +4067,17 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="19" t="n">
-        <v>0.128</v>
+        <v>0.1</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="I62" s="20">
         <f>H62-G62</f>
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="K62" s="21">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4116,21 +4092,21 @@
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>896</v>
+        <v>637</v>
       </c>
       <c r="E63" s="5">
         <f>1000*$B$4*$B$5*D63/3600000*$B$6</f>
@@ -4140,17 +4116,17 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="19" t="n">
-        <v>0.137</v>
+        <v>0.107</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I63" s="20">
         <f>H63-G63</f>
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="K63" s="21">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4165,41 +4141,41 @@
     <row r="64">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>1688</v>
+        <v>810</v>
       </c>
       <c r="E64" s="5">
         <f>1000*$B$4*$B$5*D64/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F64" s="18" t="n">
-        <v>20.71</v>
+        <v>0.5</v>
       </c>
       <c r="G64" s="19" t="n">
-        <v>0.059</v>
+        <v>0.127</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="I64" s="20">
         <f>H64-G64</f>
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>4.25</v>
+        <v>0.95</v>
       </c>
       <c r="K64" s="21">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4209,30 +4185,26 @@
         <f>IF(J64&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M64" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M64" s="22" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="D65" s="18" t="n">
-        <v>54</v>
+        <v>873</v>
       </c>
       <c r="E65" s="5">
         <f>1000*$B$4*$B$5*D65/3600000*$B$6</f>
@@ -4242,17 +4214,17 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="19" t="n">
-        <v>0.021</v>
+        <v>0.134</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I65" s="20">
         <f>H65-G65</f>
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.37</v>
+        <v>0.97</v>
       </c>
       <c r="K65" s="21">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4267,41 +4239,41 @@
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="D66" s="18" t="n">
-        <v>107</v>
+        <v>1533</v>
       </c>
       <c r="E66" s="5">
         <f>1000*$B$4*$B$5*D66/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F66" s="18" t="n">
-        <v>0.5</v>
+        <v>44.02</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>0.033</v>
+        <v>0.043</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I66" s="20">
         <f>H66-G66</f>
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>0.48</v>
+        <v>5.24</v>
       </c>
       <c r="K66" s="21">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4311,17 +4283,21 @@
         <f>IF(J66&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M66" s="22" t="inlineStr"/>
+      <c r="M66" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
@@ -4330,7 +4306,7 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>748</v>
+        <v>54</v>
       </c>
       <c r="E67" s="5">
         <f>1000*$B$4*$B$5*D67/3600000*$B$6</f>
@@ -4340,17 +4316,17 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="19" t="n">
-        <v>0.12</v>
+        <v>0.021</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="I67" s="20">
         <f>H67-G67</f>
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
       <c r="K67" s="21">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4365,21 +4341,21 @@
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="D68" s="18" t="n">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="E68" s="5">
         <f>1000*$B$4*$B$5*D68/3600000*$B$6</f>
@@ -4389,7 +4365,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="19" t="n">
-        <v>0.044</v>
+        <v>0.033</v>
       </c>
       <c r="H68" s="18" t="n">
         <v>0.3</v>
@@ -4399,7 +4375,7 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="K68" s="21">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4414,21 +4390,21 @@
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="D69" s="18" t="n">
-        <v>282</v>
+        <v>641</v>
       </c>
       <c r="E69" s="5">
         <f>1000*$B$4*$B$5*D69/3600000*$B$6</f>
@@ -4438,17 +4414,17 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="19" t="n">
-        <v>0.062</v>
+        <v>0.108</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="I69" s="20">
         <f>H69-G69</f>
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="K69" s="21">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4463,21 +4439,21 @@
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>R-20</t>
+          <t>R-18</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="D70" s="18" t="n">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="E70" s="5">
         <f>1000*$B$4*$B$5*D70/3600000*$B$6</f>
@@ -4487,7 +4463,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="19" t="n">
-        <v>0.034</v>
+        <v>0.046</v>
       </c>
       <c r="H70" s="18" t="n">
         <v>0.3</v>
@@ -4497,7 +4473,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="K70" s="21">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4512,41 +4488,41 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>R-21</t>
+          <t>R-18</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>P-55</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="D71" s="18" t="n">
-        <v>96</v>
+        <v>268</v>
       </c>
       <c r="E71" s="5">
         <f>1000*$B$4*$B$5*D71/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F71" s="18" t="n">
-        <v>3.97</v>
+        <v>0.5</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>0.016</v>
+        <v>0.06</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="I71" s="20">
         <f>H71-G71</f>
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="K71" s="21">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4557,6 +4533,55 @@
         <v/>
       </c>
       <c r="M71" s="22" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>P-57</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>P-56</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="E72" s="5">
+        <f>1000*$B$4*$B$5*D72/3600000*$B$6</f>
+        <v/>
+      </c>
+      <c r="F72" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G72" s="19" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="H72" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I72" s="20">
+        <f>H72-G72</f>
+        <v/>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K72" s="21">
+        <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
+        <v/>
+      </c>
+      <c r="L72" s="21">
+        <f>IF(J72&lt;=$B$7,"CUMPLE","GRADAS")</f>
+        <v/>
+      </c>
+      <c r="M72" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4574,7 +4599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4717,7 +4742,7 @@
         </is>
       </c>
       <c r="E5" s="24" t="n">
-        <v>21.94</v>
+        <v>23.99</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>184.5</v>
@@ -4729,7 +4754,7 @@
         <v>184.2</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>184.09</v>
+        <v>184.08</v>
       </c>
       <c r="J5" s="26">
         <f>F5-H5</f>
@@ -4760,7 +4785,7 @@
       </c>
       <c r="Q5" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste, junto al cerco</t>
+          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
         </is>
       </c>
     </row>
@@ -4784,19 +4809,19 @@
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>43.27</v>
+        <v>3.97</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>183.587</v>
+        <v>184.5</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>184.09</v>
+        <v>184.08</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>183.299</v>
+        <v>184.06</v>
       </c>
       <c r="J6" s="26">
         <f>F6-H6</f>
@@ -4827,7 +4852,7 @@
       </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste, junto al cerco</t>
+          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
         </is>
       </c>
     </row>
@@ -4847,23 +4872,23 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>P-04</t>
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>20.75</v>
+        <v>21.26</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>183.587</v>
+        <v>184.5</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>181.838</v>
+        <v>184.5</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>183.299</v>
+        <v>184.06</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>181.588</v>
+        <v>183.954</v>
       </c>
       <c r="J7" s="26">
         <f>F7-H7</f>
@@ -4894,7 +4919,7 @@
       </c>
       <c r="Q7" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste, junto al cerco</t>
+          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4929,7 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -4918,19 +4943,19 @@
         </is>
       </c>
       <c r="E8" s="24" t="n">
-        <v>11.53</v>
+        <v>42.83</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>184.5</v>
+        <v>184.45</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>184.2</v>
+        <v>183.954</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>184.038</v>
+        <v>183.657</v>
       </c>
       <c r="J8" s="26">
         <f>F8-H8</f>
@@ -4961,7 +4986,7 @@
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4996,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -4985,19 +5010,19 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>8.68</v>
+        <v>11.17</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>184.5</v>
+        <v>184.45</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>184.5</v>
+        <v>184.038</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>184.038</v>
+        <v>183.657</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>183.726</v>
+        <v>183.593</v>
       </c>
       <c r="J9" s="26">
         <f>F9-H9</f>
@@ -5028,7 +5053,7 @@
       </c>
       <c r="Q9" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5063,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -5048,23 +5073,23 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>P-07</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>11.47</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>184.5</v>
+        <v>184.038</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>184.487</v>
+        <v>184.002</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>183.726</v>
+        <v>183.593</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>183.668</v>
+        <v>183.557</v>
       </c>
       <c r="J10" s="26">
         <f>F10-H10</f>
@@ -5079,7 +5104,7 @@
         <v/>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N10" s="26">
         <f>E10-M10</f>
@@ -5095,7 +5120,7 @@
       </c>
       <c r="Q10" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
         </is>
       </c>
     </row>
@@ -5115,23 +5140,23 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>P-03</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>4.64</v>
+        <v>11.53</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>184.487</v>
+        <v>184.5</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>183.587</v>
+        <v>184.5</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>183.668</v>
+        <v>184.2</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>183.337</v>
+        <v>184.038</v>
       </c>
       <c r="J11" s="26">
         <f>F11-H11</f>
@@ -5146,7 +5171,7 @@
         <v/>
       </c>
       <c r="M11" s="24" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="N11" s="26">
         <f>E11-M11</f>
@@ -5172,7 +5197,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -5182,11 +5207,11 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>32.31</v>
+        <v>8.68</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>184.5</v>
@@ -5195,10 +5220,10 @@
         <v>184.5</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>184.2</v>
+        <v>184.038</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>184.038</v>
+        <v>183.726</v>
       </c>
       <c r="J12" s="26">
         <f>F12-H12</f>
@@ -5229,7 +5254,7 @@
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: alero sur-oeste del pabellon norte</t>
+          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5264,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -5249,23 +5274,23 @@
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>11.51</v>
+        <v>11.47</v>
       </c>
       <c r="F13" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>184.5</v>
+        <v>184.487</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>184.2</v>
+        <v>183.726</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>184.142</v>
+        <v>183.668</v>
       </c>
       <c r="J13" s="26">
         <f>F13-H13</f>
@@ -5296,7 +5321,7 @@
       </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
+          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
         </is>
       </c>
     </row>
@@ -5306,33 +5331,33 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-10</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-05</t>
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>8.710000000000001</v>
+        <v>2.29</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>184.5</v>
+        <v>184.487</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>184.5</v>
+        <v>184.45</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>184.142</v>
+        <v>183.668</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>183.89</v>
+        <v>183.657</v>
       </c>
       <c r="J14" s="26">
         <f>F14-H14</f>
@@ -5347,7 +5372,7 @@
         <v/>
       </c>
       <c r="M14" s="24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="N14" s="26">
         <f>E14-M14</f>
@@ -5363,7 +5388,7 @@
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
+          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
         </is>
       </c>
     </row>
@@ -5373,21 +5398,21 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>P-06</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>32.81</v>
+        <v>32.31</v>
       </c>
       <c r="F15" s="24" t="n">
         <v>184.5</v>
@@ -5396,10 +5421,10 @@
         <v>184.5</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>183.89</v>
+        <v>184.2</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>183.726</v>
+        <v>184.038</v>
       </c>
       <c r="J15" s="26">
         <f>F15-H15</f>
@@ -5430,7 +5455,7 @@
       </c>
       <c r="Q15" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
+          <t>Pabellones oeste: alero sur-oeste del pabellon norte</t>
         </is>
       </c>
     </row>
@@ -5440,21 +5465,21 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
+          <t>P-12</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
           <t>P-11</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>P-12</t>
-        </is>
-      </c>
       <c r="E16" s="24" t="n">
-        <v>26.1</v>
+        <v>11.51</v>
       </c>
       <c r="F16" s="24" t="n">
         <v>184.5</v>
@@ -5466,7 +5491,7 @@
         <v>184.2</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>184.07</v>
+        <v>184.142</v>
       </c>
       <c r="J16" s="26">
         <f>F16-H16</f>
@@ -5497,7 +5522,7 @@
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5532,12 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>P-12</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -5521,7 +5546,7 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>9.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F17" s="24" t="n">
         <v>184.5</v>
@@ -5530,10 +5555,10 @@
         <v>184.5</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>184.07</v>
+        <v>184.142</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>184.022</v>
+        <v>183.89</v>
       </c>
       <c r="J17" s="26">
         <f>F17-H17</f>
@@ -5548,7 +5573,7 @@
         <v/>
       </c>
       <c r="M17" s="24" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="N17" s="26">
         <f>E17-M17</f>
@@ -5564,7 +5589,7 @@
       </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5599,7 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -5584,11 +5609,11 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-09</t>
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>3.78</v>
+        <v>32.81</v>
       </c>
       <c r="F18" s="24" t="n">
         <v>184.5</v>
@@ -5597,10 +5622,10 @@
         <v>184.5</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>184.022</v>
+        <v>183.89</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>184.003</v>
+        <v>183.726</v>
       </c>
       <c r="J18" s="26">
         <f>F18-H18</f>
@@ -5631,7 +5656,7 @@
       </c>
       <c r="Q18" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5680,7 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>15.97</v>
+        <v>26.1</v>
       </c>
       <c r="F19" s="24" t="n">
         <v>184.5</v>
@@ -5664,10 +5689,10 @@
         <v>184.5</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>184.003</v>
+        <v>184.2</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>183.924</v>
+        <v>184.07</v>
       </c>
       <c r="J19" s="26">
         <f>F19-H19</f>
@@ -5718,11 +5743,11 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>6.79</v>
+        <v>9.43</v>
       </c>
       <c r="F20" s="24" t="n">
         <v>184.5</v>
@@ -5731,10 +5756,10 @@
         <v>184.5</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>183.924</v>
+        <v>184.07</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>183.89</v>
+        <v>184.022</v>
       </c>
       <c r="J20" s="26">
         <f>F20-H20</f>
@@ -5749,7 +5774,7 @@
         <v/>
       </c>
       <c r="M20" s="24" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="N20" s="26">
         <f>E20-M20</f>
@@ -5775,7 +5800,7 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -5785,11 +5810,11 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>11.74</v>
+        <v>3.78</v>
       </c>
       <c r="F21" s="24" t="n">
         <v>184.5</v>
@@ -5798,10 +5823,10 @@
         <v>184.5</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>184.2</v>
+        <v>184.022</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>184.141</v>
+        <v>184.003</v>
       </c>
       <c r="J21" s="26">
         <f>F21-H21</f>
@@ -5832,43 +5857,43 @@
       </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
-          <t>Tramo y=815.97 entre x=896.8 y x=885.1</t>
+          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>P-01</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="E22" s="24" t="n">
-        <v>31.65</v>
+        <v>15.97</v>
       </c>
       <c r="F22" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>183.5</v>
+        <v>184.5</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>184.2</v>
+        <v>184.003</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>183.25</v>
+        <v>183.924</v>
       </c>
       <c r="J22" s="26">
         <f>F22-H22</f>
@@ -5899,43 +5924,43 @@
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
-          <t>Perimetral del frente sur, tramo oeste (baja a D3)</t>
+          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="E23" s="24" t="n">
-        <v>8.779999999999999</v>
+        <v>6.79</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>183.5</v>
+        <v>184.5</v>
       </c>
       <c r="G23" s="24" t="n">
-        <v>183.368</v>
+        <v>184.5</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>183.25</v>
+        <v>183.924</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>183.118</v>
+        <v>183.89</v>
       </c>
       <c r="J23" s="26">
         <f>F23-H23</f>
@@ -5950,7 +5975,7 @@
         <v/>
       </c>
       <c r="M23" s="24" t="n">
-        <v>8.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="N23" s="26">
         <f>E23-M23</f>
@@ -5966,43 +5991,43 @@
       </c>
       <c r="Q23" s="28" t="inlineStr">
         <is>
-          <t>Perimetral del frente sur, tramo oeste (baja a D3)</t>
+          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>6.4</v>
+        <v>11.74</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>183.368</v>
+        <v>184.5</v>
       </c>
       <c r="G24" s="24" t="n">
-        <v>183.242</v>
+        <v>184.5</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>183.118</v>
+        <v>184.2</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>182.992</v>
+        <v>184.141</v>
       </c>
       <c r="J24" s="26">
         <f>F24-H24</f>
@@ -6033,7 +6058,7 @@
       </c>
       <c r="Q24" s="28" t="inlineStr">
         <is>
-          <t>Perimetral del frente sur, tramo oeste (baja a D3)</t>
+          <t>Tramo y=815.97 entre x=896.8 y x=885.1</t>
         </is>
       </c>
     </row>
@@ -6043,33 +6068,33 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>R-23</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="E25" s="24" t="n">
-        <v>0.75</v>
+        <v>11.51</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>183.477</v>
+        <v>184.5</v>
       </c>
       <c r="G25" s="24" t="n">
-        <v>183.46</v>
+        <v>184.5</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>183.177</v>
+        <v>184.2</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>183.173</v>
+        <v>184.021</v>
       </c>
       <c r="J25" s="26">
         <f>F25-H25</f>
@@ -6100,7 +6125,7 @@
       </c>
       <c r="Q25" s="28" t="inlineStr">
         <is>
-          <t>Perimetral del frente sur, tramo este (baja a D3)</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6110,33 +6135,33 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>R-23</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="E26" s="24" t="n">
-        <v>12.54</v>
+        <v>17.85</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>183.46</v>
+        <v>184.5</v>
       </c>
       <c r="G26" s="24" t="n">
-        <v>183.242</v>
+        <v>184.5</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>183.173</v>
+        <v>184.021</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>182.992</v>
+        <v>183.932</v>
       </c>
       <c r="J26" s="26">
         <f>F26-H26</f>
@@ -6167,7 +6192,7 @@
       </c>
       <c r="Q26" s="28" t="inlineStr">
         <is>
-          <t>Perimetral del frente sur, tramo este (baja a D3)</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6177,21 +6202,21 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="E27" s="24" t="n">
-        <v>11.51</v>
+        <v>6.12</v>
       </c>
       <c r="F27" s="24" t="n">
         <v>184.5</v>
@@ -6200,10 +6225,10 @@
         <v>184.5</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>184.2</v>
+        <v>183.932</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>184.021</v>
+        <v>183.901</v>
       </c>
       <c r="J27" s="26">
         <f>F27-H27</f>
@@ -6234,7 +6259,7 @@
       </c>
       <c r="Q27" s="28" t="inlineStr">
         <is>
-          <t>Patio central: lado oeste, y=815.97 y bajada x=919.6 directa a D3</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6244,12 +6269,12 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -6258,7 +6283,7 @@
         </is>
       </c>
       <c r="E28" s="24" t="n">
-        <v>17.85</v>
+        <v>22.77</v>
       </c>
       <c r="F28" s="24" t="n">
         <v>184.5</v>
@@ -6267,10 +6292,10 @@
         <v>184.5</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>184.021</v>
+        <v>183.901</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>183.932</v>
+        <v>183.787</v>
       </c>
       <c r="J28" s="26">
         <f>F28-H28</f>
@@ -6301,7 +6326,7 @@
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
-          <t>Patio central: lado oeste, y=815.97 y bajada x=919.6 directa a D3</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6336,7 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -6321,23 +6346,23 @@
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>6.12</v>
+        <v>14.84</v>
       </c>
       <c r="F29" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G29" s="24" t="n">
-        <v>184.5</v>
+        <v>184.413</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>183.932</v>
+        <v>183.787</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>183.901</v>
+        <v>183.713</v>
       </c>
       <c r="J29" s="26">
         <f>F29-H29</f>
@@ -6368,7 +6393,7 @@
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
-          <t>Patio central: lado oeste, y=815.97 y bajada x=919.6 directa a D3</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6378,33 +6403,33 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="E30" s="24" t="n">
-        <v>22.77</v>
+        <v>7.96</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>184.5</v>
+        <v>184.413</v>
       </c>
       <c r="G30" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>183.901</v>
+        <v>183.713</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>183.787</v>
+        <v>183.673</v>
       </c>
       <c r="J30" s="26">
         <f>F30-H30</f>
@@ -6419,7 +6444,7 @@
         <v/>
       </c>
       <c r="M30" s="24" t="n">
-        <v>0</v>
+        <v>7.96</v>
       </c>
       <c r="N30" s="26">
         <f>E30-M30</f>
@@ -6435,7 +6460,7 @@
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
-          <t>Patio central: lado oeste, y=815.97 y bajada x=919.6 directa a D3</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6445,33 +6470,33 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="E31" s="24" t="n">
-        <v>15.44</v>
+        <v>6.69</v>
       </c>
       <c r="F31" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>184.339</v>
+        <v>183.852</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>183.787</v>
+        <v>183.673</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>183.71</v>
+        <v>183.565</v>
       </c>
       <c r="J31" s="26">
         <f>F31-H31</f>
@@ -6486,7 +6511,7 @@
         <v/>
       </c>
       <c r="M31" s="24" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="N31" s="26">
         <f>E31-M31</f>
@@ -6502,7 +6527,7 @@
       </c>
       <c r="Q31" s="28" t="inlineStr">
         <is>
-          <t>Patio central: lado oeste, y=815.97 y bajada x=919.6 directa a D3</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6512,33 +6537,33 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="E32" s="24" t="n">
-        <v>9.630000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>184.339</v>
+        <v>183.852</v>
       </c>
       <c r="G32" s="24" t="n">
-        <v>183.242</v>
+        <v>184</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>183.71</v>
+        <v>183.565</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>182.992</v>
+        <v>183.434</v>
       </c>
       <c r="J32" s="26">
         <f>F32-H32</f>
@@ -6553,7 +6578,7 @@
         <v/>
       </c>
       <c r="M32" s="24" t="n">
-        <v>9.630000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N32" s="26">
         <f>E32-M32</f>
@@ -6569,7 +6594,7 @@
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
-          <t>Patio central: lado oeste, y=815.97 y bajada x=919.6 directa a D3</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6579,33 +6604,33 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="E33" s="24" t="n">
-        <v>35.8</v>
+        <v>0.6</v>
       </c>
       <c r="F33" s="24" t="n">
-        <v>184.5</v>
+        <v>184</v>
       </c>
       <c r="G33" s="24" t="n">
-        <v>184.5</v>
+        <v>183.836</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>184.2</v>
+        <v>183.434</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>184.021</v>
+        <v>183.431</v>
       </c>
       <c r="J33" s="26">
         <f>F33-H33</f>
@@ -6620,7 +6645,7 @@
         <v/>
       </c>
       <c r="M33" s="24" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N33" s="26">
         <f>E33-M33</f>
@@ -6636,7 +6661,7 @@
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
-          <t>Patio central: alero sur del pabellon norte (y=839.94)</t>
+          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6646,17 +6671,17 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="E34" s="24" t="n">
@@ -6703,7 +6728,7 @@
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
-          <t>Patio central: y=822.09</t>
+          <t>Patio central: alero sur del pabellon norte (y=839.94)</t>
         </is>
       </c>
     </row>
@@ -6713,21 +6738,21 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="E35" s="24" t="n">
-        <v>17.82</v>
+        <v>35.8</v>
       </c>
       <c r="F35" s="24" t="n">
         <v>184.5</v>
@@ -6739,7 +6764,7 @@
         <v>184.2</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>184.111</v>
+        <v>184.021</v>
       </c>
       <c r="J35" s="26">
         <f>F35-H35</f>
@@ -6770,7 +6795,7 @@
       </c>
       <c r="Q35" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>Patio central: y=822.09</t>
         </is>
       </c>
     </row>
@@ -6780,21 +6805,21 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="E36" s="24" t="n">
-        <v>13.53</v>
+        <v>17.82</v>
       </c>
       <c r="F36" s="24" t="n">
         <v>184.5</v>
@@ -6803,10 +6828,10 @@
         <v>184.5</v>
       </c>
       <c r="H36" s="25" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I36" s="25" t="n">
         <v>184.111</v>
-      </c>
-      <c r="I36" s="25" t="n">
-        <v>184.043</v>
       </c>
       <c r="J36" s="26">
         <f>F36-H36</f>
@@ -6847,21 +6872,21 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="E37" s="24" t="n">
-        <v>3.88</v>
+        <v>13.53</v>
       </c>
       <c r="F37" s="24" t="n">
         <v>184.5</v>
@@ -6870,10 +6895,10 @@
         <v>184.5</v>
       </c>
       <c r="H37" s="25" t="n">
+        <v>184.111</v>
+      </c>
+      <c r="I37" s="25" t="n">
         <v>184.043</v>
-      </c>
-      <c r="I37" s="25" t="n">
-        <v>184.024</v>
       </c>
       <c r="J37" s="26">
         <f>F37-H37</f>
@@ -6914,21 +6939,21 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="E38" s="24" t="n">
-        <v>17.85</v>
+        <v>3.88</v>
       </c>
       <c r="F38" s="24" t="n">
         <v>184.5</v>
@@ -6937,10 +6962,10 @@
         <v>184.5</v>
       </c>
       <c r="H38" s="25" t="n">
+        <v>184.043</v>
+      </c>
+      <c r="I38" s="25" t="n">
         <v>184.024</v>
-      </c>
-      <c r="I38" s="25" t="n">
-        <v>183.935</v>
       </c>
       <c r="J38" s="26">
         <f>F38-H38</f>
@@ -6981,21 +7006,21 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="E39" s="24" t="n">
-        <v>6.12</v>
+        <v>17.85</v>
       </c>
       <c r="F39" s="24" t="n">
         <v>184.5</v>
@@ -7004,10 +7029,10 @@
         <v>184.5</v>
       </c>
       <c r="H39" s="25" t="n">
+        <v>184.024</v>
+      </c>
+      <c r="I39" s="25" t="n">
         <v>183.935</v>
-      </c>
-      <c r="I39" s="25" t="n">
-        <v>183.904</v>
       </c>
       <c r="J39" s="26">
         <f>F39-H39</f>
@@ -7048,21 +7073,21 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="E40" s="24" t="n">
-        <v>13.03</v>
+        <v>6.12</v>
       </c>
       <c r="F40" s="24" t="n">
         <v>184.5</v>
@@ -7071,10 +7096,10 @@
         <v>184.5</v>
       </c>
       <c r="H40" s="25" t="n">
+        <v>183.935</v>
+      </c>
+      <c r="I40" s="25" t="n">
         <v>183.904</v>
-      </c>
-      <c r="I40" s="25" t="n">
-        <v>183.839</v>
       </c>
       <c r="J40" s="26">
         <f>F40-H40</f>
@@ -7115,21 +7140,21 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="E41" s="24" t="n">
-        <v>11.57</v>
+        <v>13.03</v>
       </c>
       <c r="F41" s="24" t="n">
         <v>184.5</v>
@@ -7138,10 +7163,10 @@
         <v>184.5</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>184.2</v>
+        <v>183.904</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>184.142</v>
+        <v>183.839</v>
       </c>
       <c r="J41" s="26">
         <f>F41-H41</f>
@@ -7172,7 +7197,7 @@
       </c>
       <c r="Q41" s="28" t="inlineStr">
         <is>
-          <t>Bajada x=937.3 al frente sur</t>
+          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
         </is>
       </c>
     </row>
@@ -7182,33 +7207,33 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="E42" s="24" t="n">
-        <v>14.35</v>
+        <v>11.57</v>
       </c>
       <c r="F42" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G42" s="24" t="n">
-        <v>183.46</v>
+        <v>184.5</v>
       </c>
       <c r="H42" s="25" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I42" s="25" t="n">
         <v>184.142</v>
-      </c>
-      <c r="I42" s="25" t="n">
-        <v>183.21</v>
       </c>
       <c r="J42" s="26">
         <f>F42-H42</f>
@@ -7223,7 +7248,7 @@
         <v/>
       </c>
       <c r="M42" s="24" t="n">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="N42" s="26">
         <f>E42-M42</f>
@@ -7239,43 +7264,43 @@
       </c>
       <c r="Q42" s="28" t="inlineStr">
         <is>
-          <t>Bajada x=937.3 al frente sur</t>
+          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>P-34</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="E43" s="24" t="n">
-        <v>45.04</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F43" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>184.353</v>
+        <v>184.5</v>
       </c>
       <c r="H43" s="25" t="n">
-        <v>184.2</v>
+        <v>184.142</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>183.906</v>
+        <v>184.096</v>
       </c>
       <c r="J43" s="26">
         <f>F43-H43</f>
@@ -7290,7 +7315,7 @@
         <v/>
       </c>
       <c r="M43" s="24" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N43" s="26">
         <f>E43-M43</f>
@@ -7306,43 +7331,43 @@
       </c>
       <c r="Q43" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este, junto al cerco</t>
+          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="E44" s="24" t="n">
-        <v>2.38</v>
+        <v>1.64</v>
       </c>
       <c r="F44" s="24" t="n">
-        <v>184.353</v>
+        <v>184.5</v>
       </c>
       <c r="G44" s="24" t="n">
-        <v>184.339</v>
+        <v>184.5</v>
       </c>
       <c r="H44" s="25" t="n">
-        <v>183.906</v>
+        <v>184.096</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>183.894</v>
+        <v>184.087</v>
       </c>
       <c r="J44" s="26">
         <f>F44-H44</f>
@@ -7357,7 +7382,7 @@
         <v/>
       </c>
       <c r="M44" s="24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="N44" s="26">
         <f>E44-M44</f>
@@ -7373,43 +7398,43 @@
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este, junto al cerco</t>
+          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="E45" s="24" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="F45" s="24" t="n">
-        <v>184.339</v>
+        <v>184.5</v>
       </c>
       <c r="G45" s="24" t="n">
-        <v>183.966</v>
+        <v>184</v>
       </c>
       <c r="H45" s="25" t="n">
-        <v>183.894</v>
+        <v>184.087</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>183.716</v>
+        <v>183.75</v>
       </c>
       <c r="J45" s="26">
         <f>F45-H45</f>
@@ -7424,7 +7449,7 @@
         <v/>
       </c>
       <c r="M45" s="24" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="N45" s="26">
         <f>E45-M45</f>
@@ -7440,7 +7465,7 @@
       </c>
       <c r="Q45" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este, junto al cerco</t>
+          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -7450,33 +7475,33 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="E46" s="24" t="n">
-        <v>14.11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F46" s="24" t="n">
-        <v>183.966</v>
+        <v>184.5</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>182.475</v>
+        <v>184.5</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>183.716</v>
+        <v>184.2</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>182.225</v>
+        <v>184.095</v>
       </c>
       <c r="J46" s="26">
         <f>F46-H46</f>
@@ -7507,7 +7532,7 @@
       </c>
       <c r="Q46" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este, junto al cerco</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7517,33 +7542,33 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="E47" s="24" t="n">
-        <v>8.630000000000001</v>
+        <v>35.28</v>
       </c>
       <c r="F47" s="24" t="n">
-        <v>182.475</v>
+        <v>184.5</v>
       </c>
       <c r="G47" s="24" t="n">
-        <v>181.763</v>
+        <v>184.5</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>182.225</v>
+        <v>184.095</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>181.495</v>
+        <v>183.919</v>
       </c>
       <c r="J47" s="26">
         <f>F47-H47</f>
@@ -7574,7 +7599,7 @@
       </c>
       <c r="Q47" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este, junto al cerco</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7584,33 +7609,33 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>R-22</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="E48" s="24" t="n">
-        <v>9.029999999999999</v>
+        <v>20.59</v>
       </c>
       <c r="F48" s="24" t="n">
-        <v>182.798</v>
+        <v>184.5</v>
       </c>
       <c r="G48" s="24" t="n">
-        <v>181.763</v>
+        <v>181.803</v>
       </c>
       <c r="H48" s="25" t="n">
-        <v>182.498</v>
+        <v>183.919</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>181.495</v>
+        <v>181.553</v>
       </c>
       <c r="J48" s="26">
         <f>F48-H48</f>
@@ -7641,7 +7666,7 @@
       </c>
       <c r="Q48" s="28" t="inlineStr">
         <is>
-          <t>Remate norte de la perimetral este (baja hacia la descarga)</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7651,33 +7676,33 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="E49" s="24" t="n">
-        <v>20.98</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>184.5</v>
+        <v>181.803</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>184.5</v>
+        <v>181.329</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>184.2</v>
+        <v>181.553</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>184.095</v>
+        <v>181.071</v>
       </c>
       <c r="J49" s="26">
         <f>F49-H49</f>
@@ -7708,7 +7733,7 @@
       </c>
       <c r="Q49" s="28" t="inlineStr">
         <is>
-          <t>Losa deportiva: lados sur y este</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7718,33 +7743,33 @@
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="E50" s="24" t="n">
-        <v>35.28</v>
+        <v>12.29</v>
       </c>
       <c r="F50" s="24" t="n">
-        <v>184.5</v>
+        <v>181.329</v>
       </c>
       <c r="G50" s="24" t="n">
-        <v>184.5</v>
+        <v>180.522</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>184.095</v>
+        <v>181.071</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>183.919</v>
+        <v>180.239</v>
       </c>
       <c r="J50" s="26">
         <f>F50-H50</f>
@@ -7759,7 +7784,7 @@
         <v/>
       </c>
       <c r="M50" s="24" t="n">
-        <v>0</v>
+        <v>12.29</v>
       </c>
       <c r="N50" s="26">
         <f>E50-M50</f>
@@ -7775,7 +7800,7 @@
       </c>
       <c r="Q50" s="28" t="inlineStr">
         <is>
-          <t>Losa deportiva: lados sur y este</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7785,33 +7810,33 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="E51" s="24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F51" s="24" t="n">
-        <v>184.5</v>
+        <v>180.522</v>
       </c>
       <c r="G51" s="24" t="n">
-        <v>184.353</v>
+        <v>180.623</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>183.919</v>
+        <v>180.239</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>183.906</v>
+        <v>180.207</v>
       </c>
       <c r="J51" s="26">
         <f>F51-H51</f>
@@ -7826,7 +7851,7 @@
         <v/>
       </c>
       <c r="M51" s="24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="N51" s="26">
         <f>E51-M51</f>
@@ -7842,7 +7867,7 @@
       </c>
       <c r="Q51" s="28" t="inlineStr">
         <is>
-          <t>Losa deportiva: lados sur y este</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7852,33 +7877,33 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E52" s="24" t="n">
-        <v>24.38</v>
+        <v>0.6</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>184.5</v>
+        <v>180.623</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>184.5</v>
+        <v>180.561</v>
       </c>
       <c r="H52" s="25" t="n">
-        <v>184.2</v>
+        <v>180.207</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>184.078</v>
+        <v>180.175</v>
       </c>
       <c r="J52" s="26">
         <f>F52-H52</f>
@@ -7893,7 +7918,7 @@
         <v/>
       </c>
       <c r="M52" s="24" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N52" s="26">
         <f>E52-M52</f>
@@ -7909,7 +7934,7 @@
       </c>
       <c r="Q52" s="28" t="inlineStr">
         <is>
-          <t>Losa deportiva: lado norte</t>
+          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
         </is>
       </c>
     </row>
@@ -7919,21 +7944,21 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>P-45</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="E53" s="24" t="n">
-        <v>17.06</v>
+        <v>20.98</v>
       </c>
       <c r="F53" s="24" t="n">
         <v>184.5</v>
@@ -7945,7 +7970,7 @@
         <v>184.2</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>184.115</v>
+        <v>184.095</v>
       </c>
       <c r="J53" s="26">
         <f>F53-H53</f>
@@ -7976,7 +8001,7 @@
       </c>
       <c r="Q53" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>Losa deportiva: lado sur</t>
         </is>
       </c>
     </row>
@@ -7986,21 +8011,21 @@
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-46</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="E54" s="24" t="n">
-        <v>22.85</v>
+        <v>24.38</v>
       </c>
       <c r="F54" s="24" t="n">
         <v>184.5</v>
@@ -8009,10 +8034,10 @@
         <v>184.5</v>
       </c>
       <c r="H54" s="25" t="n">
-        <v>184.115</v>
+        <v>184.2</v>
       </c>
       <c r="I54" s="25" t="n">
-        <v>184</v>
+        <v>184.078</v>
       </c>
       <c r="J54" s="26">
         <f>F54-H54</f>
@@ -8043,7 +8068,7 @@
       </c>
       <c r="Q54" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>Losa deportiva: lado norte</t>
         </is>
       </c>
     </row>
@@ -8053,21 +8078,21 @@
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="E55" s="24" t="n">
-        <v>1.12</v>
+        <v>17.06</v>
       </c>
       <c r="F55" s="24" t="n">
         <v>184.5</v>
@@ -8076,10 +8101,10 @@
         <v>184.5</v>
       </c>
       <c r="H55" s="25" t="n">
-        <v>184</v>
+        <v>184.2</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>183.995</v>
+        <v>184.115</v>
       </c>
       <c r="J55" s="26">
         <f>F55-H55</f>
@@ -8120,21 +8145,21 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="E56" s="24" t="n">
-        <v>19.39</v>
+        <v>22.85</v>
       </c>
       <c r="F56" s="24" t="n">
         <v>184.5</v>
@@ -8143,10 +8168,10 @@
         <v>184.5</v>
       </c>
       <c r="H56" s="25" t="n">
-        <v>183.995</v>
+        <v>184.115</v>
       </c>
       <c r="I56" s="25" t="n">
-        <v>183.898</v>
+        <v>184</v>
       </c>
       <c r="J56" s="26">
         <f>F56-H56</f>
@@ -8187,21 +8212,21 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="E57" s="24" t="n">
-        <v>11.93</v>
+        <v>1.12</v>
       </c>
       <c r="F57" s="24" t="n">
         <v>184.5</v>
@@ -8210,10 +8235,10 @@
         <v>184.5</v>
       </c>
       <c r="H57" s="25" t="n">
-        <v>183.898</v>
+        <v>184</v>
       </c>
       <c r="I57" s="25" t="n">
-        <v>183.838</v>
+        <v>183.995</v>
       </c>
       <c r="J57" s="26">
         <f>F57-H57</f>
@@ -8254,33 +8279,33 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="E58" s="24" t="n">
-        <v>7.79</v>
+        <v>19.39</v>
       </c>
       <c r="F58" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G58" s="24" t="n">
-        <v>182.475</v>
+        <v>184.5</v>
       </c>
       <c r="H58" s="25" t="n">
-        <v>183.838</v>
+        <v>183.995</v>
       </c>
       <c r="I58" s="25" t="n">
-        <v>182.225</v>
+        <v>183.898</v>
       </c>
       <c r="J58" s="26">
         <f>F58-H58</f>
@@ -8295,7 +8320,7 @@
         <v/>
       </c>
       <c r="M58" s="24" t="n">
-        <v>7.79</v>
+        <v>0</v>
       </c>
       <c r="N58" s="26">
         <f>E58-M58</f>
@@ -8321,21 +8346,21 @@
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="E59" s="24" t="n">
-        <v>4.19</v>
+        <v>11.93</v>
       </c>
       <c r="F59" s="24" t="n">
         <v>184.5</v>
@@ -8344,10 +8369,10 @@
         <v>184.5</v>
       </c>
       <c r="H59" s="25" t="n">
-        <v>184.2</v>
+        <v>183.898</v>
       </c>
       <c r="I59" s="25" t="n">
-        <v>184.179</v>
+        <v>183.838</v>
       </c>
       <c r="J59" s="26">
         <f>F59-H59</f>
@@ -8378,7 +8403,7 @@
       </c>
       <c r="Q59" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: tramo y=838.8</t>
+          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
         </is>
       </c>
     </row>
@@ -8388,33 +8413,33 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="C60" s="23" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="E60" s="24" t="n">
-        <v>13.05</v>
+        <v>5.19</v>
       </c>
       <c r="F60" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>184.5</v>
+        <v>181.803</v>
       </c>
       <c r="H60" s="25" t="n">
-        <v>184.2</v>
+        <v>183.838</v>
       </c>
       <c r="I60" s="25" t="n">
-        <v>184.135</v>
+        <v>181.553</v>
       </c>
       <c r="J60" s="26">
         <f>F60-H60</f>
@@ -8429,7 +8454,7 @@
         <v/>
       </c>
       <c r="M60" s="24" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="N60" s="26">
         <f>E60-M60</f>
@@ -8445,7 +8470,7 @@
       </c>
       <c r="Q60" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: x=948.1 e y=851.87</t>
+          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
         </is>
       </c>
     </row>
@@ -8455,12 +8480,12 @@
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
@@ -8469,7 +8494,7 @@
         </is>
       </c>
       <c r="E61" s="24" t="n">
-        <v>23.58</v>
+        <v>4.19</v>
       </c>
       <c r="F61" s="24" t="n">
         <v>184.5</v>
@@ -8478,10 +8503,10 @@
         <v>184.5</v>
       </c>
       <c r="H61" s="25" t="n">
-        <v>184.135</v>
+        <v>184.2</v>
       </c>
       <c r="I61" s="25" t="n">
-        <v>184.017</v>
+        <v>184.179</v>
       </c>
       <c r="J61" s="26">
         <f>F61-H61</f>
@@ -8512,7 +8537,7 @@
       </c>
       <c r="Q61" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: x=948.1 e y=851.87</t>
+          <t>Bloque nor-este: tramo y=838.8</t>
         </is>
       </c>
     </row>
@@ -8522,21 +8547,21 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="C62" s="23" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="E62" s="24" t="n">
-        <v>6.74</v>
+        <v>13.05</v>
       </c>
       <c r="F62" s="24" t="n">
         <v>184.5</v>
@@ -8548,7 +8573,7 @@
         <v>184.2</v>
       </c>
       <c r="I62" s="25" t="n">
-        <v>184.166</v>
+        <v>184.135</v>
       </c>
       <c r="J62" s="26">
         <f>F62-H62</f>
@@ -8579,7 +8604,7 @@
       </c>
       <c r="Q62" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur, lado este) y x=948.1</t>
+          <t>Bloque nor-este: x=948.1 e y=851.87</t>
         </is>
       </c>
     </row>
@@ -8589,21 +8614,21 @@
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="D63" s="23" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="E63" s="24" t="n">
-        <v>1.6</v>
+        <v>23.58</v>
       </c>
       <c r="F63" s="24" t="n">
         <v>184.5</v>
@@ -8612,10 +8637,10 @@
         <v>184.5</v>
       </c>
       <c r="H63" s="25" t="n">
-        <v>184.166</v>
+        <v>184.135</v>
       </c>
       <c r="I63" s="25" t="n">
-        <v>184.158</v>
+        <v>184.017</v>
       </c>
       <c r="J63" s="26">
         <f>F63-H63</f>
@@ -8646,7 +8671,7 @@
       </c>
       <c r="Q63" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur, lado este) y x=948.1</t>
+          <t>Bloque nor-este: x=948.1 e y=851.87</t>
         </is>
       </c>
     </row>
@@ -8656,21 +8681,21 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>R-20</t>
+          <t>R-18</t>
         </is>
       </c>
       <c r="C64" s="23" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="E64" s="24" t="n">
-        <v>1.9</v>
+        <v>6.74</v>
       </c>
       <c r="F64" s="24" t="n">
         <v>184.5</v>
@@ -8682,7 +8707,7 @@
         <v>184.2</v>
       </c>
       <c r="I64" s="25" t="n">
-        <v>184.19</v>
+        <v>184.166</v>
       </c>
       <c r="J64" s="26">
         <f>F64-H64</f>
@@ -8713,43 +8738,43 @@
       </c>
       <c r="Q64" s="28" t="inlineStr">
         <is>
-          <t>Remate y=853.47 al este de x=948.1</t>
+          <t>Bloque norte (alero sur, lado este) y x=948.1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>R-21</t>
+          <t>R-18</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
         <is>
-          <t>P-55</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="D65" s="23" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="E65" s="24" t="n">
-        <v>5.03</v>
+        <v>1.6</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>184.241</v>
+        <v>184.5</v>
       </c>
       <c r="G65" s="24" t="n">
-        <v>183.995</v>
+        <v>184.5</v>
       </c>
       <c r="H65" s="25" t="n">
-        <v>183.941</v>
+        <v>184.166</v>
       </c>
       <c r="I65" s="25" t="n">
-        <v>183.741</v>
+        <v>184.158</v>
       </c>
       <c r="J65" s="26">
         <f>F65-H65</f>
@@ -8780,26 +8805,93 @@
       </c>
       <c r="Q65" s="28" t="inlineStr">
         <is>
-          <t>Cuneta transversal del ingreso sur-este</t>
+          <t>Bloque norte (alero sur, lado este) y x=948.1</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="D66" s="7" t="inlineStr">
+      <c r="A66" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>P-57</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>P-56</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F66" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="G66" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="H66" s="25" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I66" s="25" t="n">
+        <v>184.19</v>
+      </c>
+      <c r="J66" s="26">
+        <f>F66-H66</f>
+        <v/>
+      </c>
+      <c r="K66" s="26">
+        <f>G66-I66</f>
+        <v/>
+      </c>
+      <c r="L66" s="26">
+        <f>100*(H66-I66)/E66</f>
+        <v/>
+      </c>
+      <c r="M66" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="26">
+        <f>E66-M66</f>
+        <v/>
+      </c>
+      <c r="O66" s="26">
+        <f>MAX(MIN(J66,K66)-CRITERIOS!$B$13,0.01)</f>
+        <v/>
+      </c>
+      <c r="P66" s="27">
+        <f>1000*CRITERIOS!$B$5*O66*((CRITERIOS!$B$5*O66)/(CRITERIOS!$B$5+2*O66))^(2/3)*SQRT(MAX(L66/100,CRITERIOS!$B$10))/CRITERIOS!$B$12</f>
+        <v/>
+      </c>
+      <c r="Q66" s="28" t="inlineStr">
+        <is>
+          <t>Remate y=853.47 al este de x=948.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E66" s="8">
-        <f>SUM(E5:E65)</f>
-        <v/>
-      </c>
-      <c r="M66" s="8">
-        <f>SUM(M5:M65)</f>
-        <v/>
-      </c>
-      <c r="N66" s="8">
-        <f>SUM(N5:N65)</f>
+      <c r="E67" s="8">
+        <f>SUM(E5:E66)</f>
+        <v/>
+      </c>
+      <c r="M67" s="8">
+        <f>SUM(M5:M66)</f>
+        <v/>
+      </c>
+      <c r="N67" s="8">
+        <f>SUM(N5:N66)</f>
         <v/>
       </c>
     </row>
@@ -8819,7 +8911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8877,14 +8969,14 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>354879.05</v>
+        <v>354907.615</v>
       </c>
       <c r="C5" s="29" t="n">
-        <v>9249801.720000001</v>
+        <v>9249803.210000001</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>R-01, R-07</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -8896,10 +8988,10 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>354858.75</v>
+        <v>354883.629</v>
       </c>
       <c r="C6" s="29" t="n">
-        <v>9249810.029999999</v>
+        <v>9249803.210000001</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -8915,14 +9007,14 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>354827.49</v>
+        <v>354879.734</v>
       </c>
       <c r="C7" s="29" t="n">
-        <v>9249839.945</v>
+        <v>9249803.987</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>R-01, R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -8934,14 +9026,14 @@
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>354853.1</v>
+        <v>354860.053</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>9249865.699999999</v>
+        <v>9249812.032</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -8953,14 +9045,14 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>354844.95</v>
+        <v>354829.116</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>9249857.550000001</v>
+        <v>9249841.646</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-03</t>
+          <t>R-01, R-02</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -8972,14 +9064,14 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>354838.81</v>
+        <v>354821.044</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>9249851.41</v>
+        <v>9249849.373</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-04</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -8991,10 +9083,10 @@
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>354830.7</v>
+        <v>354853.1</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>9249843.300000001</v>
+        <v>9249865.699999999</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -9010,14 +9102,14 @@
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>354867.8</v>
+        <v>354844.95</v>
       </c>
       <c r="C12" s="29" t="n">
-        <v>9249834.699999999</v>
+        <v>9249857.550000001</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>R-03, R-04</t>
+          <t>R-02, R-03</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -9029,14 +9121,14 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>354876.1</v>
+        <v>354838.81</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>9249842.67</v>
+        <v>9249851.41</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-02, R-04</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -9048,14 +9140,14 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>354862</v>
+        <v>354830.7</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>9249828.199999999</v>
+        <v>9249843.300000001</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>R-04, R-05</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -9067,14 +9159,14 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>354884.91</v>
+        <v>354867.8</v>
       </c>
       <c r="C15" s="29" t="n">
-        <v>9249851.5</v>
+        <v>9249834.699999999</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-03, R-04</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -9086,14 +9178,14 @@
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>354884.91</v>
+        <v>354876.1</v>
       </c>
       <c r="C16" s="29" t="n">
-        <v>9249825.4</v>
+        <v>9249842.67</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -9105,14 +9197,14 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>354885.1</v>
+        <v>354862</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249828.199999999</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>R-05, R-06</t>
+          <t>R-04, R-05</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -9124,10 +9216,10 @@
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>354881.6</v>
+        <v>354884.91</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>9249817.4</v>
+        <v>9249851.5</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
@@ -9143,10 +9235,10 @@
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>354866.8</v>
+        <v>354884.91</v>
       </c>
       <c r="C19" s="29" t="n">
-        <v>9249823.4</v>
+        <v>9249825.4</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
@@ -9162,14 +9254,14 @@
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>354896.84</v>
+        <v>354885.1</v>
       </c>
       <c r="C20" s="29" t="n">
         <v>9249815.970000001</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>R-06, R-08</t>
+          <t>R-05, R-06</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -9181,14 +9273,14 @@
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>354910.09</v>
+        <v>354881.6</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>9249795.529999999</v>
+        <v>9249817.4</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -9200,14 +9292,14 @@
         </is>
       </c>
       <c r="B22" s="29" t="n">
-        <v>354918.7</v>
+        <v>354866.8</v>
       </c>
       <c r="C22" s="29" t="n">
-        <v>9249793.800000001</v>
+        <v>9249823.4</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -9219,14 +9311,14 @@
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>354938</v>
+        <v>354896.84</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>9249789.9</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>R-23</t>
+          <t>R-06, R-07</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -9238,14 +9330,14 @@
         </is>
       </c>
       <c r="B24" s="29" t="n">
-        <v>354937.26</v>
+        <v>354896.84</v>
       </c>
       <c r="C24" s="29" t="n">
-        <v>9249790.050000001</v>
+        <v>9249851.449999999</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>R-23, R-12</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -9260,11 +9352,11 @@
         <v>354896.84</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>9249851.449999999</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07, R-08</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -9279,11 +9371,11 @@
         <v>354896.84</v>
       </c>
       <c r="C26" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249822.09</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>R-08, R-09</t>
+          <t>R-07, R-09</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -9295,14 +9387,14 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>354896.84</v>
+        <v>354919.61</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>9249822.09</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>R-08, R-10</t>
+          <t>R-07, R-10</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -9317,11 +9409,11 @@
         <v>354919.61</v>
       </c>
       <c r="C28" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249801.130000001</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>R-08, R-11</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -9333,14 +9425,14 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>354919.61</v>
+        <v>354927.57</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>9249800.529999999</v>
+        <v>9249801.130000001</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -9352,14 +9444,14 @@
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>354932.64</v>
+        <v>354927.57</v>
       </c>
       <c r="C30" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249794.442</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>R-09, R-11</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -9371,14 +9463,14 @@
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>354932.64</v>
+        <v>354935.617</v>
       </c>
       <c r="C31" s="29" t="n">
-        <v>9249822.09</v>
+        <v>9249792.835999999</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>R-10, R-11</t>
+          <t>R-07, R-11</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -9390,14 +9482,14 @@
         </is>
       </c>
       <c r="B32" s="29" t="n">
-        <v>354918.7</v>
+        <v>354932.64</v>
       </c>
       <c r="C32" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-08, R-10</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -9409,14 +9501,14 @@
         </is>
       </c>
       <c r="B33" s="29" t="n">
-        <v>354936.52</v>
+        <v>354932.64</v>
       </c>
       <c r="C33" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249822.09</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-09, R-10</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -9428,14 +9520,14 @@
         </is>
       </c>
       <c r="B34" s="29" t="n">
-        <v>354936.52</v>
+        <v>354918.7</v>
       </c>
       <c r="C34" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249853.470000001</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -9447,14 +9539,14 @@
         </is>
       </c>
       <c r="B35" s="29" t="n">
-        <v>354932.64</v>
+        <v>354936.52</v>
       </c>
       <c r="C35" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249853.470000001</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -9466,14 +9558,14 @@
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>354937.26</v>
+        <v>354936.52</v>
       </c>
       <c r="C36" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -9485,14 +9577,14 @@
         </is>
       </c>
       <c r="B37" s="29" t="n">
-        <v>354937.26</v>
+        <v>354932.64</v>
       </c>
       <c r="C37" s="29" t="n">
-        <v>9249804.4</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -9504,14 +9596,14 @@
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>354979.5</v>
+        <v>354937.26</v>
       </c>
       <c r="C38" s="29" t="n">
-        <v>9249786.24</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -9523,14 +9615,14 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>354979.5</v>
+        <v>354937.26</v>
       </c>
       <c r="C39" s="29" t="n">
-        <v>9249831.279999999</v>
+        <v>9249804.4</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>R-13, R-14</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -9542,14 +9634,14 @@
         </is>
       </c>
       <c r="B40" s="29" t="n">
-        <v>354979.5</v>
+        <v>354937.26</v>
       </c>
       <c r="C40" s="29" t="n">
-        <v>9249833.66</v>
+        <v>9249795.1</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -9561,14 +9653,14 @@
         </is>
       </c>
       <c r="B41" s="29" t="n">
-        <v>354979.5</v>
+        <v>354935.617</v>
       </c>
       <c r="C41" s="29" t="n">
-        <v>9249837.76</v>
+        <v>9249795.1</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -9580,14 +9672,14 @@
         </is>
       </c>
       <c r="B42" s="29" t="n">
-        <v>354979.5</v>
+        <v>354976.9</v>
       </c>
       <c r="C42" s="29" t="n">
-        <v>9249851.869999999</v>
+        <v>9249786.300000001</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>R-13, R-16</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -9599,14 +9691,14 @@
         </is>
       </c>
       <c r="B43" s="29" t="n">
-        <v>354979.5</v>
+        <v>354976.9</v>
       </c>
       <c r="C43" s="29" t="n">
-        <v>9249869.529999999</v>
+        <v>9249796</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>R-22</t>
+          <t>R-12, R-13</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -9618,14 +9710,14 @@
         </is>
       </c>
       <c r="B44" s="29" t="n">
-        <v>354955.92</v>
+        <v>354976.9</v>
       </c>
       <c r="C44" s="29" t="n">
-        <v>9249796</v>
+        <v>9249831.279999999</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12, R-14</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -9640,11 +9732,11 @@
         <v>354976.9</v>
       </c>
       <c r="C45" s="29" t="n">
-        <v>9249796</v>
+        <v>9249851.869999999</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>R-12, R-15</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -9659,11 +9751,11 @@
         <v>354976.9</v>
       </c>
       <c r="C46" s="29" t="n">
-        <v>9249831.279999999</v>
+        <v>9249860.5</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>R-14, R-15</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -9675,14 +9767,14 @@
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>354952.52</v>
+        <v>354968</v>
       </c>
       <c r="C47" s="29" t="n">
-        <v>9249831.279999999</v>
+        <v>9249868.98</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -9694,14 +9786,14 @@
         </is>
       </c>
       <c r="B48" s="29" t="n">
-        <v>354935.26</v>
+        <v>354965.5</v>
       </c>
       <c r="C48" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249868.98</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -9713,14 +9805,14 @@
         </is>
       </c>
       <c r="B49" s="29" t="n">
-        <v>354952.32</v>
+        <v>354955.92</v>
       </c>
       <c r="C49" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249796</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -9732,14 +9824,14 @@
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>354952.32</v>
+        <v>354952.52</v>
       </c>
       <c r="C50" s="29" t="n">
-        <v>9249838.82</v>
+        <v>9249831.279999999</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>R-16, R-17</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -9751,14 +9843,14 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>354952.32</v>
+        <v>354935.26</v>
       </c>
       <c r="C51" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -9770,14 +9862,14 @@
         </is>
       </c>
       <c r="B52" s="29" t="n">
-        <v>354971.71</v>
+        <v>354952.32</v>
       </c>
       <c r="C52" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -9789,14 +9881,14 @@
         </is>
       </c>
       <c r="B53" s="29" t="n">
-        <v>354971.71</v>
+        <v>354952.32</v>
       </c>
       <c r="C53" s="29" t="n">
-        <v>9249851.869999999</v>
+        <v>9249838.82</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>R-16, R-18</t>
+          <t>R-15, R-16</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -9808,14 +9900,14 @@
         </is>
       </c>
       <c r="B54" s="29" t="n">
-        <v>354948.13</v>
+        <v>354952.32</v>
       </c>
       <c r="C54" s="29" t="n">
-        <v>9249838.82</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>R-17, R-18</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -9827,14 +9919,14 @@
         </is>
       </c>
       <c r="B55" s="29" t="n">
-        <v>354948.13</v>
+        <v>354971.71</v>
       </c>
       <c r="C55" s="29" t="n">
-        <v>9249851.869999999</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>R-18, R-19</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -9846,14 +9938,14 @@
         </is>
       </c>
       <c r="B56" s="29" t="n">
-        <v>354941.39</v>
+        <v>354971.71</v>
       </c>
       <c r="C56" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249851.869999999</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-15, R-17</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -9868,11 +9960,11 @@
         <v>354948.13</v>
       </c>
       <c r="C57" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249838.82</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>R-19, R-20</t>
+          <t>R-16, R-17</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -9884,14 +9976,14 @@
         </is>
       </c>
       <c r="B58" s="29" t="n">
-        <v>354950.03</v>
+        <v>354948.13</v>
       </c>
       <c r="C58" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249851.869999999</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>R-20</t>
+          <t>R-17, R-18</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -9903,107 +9995,122 @@
         </is>
       </c>
       <c r="B59" s="29" t="n">
-        <v>354974.7</v>
+        <v>354941.39</v>
       </c>
       <c r="C59" s="29" t="n">
-        <v>9249782.6</v>
+        <v>9249853.470000001</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>R-21</t>
+          <t>R-18</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="n">
-        <v>354812.5</v>
-      </c>
-      <c r="C60" s="31" t="n">
-        <v>9249854.289999999</v>
-      </c>
-      <c r="D60" s="30" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="E60" s="30" t="inlineStr">
-        <is>
-          <t>Esquina oeste: al terreno natural (quebrada al oeste / nor-oeste)</t>
-        </is>
-      </c>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>P-56</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="n">
+        <v>354948.13</v>
+      </c>
+      <c r="C60" s="29" t="n">
+        <v>9249853.470000001</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>R-18, R-19</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B61" s="31" t="n">
-        <v>354979.5</v>
-      </c>
-      <c r="C61" s="31" t="n">
-        <v>9249860.5</v>
-      </c>
-      <c r="D61" s="30" t="inlineStr">
-        <is>
-          <t>R-13, R-22</t>
-        </is>
-      </c>
-      <c r="E61" s="30" t="inlineStr">
-        <is>
-          <t>Perimetral este, punto bajo (y = 860.5): a la cabecera de la quebrada del norte</t>
-        </is>
-      </c>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>P-57</t>
+        </is>
+      </c>
+      <c r="B61" s="29" t="n">
+        <v>354950.03</v>
+      </c>
+      <c r="C61" s="29" t="n">
+        <v>9249853.470000001</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B62" s="31" t="n">
-        <v>354924.97</v>
+        <v>354820.629</v>
       </c>
       <c r="C62" s="31" t="n">
-        <v>9249792.533</v>
+        <v>9249848.939999999</v>
       </c>
       <c r="D62" s="30" t="inlineStr">
         <is>
-          <t>R-07, R-23, R-08</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="E62" s="30" t="inlineStr">
         <is>
-          <t>Frente sur, punto bajo (x = 925.0): al Jr. Alfonso Ugarte en su punto bajo (183.00) - confirmar evacuacion de la calle</t>
+          <t>Cerco sur-oeste (lado C22-C1, x = 820.7): al talud natural que baja a la quebrada del oeste</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B63" s="31" t="n">
-        <v>354969.77</v>
+        <v>354965.5</v>
       </c>
       <c r="C63" s="31" t="n">
-        <v>9249783.6</v>
+        <v>9249869.58</v>
       </c>
       <c r="D63" s="30" t="inlineStr">
         <is>
-          <t>R-21</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E63" s="30" t="inlineStr">
         <is>
-          <t>Ingreso sur-este: a la calzada del Jr. Alfonso Ugarte, que baja hacia su punto bajo</t>
+          <t>Cerco norte (x = 965.5): poza de salida que rebalsa a nivel del fondo de la hondonada natural (baja a la quebrada del norte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n">
+        <v>354935.5</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>9249792.248</v>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>Cerco sur junto a C14 (x = 935.5): al terreno exterior que baja al Jr. Alfonso Ugarte (183.00)</t>
         </is>
       </c>
     </row>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -619,46 +619,46 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,1,TRAMOS!$E$5:$E$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,1,TRAMOS!$E$5:$E$70)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,1,TRAMOS!$N$5:$N$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,1,TRAMOS!$N$5:$N$70)</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,1,TRAMOS!$M$5:$M$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,1,TRAMOS!$M$5:$M$70)</f>
         <v/>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.827</v>
+        <v>0.832</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>D1: Cerco sur-oeste (lado C22-C1, x = 820.7): al talud natural que baja a la quebrada del oeste</t>
+          <t>D1: Cerco sur-oeste (lado C22-C1, x = 820.1): al talud natural que baja a la quebrada del oeste</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA 2 - FRENTE SUR (descarga D3)</t>
+          <t>SISTEMA 2 - CENTRO Y FRENTE SUR (descarga D3)</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,2,TRAMOS!$E$5:$E$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,2,TRAMOS!$E$5:$E$70)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,2,TRAMOS!$N$5:$N$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,2,TRAMOS!$N$5:$N$70)</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,2,TRAMOS!$M$5:$M$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,2,TRAMOS!$M$5:$M$70)</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.834</v>
+        <v>0.853</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -669,23 +669,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SISTEMA 3 - NOR-ESTE (descarga D2)</t>
+          <t>SISTEMA 3 - NOR-ESTE Y LOSA (descarga D2)</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,3,TRAMOS!$E$5:$E$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,3,TRAMOS!$E$5:$E$70)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,3,TRAMOS!$N$5:$N$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,3,TRAMOS!$N$5:$N$70)</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>SUMIF(TRAMOS!$A$5:$A$66,3,TRAMOS!$M$5:$M$66)</f>
+        <f>SUMIF(TRAMOS!$A$5:$A$70,3,TRAMOS!$M$5:$M$70)</f>
         <v/>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.662</v>
+        <v>0.734</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -694,21 +694,48 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SISTEMA 4 - NORTE (descarga D4)</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>SUMIF(TRAMOS!$A$5:$A$70,4,TRAMOS!$E$5:$E$70)</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
+        <f>SUMIF(TRAMOS!$A$5:$A$70,4,TRAMOS!$N$5:$N$70)</f>
+        <v/>
+      </c>
+      <c r="D8" s="5">
+        <f>SUMIF(TRAMOS!$A$5:$A$70,4,TRAMOS!$M$5:$M$70)</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>D4: Cerco norte (lado C3-C4, x = 911.0): al talud natural que baja a la quebrada del norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="8">
-        <f>SUM(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="8">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="8">
-        <f>SUM(D5:D7)</f>
+      <c r="B9" s="8">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="8">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>SUM(D5:D8)</f>
         <v/>
       </c>
     </row>
@@ -722,7 +749,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>1. Planteamiento preliminar sobre los ejes de cunetas del plano PLANTA_GENERAL_590_2 (capas 0_ CUNETAS y 0_REJILLA).</t>
+          <t>1. Planteamiento preliminar: ejes de cuneta en las lineas magenta del plano PLANTA_GENERAL_590 ULTIMA VERSION (lados de cada bloque, techos a dos aguas) y uniones hasta las descargas.</t>
         </is>
       </c>
     </row>
@@ -750,7 +777,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>5. D1 y D3 salen por un pase en el cimiento del cerco; D2 por una poza de salida (0.80 x 0.80 m) que rebalsa a nivel del terreno. Fuera del cerco no hay obra.</t>
+          <t>5. D1, D3 y D4 salen por un pase en el cimiento del cerco; D2 por una poza de salida (0.80 x 0.80 m) que rebalsa a nivel del terreno. Fuera del cerco no hay obra.</t>
         </is>
       </c>
     </row>
@@ -764,7 +791,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta, DC-02 cuadro y secciones, DC-03 a DC-05 perfiles, DC-06 y DC-07 isometricos, DC-08 y DC-09 cortes, DC-10 detalle de descargas.</t>
+          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta, DC-02 cuadro y secciones, DC-03 a DC-06 perfiles, DC-07 y DC-08 isometricos, DC-09 y DC-10 cortes, DC-11 detalle de descargas.</t>
         </is>
       </c>
     </row>
@@ -784,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -845,7 +872,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>19 ramales: R-01-&gt;D1, R-02-&gt;D1, R-03-&gt;D1, R-04-&gt;D1, R-05-&gt;D1, R-06-&gt;D1, R-07-&gt;D3, R-08-&gt;D3, R-09-&gt;D3, R-10-&gt;D3, R-11-&gt;D3, R-12-&gt;D2, R-13-&gt;D2, R-14-&gt;D2, R-15-&gt;D2, R-16-&gt;D2, R-17-&gt;D2, R-18-&gt;D2, R-19-&gt;D2</t>
+          <t>19 ramales: R-01-&gt;D1, R-02-&gt;D1, R-03-&gt;D1, R-04-&gt;D1, R-05-&gt;D1, R-06-&gt;D1, R-07-&gt;D3, R-08-&gt;D3, R-09-&gt;D3, R-10-&gt;D3, R-11-&gt;D3, R-12-&gt;D2, R-13-&gt;D2, R-14-&gt;D2, R-15-&gt;D2, R-16-&gt;D2, R-17-&gt;D4, R-18-&gt;D4, R-19-&gt;D4</t>
         </is>
       </c>
     </row>
@@ -885,7 +912,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>minima 0.50 % (R-01 P-01-P-02); maxima 44.02 %</t>
+          <t>minima 0.50 % (R-02 P-04-P-05); maxima 47.52 %</t>
         </is>
       </c>
     </row>
@@ -905,7 +932,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>inicio 0.30 a 0.30; minima 0.25 (R-07); maxima 0.83 (R-07, prog 82.5)</t>
+          <t>inicio 0.30 a 0.30; minima 0.25 (R-01); maxima 0.85 (R-07, prog 82.5)</t>
         </is>
       </c>
     </row>
@@ -925,11 +952,11 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>16 empalmes; caida maxima 0.32 m (R-11 en P-27)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>15 empalmes; caida maxima 0.34 m (R-11 en P-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>6</v>
       </c>
@@ -945,7 +972,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>D1 C.F. 183.557: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 1.0 m del cerco; D2 C.F. 180.175: poza de salida: rebalsa a 180.62 (fondo de la hondonada); afuera el fondo no sube y baja 0.25 m a 10.8 m; D3 C.F. 183.431: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 2.0 m del cerco</t>
+          <t>D1 C.F. 183.465: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.8 m del cerco; D2 C.F. 180.154: poza de salida: rebalsa a 180.62 (fondo de la hondonada); afuera el fondo no sube y baja 0.25 m a 11.8 m; D3 C.F. 183.482: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 1.8 m del cerco; D4 C.F. 183.999: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.8 m del cerco</t>
         </is>
       </c>
     </row>
@@ -965,7 +992,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>30 rotulos NPT revisados (bloques a menos de 5 m de una cuneta); NPT de 183.50 a 184.65; borde de cuneta &lt;= NPT en todos</t>
+          <t>41 rotulos NPT revisados (bloques a menos de 5 m de una cuneta); NPT de 183.50 a 184.65; borde de cuneta &lt;= NPT en todos</t>
         </is>
       </c>
     </row>
@@ -985,7 +1012,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.055 m en R-12 P-43-P-44 (Q 154.7 l/s, y 0.228, h 0.28)</t>
+          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.072 m en R-12 P-43-P-44 (Q 134.8 l/s, y 0.185, h 0.26)</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1032,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-06-D1 (S 6.0 %, V 3.51), R-12 P-41-P-42 (S 5.6 %, V 3.15), R-12 P-42-P-43 (S 6.8 %, V 3.42), R-15 P-52-P-41 (S 44.0 %, V 5.24) -&gt; gradas (escalones) de concreto</t>
+          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-03-D1 (S 19.1 %, V 5.28), R-12 P-40-P-41 (S 18.7 %, V 4.25), R-12 P-42-P-43 (S 6.9 %, V 3.33), R-15 P-53-P-41 (S 47.5 %, V 3.43) -&gt; gradas (escalones) de concreto</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1052,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>distancia minima eje-muro 0.55 m en 1696 puntos revisados</t>
+          <t>distancia minima eje-muro 1.22 m en 1993 puntos revisados</t>
         </is>
       </c>
     </row>
@@ -1082,11 +1109,11 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>183.557</v>
+        <v>183.465</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 1.0 m (perfilado maximo 0.31 m, sin obra)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.8 m (perfilado maximo 0.30 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1098,11 +1125,11 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>180.175</v>
+        <v>180.154</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>poza de salida: rebalsa a 180.62; el fondo exterior no sube y baja 0.25 m a 10.8 m</t>
+          <t>poza de salida: rebalsa a 180.62; el fondo exterior no sube y baja 0.25 m a 11.8 m</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1141,27 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>183.431</v>
+        <v>183.482</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 2.0 m (perfilado maximo 0.32 m, sin obra)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 1.8 m (perfilado maximo 0.26 m, sin obra)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>183.999</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.8 m (perfilado maximo 0.25 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1546,27 +1589,27 @@
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>200</v>
+        <v>533</v>
       </c>
       <c r="E11" s="5">
         <f>1000*$B$4*$B$5*D11/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.049</v>
+        <v>0.077</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="20">
         <f>H11-G11</f>
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="K11" s="21">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1595,27 +1638,27 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>225</v>
+        <v>553</v>
       </c>
       <c r="E12" s="5">
         <f>1000*$B$4*$B$5*D12/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F12" s="18" t="n">
-        <v>0.5</v>
+        <v>15.15</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.053</v>
+        <v>0.032</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="20">
         <f>H12-G12</f>
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.63</v>
+        <v>2.58</v>
       </c>
       <c r="K12" s="21">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1640,31 +1683,31 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
-        <v>370</v>
+        <v>3539</v>
       </c>
       <c r="E13" s="5">
         <f>1000*$B$4*$B$5*D13/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.5</v>
+        <v>19.13</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.074</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="I13" s="20">
         <f>H13-G13</f>
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.74</v>
+        <v>5.28</v>
       </c>
       <c r="K13" s="21">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1674,12 +1717,16 @@
         <f>IF(J13&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M13" s="22" t="inlineStr"/>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
@@ -1693,27 +1740,27 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>651</v>
+        <v>436</v>
       </c>
       <c r="E14" s="5">
         <f>1000*$B$4*$B$5*D14/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F14" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>0.097</v>
+        <v>0.083</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="20">
         <f>H14-G14</f>
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="K14" s="21">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1728,7 +1775,7 @@
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
@@ -1742,27 +1789,27 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>3533</v>
+        <v>528</v>
       </c>
       <c r="E15" s="5">
         <f>1000*$B$4*$B$5*D15/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.368</v>
+        <v>0.094</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I15" s="20">
         <f>H15-G15</f>
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.45</v>
+        <v>0.83</v>
       </c>
       <c r="K15" s="21">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1777,7 +1824,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -1787,31 +1834,31 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>3540</v>
+        <v>965</v>
       </c>
       <c r="E16" s="5">
         <f>1000*$B$4*$B$5*D16/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F16" s="18" t="n">
-        <v>5.96</v>
+        <v>2.93</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>0.151</v>
+        <v>0.078</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="I16" s="20">
         <f>H16-G16</f>
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>3.51</v>
+        <v>1.84</v>
       </c>
       <c r="K16" s="21">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1821,11 +1868,7 @@
         <f>IF(J16&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M16" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M16" s="22" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
@@ -1844,27 +1887,27 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>454</v>
+        <v>2216</v>
       </c>
       <c r="E17" s="5">
         <f>1000*$B$4*$B$5*D17/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.06</v>
+        <v>0.269</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.3</v>
+        <v>0.77</v>
       </c>
       <c r="I17" s="20">
         <f>H17-G17</f>
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="K17" s="21">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1889,31 +1932,31 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1030</v>
+        <v>2979</v>
       </c>
       <c r="E18" s="5">
         <f>1000*$B$4*$B$5*D18/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F18" s="18" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>0.076</v>
+        <v>0.339</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="I18" s="20">
         <f>H18-G18</f>
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>2.01</v>
+        <v>1.33</v>
       </c>
       <c r="K18" s="21">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1928,7 +1971,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -1938,11 +1981,11 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2668</v>
+        <v>368</v>
       </c>
       <c r="E19" s="5">
         <f>1000*$B$4*$B$5*D19/3600000*$B$6</f>
@@ -1952,17 +1995,17 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.311</v>
+        <v>0.074</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>0.77</v>
+        <v>0.3</v>
       </c>
       <c r="I19" s="20">
         <f>H19-G19</f>
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.3</v>
+        <v>0.74</v>
       </c>
       <c r="K19" s="21">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1977,7 +2020,7 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
@@ -1987,11 +2030,11 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2672</v>
+        <v>383</v>
       </c>
       <c r="E20" s="5">
         <f>1000*$B$4*$B$5*D20/3600000*$B$6</f>
@@ -2001,17 +2044,17 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>0.311</v>
+        <v>0.076</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>0.79</v>
+        <v>0.3</v>
       </c>
       <c r="I20" s="20">
         <f>H20-G20</f>
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.3</v>
+        <v>0.75</v>
       </c>
       <c r="K20" s="21">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2026,7 +2069,7 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -2036,11 +2079,11 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="E21" s="5">
         <f>1000*$B$4*$B$5*D21/3600000*$B$6</f>
@@ -2050,17 +2093,17 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.077</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="I21" s="20">
         <f>H21-G21</f>
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="K21" s="21">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2085,11 +2128,11 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>248</v>
+        <v>585</v>
       </c>
       <c r="E22" s="5">
         <f>1000*$B$4*$B$5*D22/3600000*$B$6</f>
@@ -2099,17 +2142,17 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0.057</v>
+        <v>0.101</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="I22" s="20">
         <f>H22-G22</f>
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="K22" s="21">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2129,36 +2172,36 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>307</v>
+        <v>782</v>
       </c>
       <c r="E23" s="5">
         <f>1000*$B$4*$B$5*D23/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F23" s="18" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.037</v>
+        <v>0.124</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="I23" s="20">
         <f>H23-G23</f>
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.23</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K23" s="21">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2178,16 +2221,16 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1497</v>
+        <v>858</v>
       </c>
       <c r="E24" s="5">
         <f>1000*$B$4*$B$5*D24/3600000*$B$6</f>
@@ -2197,17 +2240,17 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>0.199</v>
+        <v>0.132</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="I24" s="20">
         <f>H24-G24</f>
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.13</v>
+        <v>0.97</v>
       </c>
       <c r="K24" s="21">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2222,21 +2265,21 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>390</v>
+        <v>1161</v>
       </c>
       <c r="E25" s="5">
         <f>1000*$B$4*$B$5*D25/3600000*$B$6</f>
@@ -2246,17 +2289,17 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="19" t="n">
-        <v>0.077</v>
+        <v>0.165</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.3</v>
+        <v>0.61</v>
       </c>
       <c r="I25" s="20">
         <f>H25-G25</f>
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="K25" s="21">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2276,16 +2319,16 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>463</v>
+        <v>188</v>
       </c>
       <c r="E26" s="5">
         <f>1000*$B$4*$B$5*D26/3600000*$B$6</f>
@@ -2295,17 +2338,17 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="I26" s="20">
         <f>H26-G26</f>
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="K26" s="21">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2325,16 +2368,16 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>595</v>
+        <v>229</v>
       </c>
       <c r="E27" s="5">
         <f>1000*$B$4*$B$5*D27/3600000*$B$6</f>
@@ -2344,17 +2387,17 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.102</v>
+        <v>0.054</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="I27" s="20">
         <f>H27-G27</f>
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="K27" s="21">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2374,16 +2417,16 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>805</v>
+        <v>366</v>
       </c>
       <c r="E28" s="5">
         <f>1000*$B$4*$B$5*D28/3600000*$B$6</f>
@@ -2393,17 +2436,17 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>0.127</v>
+        <v>0.073</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="I28" s="20">
         <f>H28-G28</f>
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="K28" s="21">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2423,16 +2466,16 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
-        <v>868</v>
+        <v>410</v>
       </c>
       <c r="E29" s="5">
         <f>1000*$B$4*$B$5*D29/3600000*$B$6</f>
@@ -2442,17 +2485,17 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.134</v>
+        <v>0.079</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="I29" s="20">
         <f>H29-G29</f>
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="K29" s="21">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2467,21 +2510,21 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
-        <v>102</v>
+        <v>705</v>
       </c>
       <c r="E30" s="5">
         <f>1000*$B$4*$B$5*D30/3600000*$B$6</f>
@@ -2491,17 +2534,17 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>0.032</v>
+        <v>0.115</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="I30" s="20">
         <f>H30-G30</f>
         <v/>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.47</v>
+        <v>0.91</v>
       </c>
       <c r="K30" s="21">
         <f>IF(I30&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2516,31 +2559,31 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="E31" s="5">
         <f>1000*$B$4*$B$5*D31/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F31" s="18" t="n">
-        <v>1.55</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="H31" s="18" t="n">
         <v>0.3</v>
@@ -2550,7 +2593,7 @@
         <v/>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.85</v>
+        <v>0.47</v>
       </c>
       <c r="K31" s="21">
         <f>IF(I31&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2570,36 +2613,36 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
-        <v>860</v>
+        <v>116</v>
       </c>
       <c r="E32" s="5">
         <f>1000*$B$4*$B$5*D32/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F32" s="18" t="n">
-        <v>0.5</v>
+        <v>1.72</v>
       </c>
       <c r="G32" s="19" t="n">
-        <v>0.133</v>
+        <v>0.023</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="I32" s="20">
         <f>H32-G32</f>
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="K32" s="21">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2619,16 +2662,16 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
-        <v>1229</v>
+        <v>784</v>
       </c>
       <c r="E33" s="5">
         <f>1000*$B$4*$B$5*D33/3600000*$B$6</f>
@@ -2638,17 +2681,17 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>0.172</v>
+        <v>0.124</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="I33" s="20">
         <f>H33-G33</f>
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K33" s="21">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2668,16 +2711,16 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1416</v>
+        <v>1153</v>
       </c>
       <c r="E34" s="5">
         <f>1000*$B$4*$B$5*D34/3600000*$B$6</f>
@@ -2687,17 +2730,17 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>0.191</v>
+        <v>0.164</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I34" s="20">
         <f>H34-G34</f>
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="K34" s="21">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2717,16 +2760,16 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
-        <v>2577</v>
+        <v>1339</v>
       </c>
       <c r="E35" s="5">
         <f>1000*$B$4*$B$5*D35/3600000*$B$6</f>
@@ -2736,17 +2779,17 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>0.302</v>
+        <v>0.183</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="I35" s="20">
         <f>H35-G35</f>
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="K35" s="21">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2766,16 +2809,16 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
-        <v>2638</v>
+        <v>1768</v>
       </c>
       <c r="E36" s="5">
         <f>1000*$B$4*$B$5*D36/3600000*$B$6</f>
@@ -2785,17 +2828,17 @@
         <v>0.5</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0.308</v>
+        <v>0.226</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="I36" s="20">
         <f>H36-G36</f>
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="K36" s="21">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2815,36 +2858,36 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
-        <v>2663</v>
+        <v>2084</v>
       </c>
       <c r="E37" s="5">
         <f>1000*$B$4*$B$5*D37/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F37" s="18" t="n">
-        <v>1.61</v>
+        <v>0.5</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>0.198</v>
+        <v>0.256</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="I37" s="20">
         <f>H37-G37</f>
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="K37" s="21">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2864,36 +2907,36 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>2684</v>
+        <v>2102</v>
       </c>
       <c r="E38" s="5">
         <f>1000*$B$4*$B$5*D38/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F38" s="18" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>0.199</v>
+        <v>0.258</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="I38" s="20">
         <f>H38-G38</f>
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>2.02</v>
+        <v>1.23</v>
       </c>
       <c r="K38" s="21">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2913,36 +2956,36 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
-        <v>2966</v>
+        <v>2127</v>
       </c>
       <c r="E39" s="5">
         <f>1000*$B$4*$B$5*D39/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F39" s="18" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.338</v>
+        <v>0.19</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="I39" s="20">
         <f>H39-G39</f>
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="K39" s="21">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2957,41 +3000,41 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>491</v>
+        <v>2191</v>
       </c>
       <c r="E40" s="5">
         <f>1000*$B$4*$B$5*D40/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F40" s="18" t="n">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>0.09</v>
+        <v>0.195</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I40" s="20">
         <f>H40-G40</f>
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="K40" s="21">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3006,21 +3049,21 @@
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
-        <v>342</v>
+        <v>2193</v>
       </c>
       <c r="E41" s="5">
         <f>1000*$B$4*$B$5*D41/3600000*$B$6</f>
@@ -3030,17 +3073,17 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="I41" s="20">
         <f>H41-G41</f>
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.72</v>
+        <v>1.24</v>
       </c>
       <c r="K41" s="21">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3055,21 +3098,21 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>547</v>
+        <v>47</v>
       </c>
       <c r="E42" s="5">
         <f>1000*$B$4*$B$5*D42/3600000*$B$6</f>
@@ -3079,7 +3122,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="19" t="n">
-        <v>0.097</v>
+        <v>0.02</v>
       </c>
       <c r="H42" s="18" t="n">
         <v>0.3</v>
@@ -3089,7 +3132,7 @@
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.84</v>
+        <v>0.35</v>
       </c>
       <c r="K42" s="21">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3104,21 +3147,21 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>682</v>
+        <v>488</v>
       </c>
       <c r="E43" s="5">
         <f>1000*$B$4*$B$5*D43/3600000*$B$6</f>
@@ -3128,17 +3171,17 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.113</v>
+        <v>0.089</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="I43" s="20">
         <f>H43-G43</f>
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K43" s="21">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3153,21 +3196,21 @@
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>698</v>
+        <v>342</v>
       </c>
       <c r="E44" s="5">
         <f>1000*$B$4*$B$5*D44/3600000*$B$6</f>
@@ -3177,17 +3220,17 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="19" t="n">
-        <v>0.114</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="I44" s="20">
         <f>H44-G44</f>
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.91</v>
+        <v>0.72</v>
       </c>
       <c r="K44" s="21">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3207,16 +3250,16 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>903</v>
+        <v>205</v>
       </c>
       <c r="E45" s="5">
         <f>1000*$B$4*$B$5*D45/3600000*$B$6</f>
@@ -3226,17 +3269,17 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="19" t="n">
-        <v>0.137</v>
+        <v>0.05</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="I45" s="20">
         <f>H45-G45</f>
         <v/>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.98</v>
+        <v>0.61</v>
       </c>
       <c r="K45" s="21">
         <f>IF(I45&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3256,16 +3299,16 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>935</v>
+        <v>239</v>
       </c>
       <c r="E46" s="5">
         <f>1000*$B$4*$B$5*D46/3600000*$B$6</f>
@@ -3275,17 +3318,17 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>0.141</v>
+        <v>0.055</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="I46" s="20">
         <f>H46-G46</f>
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="K46" s="21">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3305,16 +3348,16 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>1036</v>
+        <v>335</v>
       </c>
       <c r="E47" s="5">
         <f>1000*$B$4*$B$5*D47/3600000*$B$6</f>
@@ -3324,17 +3367,17 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>0.152</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="I47" s="20">
         <f>H47-G47</f>
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.02</v>
+        <v>0.72</v>
       </c>
       <c r="K47" s="21">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3354,16 +3397,16 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>P-34</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>130</v>
+        <v>301</v>
       </c>
       <c r="E48" s="5">
         <f>1000*$B$4*$B$5*D48/3600000*$B$6</f>
@@ -3373,7 +3416,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="19" t="n">
-        <v>0.037</v>
+        <v>0.064</v>
       </c>
       <c r="H48" s="18" t="n">
         <v>0.3</v>
@@ -3383,7 +3426,7 @@
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K48" s="21">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3398,21 +3441,21 @@
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="E49" s="5">
         <f>1000*$B$4*$B$5*D49/3600000*$B$6</f>
@@ -3422,17 +3465,17 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="19" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="I49" s="20">
         <f>H49-G49</f>
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="K49" s="21">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3447,21 +3490,21 @@
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>276</v>
+        <v>532</v>
       </c>
       <c r="E50" s="5">
         <f>1000*$B$4*$B$5*D50/3600000*$B$6</f>
@@ -3471,17 +3514,17 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>0.061</v>
+        <v>0.095</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I50" s="20">
         <f>H50-G50</f>
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="K50" s="21">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3496,41 +3539,41 @@
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
-        <v>280</v>
+        <v>855</v>
       </c>
       <c r="E51" s="5">
         <f>1000*$B$4*$B$5*D51/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F51" s="18" t="n">
-        <v>14.89</v>
+        <v>0.5</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.021</v>
+        <v>0.132</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I51" s="20">
         <f>H51-G51</f>
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.99</v>
+        <v>0.97</v>
       </c>
       <c r="K51" s="21">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3550,36 +3593,36 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>70</v>
+        <v>1128</v>
       </c>
       <c r="E52" s="5">
         <f>1000*$B$4*$B$5*D52/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F52" s="18" t="n">
-        <v>1.08</v>
+        <v>0.5</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>0.02</v>
+        <v>0.161</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
       <c r="I52" s="20">
         <f>H52-G52</f>
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="K52" s="21">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3599,36 +3642,36 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>753</v>
+        <v>1869</v>
       </c>
       <c r="E53" s="5">
         <f>1000*$B$4*$B$5*D53/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F53" s="18" t="n">
-        <v>0.5</v>
+        <v>18.72</v>
       </c>
       <c r="G53" s="19" t="n">
-        <v>0.121</v>
+        <v>0.065</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="I53" s="20">
         <f>H53-G53</f>
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.93</v>
+        <v>4.25</v>
       </c>
       <c r="K53" s="21">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3638,7 +3681,11 @@
         <f>IF(J53&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M53" s="22" t="inlineStr"/>
+      <c r="M53" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
@@ -3648,26 +3695,26 @@
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>1071</v>
+        <v>2361</v>
       </c>
       <c r="E54" s="5">
         <f>1000*$B$4*$B$5*D54/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F54" s="18" t="n">
-        <v>11.49</v>
+        <v>5.03</v>
       </c>
       <c r="G54" s="19" t="n">
-        <v>0.053</v>
+        <v>0.12</v>
       </c>
       <c r="H54" s="18" t="n">
         <v>0.25</v>
@@ -3677,7 +3724,7 @@
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="K54" s="21">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3697,36 +3744,36 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2641</v>
+        <v>2487</v>
       </c>
       <c r="E55" s="5">
         <f>1000*$B$4*$B$5*D55/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F55" s="18" t="n">
-        <v>5.59</v>
+        <v>6.92</v>
       </c>
       <c r="G55" s="19" t="n">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="I55" s="20">
         <f>H55-G55</f>
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="K55" s="21">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3750,26 +3797,26 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2767</v>
+        <v>2500</v>
       </c>
       <c r="E56" s="5">
         <f>1000*$B$4*$B$5*D56/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F56" s="18" t="n">
-        <v>6.76</v>
+        <v>1.69</v>
       </c>
       <c r="G56" s="19" t="n">
-        <v>0.121</v>
+        <v>0.185</v>
       </c>
       <c r="H56" s="18" t="n">
         <v>0.26</v>
@@ -3779,7 +3826,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3.42</v>
+        <v>2.02</v>
       </c>
       <c r="K56" s="21">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3789,11 +3836,7 @@
         <f>IF(J56&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M56" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M56" s="22" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
@@ -3803,36 +3846,36 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>2870</v>
+        <v>3029</v>
       </c>
       <c r="E57" s="5">
         <f>1000*$B$4*$B$5*D57/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F57" s="18" t="n">
-        <v>1.29</v>
+        <v>11.71</v>
       </c>
       <c r="G57" s="19" t="n">
-        <v>0.228</v>
+        <v>0.106</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="I57" s="20">
         <f>H57-G57</f>
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>1.89</v>
+        <v>4.25</v>
       </c>
       <c r="K57" s="21">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3847,41 +3890,41 @@
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>P-45</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>2887</v>
+        <v>244</v>
       </c>
       <c r="E58" s="5">
         <f>1000*$B$4*$B$5*D58/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F58" s="18" t="n">
-        <v>5.27</v>
+        <v>0.5</v>
       </c>
       <c r="G58" s="19" t="n">
-        <v>0.136</v>
+        <v>0.056</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="I58" s="20">
         <f>H58-G58</f>
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>3.17</v>
+        <v>0.64</v>
       </c>
       <c r="K58" s="21">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3896,21 +3939,21 @@
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-46</t>
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>354</v>
+        <v>211</v>
       </c>
       <c r="E59" s="5">
         <f>1000*$B$4*$B$5*D59/3600000*$B$6</f>
@@ -3920,7 +3963,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="19" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="H59" s="18" t="n">
         <v>0.3</v>
@@ -3930,7 +3973,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="K59" s="21">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3950,16 +3993,16 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
-        <v>244</v>
+        <v>480</v>
       </c>
       <c r="E60" s="5">
         <f>1000*$B$4*$B$5*D60/3600000*$B$6</f>
@@ -3969,17 +4012,17 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="19" t="n">
-        <v>0.056</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="I60" s="20">
         <f>H60-G60</f>
         <v/>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K60" s="21">
         <f>IF(I60&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3994,21 +4037,21 @@
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>313</v>
+        <v>487</v>
       </c>
       <c r="E61" s="5">
         <f>1000*$B$4*$B$5*D61/3600000*$B$6</f>
@@ -4018,17 +4061,17 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="19" t="n">
-        <v>0.066</v>
+        <v>0.089</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I61" s="20">
         <f>H61-G61</f>
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K61" s="21">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4043,21 +4086,21 @@
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>579</v>
+        <v>673</v>
       </c>
       <c r="E62" s="5">
         <f>1000*$B$4*$B$5*D62/3600000*$B$6</f>
@@ -4067,17 +4110,17 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="19" t="n">
-        <v>0.1</v>
+        <v>0.112</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0.39</v>
+        <v>0.51</v>
       </c>
       <c r="I62" s="20">
         <f>H62-G62</f>
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K62" s="21">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4092,21 +4135,21 @@
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>637</v>
+        <v>693</v>
       </c>
       <c r="E63" s="5">
         <f>1000*$B$4*$B$5*D63/3600000*$B$6</f>
@@ -4116,17 +4159,17 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="19" t="n">
-        <v>0.107</v>
+        <v>0.114</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I63" s="20">
         <f>H63-G63</f>
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="K63" s="21">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4146,16 +4189,16 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>810</v>
+        <v>156</v>
       </c>
       <c r="E64" s="5">
         <f>1000*$B$4*$B$5*D64/3600000*$B$6</f>
@@ -4165,17 +4208,17 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="19" t="n">
-        <v>0.127</v>
+        <v>0.042</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="I64" s="20">
         <f>H64-G64</f>
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="K64" s="21">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4195,16 +4238,16 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="D65" s="18" t="n">
-        <v>873</v>
+        <v>430</v>
       </c>
       <c r="E65" s="5">
         <f>1000*$B$4*$B$5*D65/3600000*$B$6</f>
@@ -4214,17 +4257,17 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="19" t="n">
-        <v>0.134</v>
+        <v>0.082</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="I65" s="20">
         <f>H65-G65</f>
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="K65" s="21">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4244,7 +4287,7 @@
       </c>
       <c r="B66" s="18" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
@@ -4253,17 +4296,17 @@
         </is>
       </c>
       <c r="D66" s="18" t="n">
-        <v>1533</v>
+        <v>455</v>
       </c>
       <c r="E66" s="5">
         <f>1000*$B$4*$B$5*D66/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F66" s="18" t="n">
-        <v>44.02</v>
+        <v>47.52</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>0.043</v>
+        <v>0.02</v>
       </c>
       <c r="H66" s="18" t="n">
         <v>0.25</v>
@@ -4273,7 +4316,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>5.24</v>
+        <v>3.43</v>
       </c>
       <c r="K66" s="21">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4297,16 +4340,16 @@
       </c>
       <c r="B67" s="18" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>54</v>
+        <v>398</v>
       </c>
       <c r="E67" s="5">
         <f>1000*$B$4*$B$5*D67/3600000*$B$6</f>
@@ -4316,7 +4359,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="19" t="n">
-        <v>0.021</v>
+        <v>0.078</v>
       </c>
       <c r="H67" s="18" t="n">
         <v>0.3</v>
@@ -4326,7 +4369,7 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>0.37</v>
+        <v>0.76</v>
       </c>
       <c r="K67" s="21">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4341,41 +4384,41 @@
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="D68" s="18" t="n">
-        <v>107</v>
+        <v>419</v>
       </c>
       <c r="E68" s="5">
         <f>1000*$B$4*$B$5*D68/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F68" s="18" t="n">
-        <v>0.5</v>
+        <v>11.05</v>
       </c>
       <c r="G68" s="19" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I68" s="20">
         <f>H68-G68</f>
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>0.48</v>
+        <v>2.11</v>
       </c>
       <c r="K68" s="21">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4390,41 +4433,41 @@
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="D69" s="18" t="n">
-        <v>641</v>
+        <v>528</v>
       </c>
       <c r="E69" s="5">
         <f>1000*$B$4*$B$5*D69/3600000*$B$6</f>
         <v/>
       </c>
       <c r="F69" s="18" t="n">
-        <v>0.5</v>
+        <v>21.72</v>
       </c>
       <c r="G69" s="19" t="n">
-        <v>0.108</v>
+        <v>0.027</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="I69" s="20">
         <f>H69-G69</f>
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>0.88</v>
+        <v>2.84</v>
       </c>
       <c r="K69" s="21">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4439,21 +4482,21 @@
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
         <is>
-          <t>P-55</t>
+          <t>P-57</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>P-58</t>
         </is>
       </c>
       <c r="D70" s="18" t="n">
-        <v>178</v>
+        <v>263</v>
       </c>
       <c r="E70" s="5">
         <f>1000*$B$4*$B$5*D70/3600000*$B$6</f>
@@ -4463,7 +4506,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="19" t="n">
-        <v>0.046</v>
+        <v>0.059</v>
       </c>
       <c r="H70" s="18" t="n">
         <v>0.3</v>
@@ -4473,7 +4516,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="K70" s="21">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4488,21 +4531,21 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>P-58</t>
         </is>
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-59</t>
         </is>
       </c>
       <c r="D71" s="18" t="n">
-        <v>268</v>
+        <v>628</v>
       </c>
       <c r="E71" s="5">
         <f>1000*$B$4*$B$5*D71/3600000*$B$6</f>
@@ -4512,17 +4555,17 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>0.06</v>
+        <v>0.106</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I71" s="20">
         <f>H71-G71</f>
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="K71" s="21">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4537,21 +4580,21 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
         <is>
-          <t>P-57</t>
+          <t>P-59</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>88</v>
+        <v>632</v>
       </c>
       <c r="E72" s="5">
         <f>1000*$B$4*$B$5*D72/3600000*$B$6</f>
@@ -4561,17 +4604,17 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="19" t="n">
-        <v>0.029</v>
+        <v>0.107</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I72" s="20">
         <f>H72-G72</f>
         <v/>
       </c>
       <c r="J72" s="6" t="n">
-        <v>0.45</v>
+        <v>0.88</v>
       </c>
       <c r="K72" s="21">
         <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4582,6 +4625,202 @@
         <v/>
       </c>
       <c r="M72" s="22" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>P-31</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>P-60</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>93</v>
+      </c>
+      <c r="E73" s="5">
+        <f>1000*$B$4*$B$5*D73/3600000*$B$6</f>
+        <v/>
+      </c>
+      <c r="F73" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H73" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I73" s="20">
+        <f>H73-G73</f>
+        <v/>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K73" s="21">
+        <f>IF(I73&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
+        <v/>
+      </c>
+      <c r="L73" s="21">
+        <f>IF(J73&lt;=$B$7,"CUMPLE","GRADAS")</f>
+        <v/>
+      </c>
+      <c r="M73" s="22" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>P-60</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>252</v>
+      </c>
+      <c r="E74" s="5">
+        <f>1000*$B$4*$B$5*D74/3600000*$B$6</f>
+        <v/>
+      </c>
+      <c r="F74" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G74" s="19" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H74" s="18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I74" s="20">
+        <f>H74-G74</f>
+        <v/>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K74" s="21">
+        <f>IF(I74&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
+        <v/>
+      </c>
+      <c r="L74" s="21">
+        <f>IF(J74&lt;=$B$7,"CUMPLE","GRADAS")</f>
+        <v/>
+      </c>
+      <c r="M74" s="22" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>P-58</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>365</v>
+      </c>
+      <c r="E75" s="5">
+        <f>1000*$B$4*$B$5*D75/3600000*$B$6</f>
+        <v/>
+      </c>
+      <c r="F75" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G75" s="19" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="H75" s="18" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I75" s="20">
+        <f>H75-G75</f>
+        <v/>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K75" s="21">
+        <f>IF(I75&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
+        <v/>
+      </c>
+      <c r="L75" s="21">
+        <f>IF(J75&lt;=$B$7,"CUMPLE","GRADAS")</f>
+        <v/>
+      </c>
+      <c r="M75" s="22" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>P-62</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>109</v>
+      </c>
+      <c r="E76" s="5">
+        <f>1000*$B$4*$B$5*D76/3600000*$B$6</f>
+        <v/>
+      </c>
+      <c r="F76" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G76" s="19" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="H76" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I76" s="20">
+        <f>H76-G76</f>
+        <v/>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K76" s="21">
+        <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
+        <v/>
+      </c>
+      <c r="L76" s="21">
+        <f>IF(J76&lt;=$B$7,"CUMPLE","GRADAS")</f>
+        <v/>
+      </c>
+      <c r="M76" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4599,7 +4838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4742,19 +4981,19 @@
         </is>
       </c>
       <c r="E5" s="24" t="n">
-        <v>23.99</v>
+        <v>31.9</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>184.5</v>
+        <v>184.155</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>184.2</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>184.08</v>
+        <v>183.905</v>
       </c>
       <c r="J5" s="26">
         <f>F5-H5</f>
@@ -4785,7 +5024,7 @@
       </c>
       <c r="Q5" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
+          <t>Pabellon oeste A: lado nor-oeste y salida D1</t>
         </is>
       </c>
     </row>
@@ -4809,19 +5048,19 @@
         </is>
       </c>
       <c r="E6" s="24" t="n">
-        <v>3.97</v>
+        <v>2.15</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>184.5</v>
+        <v>184.155</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>184.5</v>
+        <v>184.024</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>184.08</v>
+        <v>183.905</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>184.06</v>
+        <v>183.579</v>
       </c>
       <c r="J6" s="26">
         <f>F6-H6</f>
@@ -4852,7 +5091,7 @@
       </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
+          <t>Pabellon oeste A: lado nor-oeste y salida D1</t>
         </is>
       </c>
     </row>
@@ -4872,23 +5111,23 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>P-04</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>21.26</v>
+        <v>0.6</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>184.5</v>
+        <v>184.024</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>184.5</v>
+        <v>183.91</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>184.06</v>
+        <v>183.579</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>183.954</v>
+        <v>183.465</v>
       </c>
       <c r="J7" s="26">
         <f>F7-H7</f>
@@ -4903,7 +5142,7 @@
         <v/>
       </c>
       <c r="M7" s="24" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N7" s="26">
         <f>E7-M7</f>
@@ -4919,7 +5158,7 @@
       </c>
       <c r="Q7" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
+          <t>Pabellon oeste A: lado nor-oeste y salida D1</t>
         </is>
       </c>
     </row>
@@ -4929,7 +5168,7 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -4943,19 +5182,19 @@
         </is>
       </c>
       <c r="E8" s="24" t="n">
-        <v>42.83</v>
+        <v>32.42</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>184.45</v>
+        <v>184.5</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>183.954</v>
+        <v>184.2</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>183.657</v>
+        <v>184.038</v>
       </c>
       <c r="J8" s="26">
         <f>F8-H8</f>
@@ -4986,7 +5225,7 @@
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
+          <t>Pabellon oeste B: lado nor-este; pabellon A: lado sur-este; union a D1</t>
         </is>
       </c>
     </row>
@@ -4996,7 +5235,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -5010,19 +5249,19 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>11.17</v>
+        <v>11.53</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>184.45</v>
+        <v>184.5</v>
       </c>
       <c r="G9" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="H9" s="25" t="n">
         <v>184.038</v>
       </c>
-      <c r="H9" s="25" t="n">
-        <v>183.657</v>
-      </c>
       <c r="I9" s="25" t="n">
-        <v>183.593</v>
+        <v>183.98</v>
       </c>
       <c r="J9" s="26">
         <f>F9-H9</f>
@@ -5053,7 +5292,7 @@
       </c>
       <c r="Q9" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
+          <t>Pabellon oeste B: lado nor-este; pabellon A: lado sur-este; union a D1</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5302,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -5073,23 +5312,23 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>0.6</v>
+        <v>8.68</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>184.038</v>
+        <v>184.5</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>184.002</v>
+        <v>184.5</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>183.593</v>
+        <v>183.98</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>183.557</v>
+        <v>183.726</v>
       </c>
       <c r="J10" s="26">
         <f>F10-H10</f>
@@ -5104,7 +5343,7 @@
         <v/>
       </c>
       <c r="M10" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N10" s="26">
         <f>E10-M10</f>
@@ -5120,7 +5359,7 @@
       </c>
       <c r="Q10" s="28" t="inlineStr">
         <is>
-          <t>Perimetral sur-oeste por dentro del cerco (C19 a C1)</t>
+          <t>Pabellon oeste B: lado nor-este; pabellon A: lado sur-este; union a D1</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5383,7 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>11.53</v>
+        <v>11.47</v>
       </c>
       <c r="F11" s="24" t="n">
         <v>184.5</v>
@@ -5153,10 +5392,10 @@
         <v>184.5</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>184.2</v>
+        <v>183.726</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>184.038</v>
+        <v>183.668</v>
       </c>
       <c r="J11" s="26">
         <f>F11-H11</f>
@@ -5187,7 +5426,7 @@
       </c>
       <c r="Q11" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Pabellon oeste B: lado nor-este; pabellon A: lado sur-este; union a D1</t>
         </is>
       </c>
     </row>
@@ -5207,23 +5446,23 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-03</t>
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>8.68</v>
+        <v>12.1</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>184.5</v>
+        <v>184.024</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>184.038</v>
+        <v>183.668</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>183.726</v>
+        <v>183.608</v>
       </c>
       <c r="J12" s="26">
         <f>F12-H12</f>
@@ -5254,7 +5493,7 @@
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Pabellon oeste B: lado nor-este; pabellon A: lado sur-este; union a D1</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5503,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -5274,23 +5513,23 @@
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>P-10</t>
+          <t>P-06</t>
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>11.47</v>
+        <v>32.31</v>
       </c>
       <c r="F13" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>184.487</v>
+        <v>184.5</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>183.726</v>
+        <v>184.2</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>183.668</v>
+        <v>184.038</v>
       </c>
       <c r="J13" s="26">
         <f>F13-H13</f>
@@ -5321,7 +5560,7 @@
       </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Pabellon oeste B: lado sur-oeste (patio)</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5570,7 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -5341,23 +5580,23 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>P-05</t>
+          <t>P-11</t>
         </is>
       </c>
       <c r="E14" s="24" t="n">
-        <v>2.29</v>
+        <v>26.1</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>184.487</v>
+        <v>184.5</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>184.45</v>
+        <v>184.5</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>183.668</v>
+        <v>184.2</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>183.657</v>
+        <v>184.07</v>
       </c>
       <c r="J14" s="26">
         <f>F14-H14</f>
@@ -5372,7 +5611,7 @@
         <v/>
       </c>
       <c r="M14" s="24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="N14" s="26">
         <f>E14-M14</f>
@@ -5388,7 +5627,7 @@
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo nor-oeste del patio, empalma a R-01</t>
+          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5637,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -5408,11 +5647,11 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>P-08</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>32.31</v>
+        <v>9.43</v>
       </c>
       <c r="F15" s="24" t="n">
         <v>184.5</v>
@@ -5421,10 +5660,10 @@
         <v>184.5</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>184.2</v>
+        <v>184.07</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>184.038</v>
+        <v>184.022</v>
       </c>
       <c r="J15" s="26">
         <f>F15-H15</f>
@@ -5455,7 +5694,7 @@
       </c>
       <c r="Q15" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: alero sur-oeste del pabellon norte</t>
+          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -5475,11 +5714,11 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="E16" s="24" t="n">
-        <v>11.51</v>
+        <v>3.78</v>
       </c>
       <c r="F16" s="24" t="n">
         <v>184.5</v>
@@ -5488,10 +5727,10 @@
         <v>184.5</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>184.2</v>
+        <v>184.022</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>184.142</v>
+        <v>184.003</v>
       </c>
       <c r="J16" s="26">
         <f>F16-H16</f>
@@ -5522,7 +5761,7 @@
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
+          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -5537,16 +5776,16 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>P-11</t>
+          <t>P-13</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>8.710000000000001</v>
+        <v>15.97</v>
       </c>
       <c r="F17" s="24" t="n">
         <v>184.5</v>
@@ -5555,10 +5794,10 @@
         <v>184.5</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>184.142</v>
+        <v>184.003</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>183.89</v>
+        <v>183.924</v>
       </c>
       <c r="J17" s="26">
         <f>F17-H17</f>
@@ -5589,7 +5828,7 @@
       </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
+          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -5604,16 +5843,16 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-14</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>P-09</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>32.81</v>
+        <v>6.79</v>
       </c>
       <c r="F18" s="24" t="n">
         <v>184.5</v>
@@ -5622,10 +5861,10 @@
         <v>184.5</v>
       </c>
       <c r="H18" s="25" t="n">
+        <v>183.924</v>
+      </c>
+      <c r="I18" s="25" t="n">
         <v>183.89</v>
-      </c>
-      <c r="I18" s="25" t="n">
-        <v>183.726</v>
       </c>
       <c r="J18" s="26">
         <f>F18-H18</f>
@@ -5656,7 +5895,7 @@
       </c>
       <c r="Q18" s="28" t="inlineStr">
         <is>
-          <t>Pabellones oeste: extremo sur-este del patio y alero nor-este del pabellon sur</t>
+          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -5666,21 +5905,21 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>P-14</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-07</t>
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>26.1</v>
+        <v>32.81</v>
       </c>
       <c r="F19" s="24" t="n">
         <v>184.5</v>
@@ -5689,10 +5928,10 @@
         <v>184.5</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>184.2</v>
+        <v>183.89</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>184.07</v>
+        <v>183.726</v>
       </c>
       <c r="J19" s="26">
         <f>F19-H19</f>
@@ -5723,7 +5962,7 @@
       </c>
       <c r="Q19" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -5738,16 +5977,16 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>9.43</v>
+        <v>21.32</v>
       </c>
       <c r="F20" s="24" t="n">
         <v>184.5</v>
@@ -5756,10 +5995,10 @@
         <v>184.5</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>184.07</v>
+        <v>184.2</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>184.022</v>
+        <v>184.093</v>
       </c>
       <c r="J20" s="26">
         <f>F20-H20</f>
@@ -5774,7 +6013,7 @@
         <v/>
       </c>
       <c r="M20" s="24" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="N20" s="26">
         <f>E20-M20</f>
@@ -5790,7 +6029,7 @@
       </c>
       <c r="Q20" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Bloque del ingreso (lado sur), bloque D (lado sur) y pabellon C (lado sur-oeste)</t>
         </is>
       </c>
     </row>
@@ -5805,16 +6044,16 @@
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>3.78</v>
+        <v>5.89</v>
       </c>
       <c r="F21" s="24" t="n">
         <v>184.5</v>
@@ -5823,10 +6062,10 @@
         <v>184.5</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>184.022</v>
+        <v>184.093</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>184.003</v>
+        <v>184.064</v>
       </c>
       <c r="J21" s="26">
         <f>F21-H21</f>
@@ -5857,7 +6096,7 @@
       </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Bloque del ingreso (lado sur), bloque D (lado sur) y pabellon C (lado sur-oeste)</t>
         </is>
       </c>
     </row>
@@ -5872,16 +6111,16 @@
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="E22" s="24" t="n">
-        <v>15.97</v>
+        <v>17.83</v>
       </c>
       <c r="F22" s="24" t="n">
         <v>184.5</v>
@@ -5890,10 +6129,10 @@
         <v>184.5</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>184.003</v>
+        <v>184.064</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>183.924</v>
+        <v>183.975</v>
       </c>
       <c r="J22" s="26">
         <f>F22-H22</f>
@@ -5924,7 +6163,7 @@
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Bloque del ingreso (lado sur), bloque D (lado sur) y pabellon C (lado sur-oeste)</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6178,16 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>P-13</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="E23" s="24" t="n">
-        <v>6.79</v>
+        <v>5.77</v>
       </c>
       <c r="F23" s="24" t="n">
         <v>184.5</v>
@@ -5957,10 +6196,10 @@
         <v>184.5</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>183.924</v>
+        <v>183.975</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>183.89</v>
+        <v>183.946</v>
       </c>
       <c r="J23" s="26">
         <f>F23-H23</f>
@@ -5991,7 +6230,7 @@
       </c>
       <c r="Q23" s="28" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste) y union al patio de pabellones oeste</t>
+          <t>Bloque del ingreso (lado sur), bloque D (lado sur) y pabellon C (lado sur-oeste)</t>
         </is>
       </c>
     </row>
@@ -6001,21 +6240,21 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-08</t>
         </is>
       </c>
       <c r="E24" s="24" t="n">
-        <v>11.74</v>
+        <v>39.15</v>
       </c>
       <c r="F24" s="24" t="n">
         <v>184.5</v>
@@ -6024,10 +6263,10 @@
         <v>184.5</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>184.2</v>
+        <v>183.946</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>184.141</v>
+        <v>183.75</v>
       </c>
       <c r="J24" s="26">
         <f>F24-H24</f>
@@ -6058,31 +6297,31 @@
       </c>
       <c r="Q24" s="28" t="inlineStr">
         <is>
-          <t>Tramo y=815.97 entre x=896.8 y x=885.1</t>
+          <t>Bloque del ingreso (lado sur), bloque D (lado sur) y pabellon C (lado sur-oeste)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-12</t>
         </is>
       </c>
       <c r="E25" s="24" t="n">
-        <v>11.51</v>
+        <v>11.74</v>
       </c>
       <c r="F25" s="24" t="n">
         <v>184.5</v>
@@ -6094,7 +6333,7 @@
         <v>184.2</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>184.021</v>
+        <v>184.141</v>
       </c>
       <c r="J25" s="26">
         <f>F25-H25</f>
@@ -6125,7 +6364,7 @@
       </c>
       <c r="Q25" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Bloque del ingreso: lado norte (y=815.97) al oeste de x=896.8</t>
         </is>
       </c>
     </row>
@@ -6140,16 +6379,16 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="E26" s="24" t="n">
-        <v>17.85</v>
+        <v>11.51</v>
       </c>
       <c r="F26" s="24" t="n">
         <v>184.5</v>
@@ -6158,10 +6397,10 @@
         <v>184.5</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>184.021</v>
+        <v>184.2</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>183.932</v>
+        <v>184.002</v>
       </c>
       <c r="J26" s="26">
         <f>F26-H26</f>
@@ -6192,7 +6431,7 @@
       </c>
       <c r="Q26" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6207,16 +6446,16 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="E27" s="24" t="n">
-        <v>6.12</v>
+        <v>17.85</v>
       </c>
       <c r="F27" s="24" t="n">
         <v>184.5</v>
@@ -6225,10 +6464,10 @@
         <v>184.5</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>183.932</v>
+        <v>184.002</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>183.901</v>
+        <v>183.912</v>
       </c>
       <c r="J27" s="26">
         <f>F27-H27</f>
@@ -6259,7 +6498,7 @@
       </c>
       <c r="Q27" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6274,16 +6513,16 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="E28" s="24" t="n">
-        <v>22.77</v>
+        <v>6.12</v>
       </c>
       <c r="F28" s="24" t="n">
         <v>184.5</v>
@@ -6292,10 +6531,10 @@
         <v>184.5</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>183.901</v>
+        <v>183.912</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>183.787</v>
+        <v>183.882</v>
       </c>
       <c r="J28" s="26">
         <f>F28-H28</f>
@@ -6326,7 +6565,7 @@
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6341,28 +6580,28 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>14.84</v>
+        <v>22.77</v>
       </c>
       <c r="F29" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G29" s="24" t="n">
-        <v>184.413</v>
+        <v>184.5</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>183.787</v>
+        <v>183.882</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>183.713</v>
+        <v>183.768</v>
       </c>
       <c r="J29" s="26">
         <f>F29-H29</f>
@@ -6393,7 +6632,7 @@
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6408,28 +6647,28 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>P-24</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="E30" s="24" t="n">
-        <v>7.96</v>
+        <v>11.77</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>184.413</v>
+        <v>184.5</v>
       </c>
       <c r="G30" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>183.713</v>
+        <v>183.768</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>183.673</v>
+        <v>183.709</v>
       </c>
       <c r="J30" s="26">
         <f>F30-H30</f>
@@ -6444,7 +6683,7 @@
         <v/>
       </c>
       <c r="M30" s="24" t="n">
-        <v>7.96</v>
+        <v>0</v>
       </c>
       <c r="N30" s="26">
         <f>E30-M30</f>
@@ -6460,7 +6699,7 @@
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6475,28 +6714,28 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>P-25</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="E31" s="24" t="n">
-        <v>6.69</v>
+        <v>3.07</v>
       </c>
       <c r="F31" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>183.852</v>
+        <v>184.412</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>183.673</v>
+        <v>183.709</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>183.565</v>
+        <v>183.694</v>
       </c>
       <c r="J31" s="26">
         <f>F31-H31</f>
@@ -6511,7 +6750,7 @@
         <v/>
       </c>
       <c r="M31" s="24" t="n">
-        <v>6.69</v>
+        <v>0</v>
       </c>
       <c r="N31" s="26">
         <f>E31-M31</f>
@@ -6527,7 +6766,7 @@
       </c>
       <c r="Q31" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6542,28 +6781,28 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>P-26</t>
+          <t>P-27</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="E32" s="24" t="n">
-        <v>8.210000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>183.852</v>
+        <v>184.412</v>
       </c>
       <c r="G32" s="24" t="n">
-        <v>184</v>
+        <v>184.5</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>183.565</v>
+        <v>183.694</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>183.434</v>
+        <v>183.654</v>
       </c>
       <c r="J32" s="26">
         <f>F32-H32</f>
@@ -6578,7 +6817,7 @@
         <v/>
       </c>
       <c r="M32" s="24" t="n">
-        <v>8.210000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="N32" s="26">
         <f>E32-M32</f>
@@ -6594,7 +6833,7 @@
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6609,28 +6848,28 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-28</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="E33" s="24" t="n">
-        <v>0.6</v>
+        <v>6.69</v>
       </c>
       <c r="F33" s="24" t="n">
-        <v>184</v>
+        <v>184.5</v>
       </c>
       <c r="G33" s="24" t="n">
-        <v>183.836</v>
+        <v>183.852</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>183.434</v>
+        <v>183.654</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>183.431</v>
+        <v>183.578</v>
       </c>
       <c r="J33" s="26">
         <f>F33-H33</f>
@@ -6645,7 +6884,7 @@
         <v/>
       </c>
       <c r="M33" s="24" t="n">
-        <v>0.6</v>
+        <v>6.69</v>
       </c>
       <c r="N33" s="26">
         <f>E33-M33</f>
@@ -6661,7 +6900,7 @@
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8, y=815.97), bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6671,33 +6910,33 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-29</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="E34" s="24" t="n">
-        <v>35.8</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>184.5</v>
+        <v>183.852</v>
       </c>
       <c r="G34" s="24" t="n">
-        <v>184.5</v>
+        <v>184.023</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>184.2</v>
+        <v>183.578</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>184.021</v>
+        <v>183.485</v>
       </c>
       <c r="J34" s="26">
         <f>F34-H34</f>
@@ -6712,7 +6951,7 @@
         <v/>
       </c>
       <c r="M34" s="24" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N34" s="26">
         <f>E34-M34</f>
@@ -6728,7 +6967,7 @@
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
-          <t>Patio central: alero sur del pabellon norte (y=839.94)</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6738,33 +6977,33 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-30</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="E35" s="24" t="n">
-        <v>35.8</v>
+        <v>0.6</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>184.5</v>
+        <v>184.023</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>184.5</v>
+        <v>183.826</v>
       </c>
       <c r="H35" s="25" t="n">
-        <v>184.2</v>
+        <v>183.485</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>184.021</v>
+        <v>183.482</v>
       </c>
       <c r="J35" s="26">
         <f>F35-H35</f>
@@ -6779,7 +7018,7 @@
         <v/>
       </c>
       <c r="M35" s="24" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N35" s="26">
         <f>E35-M35</f>
@@ -6795,7 +7034,7 @@
       </c>
       <c r="Q35" s="28" t="inlineStr">
         <is>
-          <t>Patio central: y=822.09</t>
+          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
         </is>
       </c>
     </row>
@@ -6805,21 +7044,21 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>P-30</t>
+          <t>P-31</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="E36" s="24" t="n">
-        <v>17.82</v>
+        <v>3.88</v>
       </c>
       <c r="F36" s="24" t="n">
         <v>184.5</v>
@@ -6831,7 +7070,7 @@
         <v>184.2</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>184.111</v>
+        <v>184.181</v>
       </c>
       <c r="J36" s="26">
         <f>F36-H36</f>
@@ -6862,7 +7101,7 @@
       </c>
       <c r="Q36" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>Bloque del centro: lado sur (y=839.94)</t>
         </is>
       </c>
     </row>
@@ -6872,21 +7111,21 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
-          <t>P-31</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="E37" s="24" t="n">
-        <v>13.53</v>
+        <v>35.8</v>
       </c>
       <c r="F37" s="24" t="n">
         <v>184.5</v>
@@ -6895,10 +7134,10 @@
         <v>184.5</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>184.111</v>
+        <v>184.181</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>184.043</v>
+        <v>184.002</v>
       </c>
       <c r="J37" s="26">
         <f>F37-H37</f>
@@ -6929,7 +7168,7 @@
       </c>
       <c r="Q37" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>Bloque del centro: lado sur (y=839.94)</t>
         </is>
       </c>
     </row>
@@ -6939,21 +7178,21 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>P-32</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-24</t>
         </is>
       </c>
       <c r="E38" s="24" t="n">
-        <v>3.88</v>
+        <v>35.8</v>
       </c>
       <c r="F38" s="24" t="n">
         <v>184.5</v>
@@ -6962,10 +7201,10 @@
         <v>184.5</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>184.043</v>
+        <v>184.2</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>184.024</v>
+        <v>184.021</v>
       </c>
       <c r="J38" s="26">
         <f>F38-H38</f>
@@ -6996,7 +7235,7 @@
       </c>
       <c r="Q38" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>Patio central: y=822.09</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7250,12 @@
       </c>
       <c r="C39" s="23" t="inlineStr">
         <is>
-          <t>P-28</t>
+          <t>P-32</t>
         </is>
       </c>
       <c r="D39" s="23" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="E39" s="24" t="n">
@@ -7029,10 +7268,10 @@
         <v>184.5</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>184.024</v>
+        <v>184.2</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>183.935</v>
+        <v>184.111</v>
       </c>
       <c r="J39" s="26">
         <f>F39-H39</f>
@@ -7063,7 +7302,7 @@
       </c>
       <c r="Q39" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
         </is>
       </c>
     </row>
@@ -7078,12 +7317,12 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>P-29</t>
+          <t>P-33</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="E40" s="24" t="n">
@@ -7096,10 +7335,10 @@
         <v>184.5</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>183.935</v>
+        <v>184.111</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>183.904</v>
+        <v>184.08</v>
       </c>
       <c r="J40" s="26">
         <f>F40-H40</f>
@@ -7130,7 +7369,7 @@
       </c>
       <c r="Q40" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7384,12 @@
       </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
-          <t>P-33</t>
+          <t>P-34</t>
         </is>
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>P-25</t>
         </is>
       </c>
       <c r="E41" s="24" t="n">
@@ -7163,10 +7402,10 @@
         <v>184.5</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>183.904</v>
+        <v>184.08</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>183.839</v>
+        <v>184.015</v>
       </c>
       <c r="J41" s="26">
         <f>F41-H41</f>
@@ -7197,7 +7436,7 @@
       </c>
       <c r="Q41" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur), x=936.5, x=932.6 (muro de contencion) e y=815.97</t>
+          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
         </is>
       </c>
     </row>
@@ -7212,16 +7451,16 @@
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>P-34</t>
+          <t>P-35</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-26</t>
         </is>
       </c>
       <c r="E42" s="24" t="n">
-        <v>11.57</v>
+        <v>30.36</v>
       </c>
       <c r="F42" s="24" t="n">
         <v>184.5</v>
@@ -7233,7 +7472,7 @@
         <v>184.2</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>184.142</v>
+        <v>184.048</v>
       </c>
       <c r="J42" s="26">
         <f>F42-H42</f>
@@ -7248,7 +7487,7 @@
         <v/>
       </c>
       <c r="M42" s="24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N42" s="26">
         <f>E42-M42</f>
@@ -7264,31 +7503,31 @@
       </c>
       <c r="Q42" s="28" t="inlineStr">
         <is>
-          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
+          <t>Bloque del frente: lado sur (y=804.1)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
-          <t>P-35</t>
+          <t>P-36</t>
         </is>
       </c>
       <c r="D43" s="23" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="E43" s="24" t="n">
-        <v>9.300000000000001</v>
+        <v>15.66</v>
       </c>
       <c r="F43" s="24" t="n">
         <v>184.5</v>
@@ -7297,10 +7536,10 @@
         <v>184.5</v>
       </c>
       <c r="H43" s="25" t="n">
-        <v>184.142</v>
+        <v>184.2</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>184.096</v>
+        <v>184.122</v>
       </c>
       <c r="J43" s="26">
         <f>F43-H43</f>
@@ -7315,7 +7554,7 @@
         <v/>
       </c>
       <c r="M43" s="24" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="N43" s="26">
         <f>E43-M43</f>
@@ -7331,31 +7570,31 @@
       </c>
       <c r="Q43" s="28" t="inlineStr">
         <is>
-          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>P-36</t>
+          <t>P-37</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="E44" s="24" t="n">
-        <v>1.64</v>
+        <v>23.7</v>
       </c>
       <c r="F44" s="24" t="n">
         <v>184.5</v>
@@ -7364,10 +7603,10 @@
         <v>184.5</v>
       </c>
       <c r="H44" s="25" t="n">
-        <v>184.096</v>
+        <v>184.122</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>184.087</v>
+        <v>184.003</v>
       </c>
       <c r="J44" s="26">
         <f>F44-H44</f>
@@ -7382,7 +7621,7 @@
         <v/>
       </c>
       <c r="M44" s="24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="N44" s="26">
         <f>E44-M44</f>
@@ -7398,43 +7637,43 @@
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
-          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>P-37</t>
+          <t>P-38</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>P-27</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="E45" s="24" t="n">
-        <v>2.26</v>
+        <v>35.28</v>
       </c>
       <c r="F45" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G45" s="24" t="n">
-        <v>184</v>
+        <v>184.5</v>
       </c>
       <c r="H45" s="25" t="n">
-        <v>184.087</v>
+        <v>184.003</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>183.75</v>
+        <v>183.827</v>
       </c>
       <c r="J45" s="26">
         <f>F45-H45</f>
@@ -7449,7 +7688,7 @@
         <v/>
       </c>
       <c r="M45" s="24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="N45" s="26">
         <f>E45-M45</f>
@@ -7465,7 +7704,7 @@
       </c>
       <c r="Q45" s="28" t="inlineStr">
         <is>
-          <t>Bajada x=937.3 por el atrio de ingreso a D3</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7480,16 +7719,16 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>P-38</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="E46" s="24" t="n">
-        <v>9.699999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="F46" s="24" t="n">
         <v>184.5</v>
@@ -7498,10 +7737,10 @@
         <v>184.5</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>184.2</v>
+        <v>183.827</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>184.095</v>
+        <v>183.783</v>
       </c>
       <c r="J46" s="26">
         <f>F46-H46</f>
@@ -7532,7 +7771,7 @@
       </c>
       <c r="Q46" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7547,28 +7786,28 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="E47" s="24" t="n">
-        <v>35.28</v>
+        <v>11.93</v>
       </c>
       <c r="F47" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G47" s="24" t="n">
-        <v>184.5</v>
+        <v>181.8</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>184.095</v>
+        <v>183.783</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>183.919</v>
+        <v>181.55</v>
       </c>
       <c r="J47" s="26">
         <f>F47-H47</f>
@@ -7599,7 +7838,7 @@
       </c>
       <c r="Q47" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7614,28 +7853,28 @@
       </c>
       <c r="C48" s="23" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-41</t>
         </is>
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="E48" s="24" t="n">
-        <v>20.59</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F48" s="24" t="n">
-        <v>184.5</v>
+        <v>181.8</v>
       </c>
       <c r="G48" s="24" t="n">
-        <v>181.803</v>
+        <v>181.418</v>
       </c>
       <c r="H48" s="25" t="n">
-        <v>183.919</v>
+        <v>181.55</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>181.553</v>
+        <v>181.117</v>
       </c>
       <c r="J48" s="26">
         <f>F48-H48</f>
@@ -7666,7 +7905,7 @@
       </c>
       <c r="Q48" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7681,28 +7920,28 @@
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
-          <t>P-41</t>
+          <t>P-42</t>
         </is>
       </c>
       <c r="D49" s="23" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="E49" s="24" t="n">
-        <v>8.630000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>181.803</v>
+        <v>181.418</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>181.329</v>
+        <v>180.523</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>181.553</v>
+        <v>181.117</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>181.071</v>
+        <v>180.266</v>
       </c>
       <c r="J49" s="26">
         <f>F49-H49</f>
@@ -7717,7 +7956,7 @@
         <v/>
       </c>
       <c r="M49" s="24" t="n">
-        <v>0</v>
+        <v>12.29</v>
       </c>
       <c r="N49" s="26">
         <f>E49-M49</f>
@@ -7733,7 +7972,7 @@
       </c>
       <c r="Q49" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7748,28 +7987,28 @@
       </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
-          <t>P-42</t>
+          <t>P-43</t>
         </is>
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="E50" s="24" t="n">
-        <v>12.29</v>
+        <v>2.5</v>
       </c>
       <c r="F50" s="24" t="n">
-        <v>181.329</v>
+        <v>180.523</v>
       </c>
       <c r="G50" s="24" t="n">
-        <v>180.522</v>
+        <v>180.623</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>181.071</v>
+        <v>180.266</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>180.239</v>
+        <v>180.224</v>
       </c>
       <c r="J50" s="26">
         <f>F50-H50</f>
@@ -7784,7 +8023,7 @@
         <v/>
       </c>
       <c r="M50" s="24" t="n">
-        <v>12.29</v>
+        <v>2.5</v>
       </c>
       <c r="N50" s="26">
         <f>E50-M50</f>
@@ -7800,7 +8039,7 @@
       </c>
       <c r="Q50" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7815,28 +8054,28 @@
       </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
-          <t>P-43</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="D51" s="23" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="E51" s="24" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="F51" s="24" t="n">
-        <v>180.522</v>
+        <v>180.623</v>
       </c>
       <c r="G51" s="24" t="n">
-        <v>180.623</v>
+        <v>180.553</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>180.239</v>
+        <v>180.224</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>180.207</v>
+        <v>180.154</v>
       </c>
       <c r="J51" s="26">
         <f>F51-H51</f>
@@ -7851,7 +8090,7 @@
         <v/>
       </c>
       <c r="M51" s="24" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="N51" s="26">
         <f>E51-M51</f>
@@ -7867,7 +8106,7 @@
       </c>
       <c r="Q51" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lados oeste, sur y este; union por dentro del cerco a D2</t>
         </is>
       </c>
     </row>
@@ -7877,33 +8116,33 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>P-44</t>
+          <t>P-45</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>P-39</t>
         </is>
       </c>
       <c r="E52" s="24" t="n">
-        <v>0.6</v>
+        <v>24.38</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>180.623</v>
+        <v>184.5</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>180.561</v>
+        <v>184.5</v>
       </c>
       <c r="H52" s="25" t="n">
-        <v>180.207</v>
+        <v>184.2</v>
       </c>
       <c r="I52" s="25" t="n">
-        <v>180.175</v>
+        <v>184.078</v>
       </c>
       <c r="J52" s="26">
         <f>F52-H52</f>
@@ -7918,7 +8157,7 @@
         <v/>
       </c>
       <c r="M52" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N52" s="26">
         <f>E52-M52</f>
@@ -7934,7 +8173,7 @@
       </c>
       <c r="Q52" s="28" t="inlineStr">
         <is>
-          <t>Perimetral este por dentro del cerco (x=976.9) y salida al cerco norte</t>
+          <t>Losa: lado norte (y=831.3)</t>
         </is>
       </c>
     </row>
@@ -7944,21 +8183,21 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>P-45</t>
+          <t>P-46</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
         <is>
-          <t>P-39</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="E53" s="24" t="n">
-        <v>20.98</v>
+        <v>17.06</v>
       </c>
       <c r="F53" s="24" t="n">
         <v>184.5</v>
@@ -7970,7 +8209,7 @@
         <v>184.2</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>184.095</v>
+        <v>184.115</v>
       </c>
       <c r="J53" s="26">
         <f>F53-H53</f>
@@ -8001,7 +8240,7 @@
       </c>
       <c r="Q53" s="28" t="inlineStr">
         <is>
-          <t>Losa deportiva: lado sur</t>
+          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
         </is>
       </c>
     </row>
@@ -8016,16 +8255,16 @@
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>P-46</t>
+          <t>P-47</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>P-40</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="E54" s="24" t="n">
-        <v>24.38</v>
+        <v>22.85</v>
       </c>
       <c r="F54" s="24" t="n">
         <v>184.5</v>
@@ -8034,10 +8273,10 @@
         <v>184.5</v>
       </c>
       <c r="H54" s="25" t="n">
-        <v>184.2</v>
+        <v>184.115</v>
       </c>
       <c r="I54" s="25" t="n">
-        <v>184.078</v>
+        <v>184</v>
       </c>
       <c r="J54" s="26">
         <f>F54-H54</f>
@@ -8068,7 +8307,7 @@
       </c>
       <c r="Q54" s="28" t="inlineStr">
         <is>
-          <t>Losa deportiva: lado norte</t>
+          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
         </is>
       </c>
     </row>
@@ -8078,21 +8317,21 @@
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
-          <t>P-47</t>
+          <t>P-48</t>
         </is>
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="E55" s="24" t="n">
-        <v>17.06</v>
+        <v>1.12</v>
       </c>
       <c r="F55" s="24" t="n">
         <v>184.5</v>
@@ -8101,10 +8340,10 @@
         <v>184.5</v>
       </c>
       <c r="H55" s="25" t="n">
-        <v>184.2</v>
+        <v>184</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>184.115</v>
+        <v>183.995</v>
       </c>
       <c r="J55" s="26">
         <f>F55-H55</f>
@@ -8135,7 +8374,7 @@
       </c>
       <c r="Q55" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
         </is>
       </c>
     </row>
@@ -8145,21 +8384,21 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>P-48</t>
+          <t>P-49</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="E56" s="24" t="n">
-        <v>22.85</v>
+        <v>19.39</v>
       </c>
       <c r="F56" s="24" t="n">
         <v>184.5</v>
@@ -8168,10 +8407,10 @@
         <v>184.5</v>
       </c>
       <c r="H56" s="25" t="n">
-        <v>184.115</v>
+        <v>183.995</v>
       </c>
       <c r="I56" s="25" t="n">
-        <v>184</v>
+        <v>183.898</v>
       </c>
       <c r="J56" s="26">
         <f>F56-H56</f>
@@ -8202,7 +8441,7 @@
       </c>
       <c r="Q56" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
         </is>
       </c>
     </row>
@@ -8212,21 +8451,21 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-50</t>
         </is>
       </c>
       <c r="D57" s="23" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-40</t>
         </is>
       </c>
       <c r="E57" s="24" t="n">
-        <v>1.12</v>
+        <v>5.19</v>
       </c>
       <c r="F57" s="24" t="n">
         <v>184.5</v>
@@ -8235,10 +8474,10 @@
         <v>184.5</v>
       </c>
       <c r="H57" s="25" t="n">
-        <v>184</v>
+        <v>183.898</v>
       </c>
       <c r="I57" s="25" t="n">
-        <v>183.995</v>
+        <v>183.872</v>
       </c>
       <c r="J57" s="26">
         <f>F57-H57</f>
@@ -8269,7 +8508,7 @@
       </c>
       <c r="Q57" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
         </is>
       </c>
     </row>
@@ -8284,16 +8523,16 @@
       </c>
       <c r="C58" s="23" t="inlineStr">
         <is>
-          <t>P-50</t>
+          <t>P-51</t>
         </is>
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="E58" s="24" t="n">
-        <v>19.39</v>
+        <v>13.05</v>
       </c>
       <c r="F58" s="24" t="n">
         <v>184.5</v>
@@ -8302,10 +8541,10 @@
         <v>184.5</v>
       </c>
       <c r="H58" s="25" t="n">
-        <v>183.995</v>
+        <v>184.2</v>
       </c>
       <c r="I58" s="25" t="n">
-        <v>183.898</v>
+        <v>184.135</v>
       </c>
       <c r="J58" s="26">
         <f>F58-H58</f>
@@ -8336,7 +8575,7 @@
       </c>
       <c r="Q58" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
         </is>
       </c>
     </row>
@@ -8351,16 +8590,16 @@
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>P-51</t>
+          <t>P-52</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="E59" s="24" t="n">
-        <v>11.93</v>
+        <v>23.58</v>
       </c>
       <c r="F59" s="24" t="n">
         <v>184.5</v>
@@ -8369,10 +8608,10 @@
         <v>184.5</v>
       </c>
       <c r="H59" s="25" t="n">
-        <v>183.898</v>
+        <v>184.135</v>
       </c>
       <c r="I59" s="25" t="n">
-        <v>183.838</v>
+        <v>184.017</v>
       </c>
       <c r="J59" s="26">
         <f>F59-H59</f>
@@ -8403,7 +8642,7 @@
       </c>
       <c r="Q59" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8657,7 @@
       </c>
       <c r="C60" s="23" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-53</t>
         </is>
       </c>
       <c r="D60" s="23" t="inlineStr">
@@ -8433,13 +8672,13 @@
         <v>184.5</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>181.803</v>
+        <v>181.8</v>
       </c>
       <c r="H60" s="25" t="n">
-        <v>183.838</v>
+        <v>184.017</v>
       </c>
       <c r="I60" s="25" t="n">
-        <v>181.553</v>
+        <v>181.55</v>
       </c>
       <c r="J60" s="26">
         <f>F60-H60</f>
@@ -8454,7 +8693,7 @@
         <v/>
       </c>
       <c r="M60" s="24" t="n">
-        <v>5.19</v>
+        <v>0</v>
       </c>
       <c r="N60" s="26">
         <f>E60-M60</f>
@@ -8470,7 +8709,7 @@
       </c>
       <c r="Q60" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: y=815.97, x=952.3, y=839.94, x=971.7</t>
+          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
         </is>
       </c>
     </row>
@@ -8485,16 +8724,16 @@
       </c>
       <c r="C61" s="23" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-54</t>
         </is>
       </c>
       <c r="D61" s="23" t="inlineStr">
         <is>
-          <t>P-49</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="E61" s="24" t="n">
-        <v>4.19</v>
+        <v>31.2</v>
       </c>
       <c r="F61" s="24" t="n">
         <v>184.5</v>
@@ -8506,7 +8745,7 @@
         <v>184.2</v>
       </c>
       <c r="I61" s="25" t="n">
-        <v>184.179</v>
+        <v>184.044</v>
       </c>
       <c r="J61" s="26">
         <f>F61-H61</f>
@@ -8537,7 +8776,7 @@
       </c>
       <c r="Q61" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: tramo y=838.8</t>
+          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -8547,33 +8786,33 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="C62" s="23" t="inlineStr">
         <is>
-          <t>P-53</t>
+          <t>P-55</t>
         </is>
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="E62" s="24" t="n">
-        <v>13.05</v>
+        <v>3.93</v>
       </c>
       <c r="F62" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="G62" s="24" t="n">
-        <v>184.5</v>
+        <v>183.86</v>
       </c>
       <c r="H62" s="25" t="n">
-        <v>184.2</v>
+        <v>184.044</v>
       </c>
       <c r="I62" s="25" t="n">
-        <v>184.135</v>
+        <v>183.61</v>
       </c>
       <c r="J62" s="26">
         <f>F62-H62</f>
@@ -8604,7 +8843,7 @@
       </c>
       <c r="Q62" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: x=948.1 e y=851.87</t>
+          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -8614,33 +8853,33 @@
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-56</t>
         </is>
       </c>
       <c r="D63" s="23" t="inlineStr">
         <is>
-          <t>P-52</t>
+          <t>P-44</t>
         </is>
       </c>
       <c r="E63" s="24" t="n">
-        <v>23.58</v>
+        <v>14.9</v>
       </c>
       <c r="F63" s="24" t="n">
-        <v>184.5</v>
+        <v>183.86</v>
       </c>
       <c r="G63" s="24" t="n">
-        <v>184.5</v>
+        <v>180.623</v>
       </c>
       <c r="H63" s="25" t="n">
-        <v>184.135</v>
+        <v>183.61</v>
       </c>
       <c r="I63" s="25" t="n">
-        <v>184.017</v>
+        <v>180.373</v>
       </c>
       <c r="J63" s="26">
         <f>F63-H63</f>
@@ -8671,31 +8910,31 @@
       </c>
       <c r="Q63" s="28" t="inlineStr">
         <is>
-          <t>Bloque nor-este: x=948.1 e y=851.87</t>
+          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="C64" s="23" t="inlineStr">
         <is>
-          <t>P-55</t>
+          <t>P-57</t>
         </is>
       </c>
       <c r="D64" s="23" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>P-58</t>
         </is>
       </c>
       <c r="E64" s="24" t="n">
-        <v>6.74</v>
+        <v>39.03</v>
       </c>
       <c r="F64" s="24" t="n">
         <v>184.5</v>
@@ -8707,7 +8946,7 @@
         <v>184.2</v>
       </c>
       <c r="I64" s="25" t="n">
-        <v>184.166</v>
+        <v>184.004</v>
       </c>
       <c r="J64" s="26">
         <f>F64-H64</f>
@@ -8722,7 +8961,7 @@
         <v/>
       </c>
       <c r="M64" s="24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N64" s="26">
         <f>E64-M64</f>
@@ -8738,31 +8977,31 @@
       </c>
       <c r="Q64" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur, lado este) y x=948.1</t>
+          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>P-58</t>
         </is>
       </c>
       <c r="D65" s="23" t="inlineStr">
         <is>
-          <t>P-54</t>
+          <t>P-59</t>
         </is>
       </c>
       <c r="E65" s="24" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F65" s="24" t="n">
         <v>184.5</v>
@@ -8771,10 +9010,10 @@
         <v>184.5</v>
       </c>
       <c r="H65" s="25" t="n">
-        <v>184.166</v>
+        <v>184.004</v>
       </c>
       <c r="I65" s="25" t="n">
-        <v>184.158</v>
+        <v>184.002</v>
       </c>
       <c r="J65" s="26">
         <f>F65-H65</f>
@@ -8805,31 +9044,31 @@
       </c>
       <c r="Q65" s="28" t="inlineStr">
         <is>
-          <t>Bloque norte (alero sur, lado este) y x=948.1</t>
+          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B66" s="23" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>R-17</t>
         </is>
       </c>
       <c r="C66" s="23" t="inlineStr">
         <is>
-          <t>P-57</t>
+          <t>P-59</t>
         </is>
       </c>
       <c r="D66" s="23" t="inlineStr">
         <is>
-          <t>P-56</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="E66" s="24" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="F66" s="24" t="n">
         <v>184.5</v>
@@ -8838,10 +9077,10 @@
         <v>184.5</v>
       </c>
       <c r="H66" s="25" t="n">
-        <v>184.2</v>
+        <v>184.002</v>
       </c>
       <c r="I66" s="25" t="n">
-        <v>184.19</v>
+        <v>183.999</v>
       </c>
       <c r="J66" s="26">
         <f>F66-H66</f>
@@ -8856,7 +9095,7 @@
         <v/>
       </c>
       <c r="M66" s="24" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N66" s="26">
         <f>E66-M66</f>
@@ -8872,26 +9111,294 @@
       </c>
       <c r="Q66" s="28" t="inlineStr">
         <is>
-          <t>Remate y=853.47 al este de x=948.1</t>
+          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="D67" s="7" t="inlineStr">
+      <c r="A67" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>P-31</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>P-60</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F67" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="G67" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="H67" s="25" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I67" s="25" t="n">
+        <v>184.141</v>
+      </c>
+      <c r="J67" s="26">
+        <f>F67-H67</f>
+        <v/>
+      </c>
+      <c r="K67" s="26">
+        <f>G67-I67</f>
+        <v/>
+      </c>
+      <c r="L67" s="26">
+        <f>100*(H67-I67)/E67</f>
+        <v/>
+      </c>
+      <c r="M67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="26">
+        <f>E67-M67</f>
+        <v/>
+      </c>
+      <c r="O67" s="26">
+        <f>MAX(MIN(J67,K67)-CRITERIOS!$B$13,0.01)</f>
+        <v/>
+      </c>
+      <c r="P67" s="27">
+        <f>1000*CRITERIOS!$B$5*O67*((CRITERIOS!$B$5*O67)/(CRITERIOS!$B$5+2*O67))^(2/3)*SQRT(MAX(L67/100,CRITERIOS!$B$10))/CRITERIOS!$B$12</f>
+        <v/>
+      </c>
+      <c r="Q67" s="28" t="inlineStr">
+        <is>
+          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>P-60</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="F68" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="G68" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="H68" s="25" t="n">
+        <v>184.141</v>
+      </c>
+      <c r="I68" s="25" t="n">
+        <v>184.014</v>
+      </c>
+      <c r="J68" s="26">
+        <f>F68-H68</f>
+        <v/>
+      </c>
+      <c r="K68" s="26">
+        <f>G68-I68</f>
+        <v/>
+      </c>
+      <c r="L68" s="26">
+        <f>100*(H68-I68)/E68</f>
+        <v/>
+      </c>
+      <c r="M68" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="26">
+        <f>E68-M68</f>
+        <v/>
+      </c>
+      <c r="O68" s="26">
+        <f>MAX(MIN(J68,K68)-CRITERIOS!$B$13,0.01)</f>
+        <v/>
+      </c>
+      <c r="P68" s="27">
+        <f>1000*CRITERIOS!$B$5*O68*((CRITERIOS!$B$5*O68)/(CRITERIOS!$B$5+2*O68))^(2/3)*SQRT(MAX(L68/100,CRITERIOS!$B$10))/CRITERIOS!$B$12</f>
+        <v/>
+      </c>
+      <c r="Q68" s="28" t="inlineStr">
+        <is>
+          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>P-58</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F69" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="G69" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="H69" s="25" t="n">
+        <v>184.014</v>
+      </c>
+      <c r="I69" s="25" t="n">
+        <v>184.004</v>
+      </c>
+      <c r="J69" s="26">
+        <f>F69-H69</f>
+        <v/>
+      </c>
+      <c r="K69" s="26">
+        <f>G69-I69</f>
+        <v/>
+      </c>
+      <c r="L69" s="26">
+        <f>100*(H69-I69)/E69</f>
+        <v/>
+      </c>
+      <c r="M69" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="26">
+        <f>E69-M69</f>
+        <v/>
+      </c>
+      <c r="O69" s="26">
+        <f>MAX(MIN(J69,K69)-CRITERIOS!$B$13,0.01)</f>
+        <v/>
+      </c>
+      <c r="P69" s="27">
+        <f>1000*CRITERIOS!$B$5*O69*((CRITERIOS!$B$5*O69)/(CRITERIOS!$B$5+2*O69))^(2/3)*SQRT(MAX(L69/100,CRITERIOS!$B$10))/CRITERIOS!$B$12</f>
+        <v/>
+      </c>
+      <c r="Q69" s="28" t="inlineStr">
+        <is>
+          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>R-19</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>P-62</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="F70" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="G70" s="24" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="H70" s="25" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="I70" s="25" t="n">
+        <v>184.131</v>
+      </c>
+      <c r="J70" s="26">
+        <f>F70-H70</f>
+        <v/>
+      </c>
+      <c r="K70" s="26">
+        <f>G70-I70</f>
+        <v/>
+      </c>
+      <c r="L70" s="26">
+        <f>100*(H70-I70)/E70</f>
+        <v/>
+      </c>
+      <c r="M70" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="26">
+        <f>E70-M70</f>
+        <v/>
+      </c>
+      <c r="O70" s="26">
+        <f>MAX(MIN(J70,K70)-CRITERIOS!$B$13,0.01)</f>
+        <v/>
+      </c>
+      <c r="P70" s="27">
+        <f>1000*CRITERIOS!$B$5*O70*((CRITERIOS!$B$5*O70)/(CRITERIOS!$B$5+2*O70))^(2/3)*SQRT(MAX(L70/100,CRITERIOS!$B$10))/CRITERIOS!$B$12</f>
+        <v/>
+      </c>
+      <c r="Q70" s="28" t="inlineStr">
+        <is>
+          <t>Bloque del centro: lado norte (y=851.7), tramo oeste</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E67" s="8">
-        <f>SUM(E5:E66)</f>
-        <v/>
-      </c>
-      <c r="M67" s="8">
-        <f>SUM(M5:M66)</f>
-        <v/>
-      </c>
-      <c r="N67" s="8">
-        <f>SUM(N5:N66)</f>
+      <c r="E71" s="8">
+        <f>SUM(E5:E70)</f>
+        <v/>
+      </c>
+      <c r="M71" s="8">
+        <f>SUM(M5:M70)</f>
+        <v/>
+      </c>
+      <c r="N71" s="8">
+        <f>SUM(N5:N70)</f>
         <v/>
       </c>
     </row>
@@ -8911,7 +9418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8969,10 +9476,10 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>354907.615</v>
+        <v>354844.67</v>
       </c>
       <c r="C5" s="29" t="n">
-        <v>9249803.210000001</v>
+        <v>9249873.869999999</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -8988,10 +9495,10 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>354883.629</v>
+        <v>354822.02</v>
       </c>
       <c r="C6" s="29" t="n">
-        <v>9249803.210000001</v>
+        <v>9249851.41</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -9007,14 +9514,14 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>354879.734</v>
+        <v>354820.536</v>
       </c>
       <c r="C7" s="29" t="n">
-        <v>9249803.987</v>
+        <v>9249849.859999999</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-01, R-02</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -9026,14 +9533,14 @@
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>354860.053</v>
+        <v>354876.15</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>9249812.032</v>
+        <v>9249842.9</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -9045,14 +9552,14 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>354829.116</v>
+        <v>354853.1</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>9249841.646</v>
+        <v>9249865.699999999</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R-01, R-02</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -9064,14 +9571,14 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>354821.044</v>
+        <v>354844.95</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>9249849.373</v>
+        <v>9249857.550000001</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-02, R-03</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -9083,14 +9590,14 @@
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>354853.1</v>
+        <v>354838.81</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>9249865.699999999</v>
+        <v>9249851.41</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-02, R-04</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -9102,14 +9609,14 @@
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>354844.95</v>
+        <v>354830.7</v>
       </c>
       <c r="C12" s="29" t="n">
-        <v>9249857.550000001</v>
+        <v>9249843.300000001</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-03</t>
+          <t>R-02, R-05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -9121,14 +9628,14 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>354838.81</v>
+        <v>354867.8</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>9249851.41</v>
+        <v>9249834.699999999</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -9140,14 +9647,14 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>354830.7</v>
+        <v>354884.91</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>9249843.300000001</v>
+        <v>9249851.5</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -9159,14 +9666,14 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>354867.8</v>
+        <v>354884.91</v>
       </c>
       <c r="C15" s="29" t="n">
-        <v>9249834.699999999</v>
+        <v>9249825.4</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>R-03, R-04</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -9178,14 +9685,14 @@
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>354876.1</v>
+        <v>354885.1</v>
       </c>
       <c r="C16" s="29" t="n">
-        <v>9249842.67</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-04, R-06</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -9197,14 +9704,14 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>354862</v>
+        <v>354881.6</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>9249828.199999999</v>
+        <v>9249817.4</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>R-04, R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -9216,14 +9723,14 @@
         </is>
       </c>
       <c r="B18" s="29" t="n">
-        <v>354884.91</v>
+        <v>354866.8</v>
       </c>
       <c r="C18" s="29" t="n">
-        <v>9249851.5</v>
+        <v>9249823.4</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -9235,14 +9742,14 @@
         </is>
       </c>
       <c r="B19" s="29" t="n">
-        <v>354884.91</v>
+        <v>354862</v>
       </c>
       <c r="C19" s="29" t="n">
-        <v>9249825.4</v>
+        <v>9249828.199999999</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -9254,14 +9761,14 @@
         </is>
       </c>
       <c r="B20" s="29" t="n">
-        <v>354885.1</v>
+        <v>354906.62</v>
       </c>
       <c r="C20" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249804.220000001</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>R-05, R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -9273,10 +9780,10 @@
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>354881.6</v>
+        <v>354885.3</v>
       </c>
       <c r="C21" s="29" t="n">
-        <v>9249817.4</v>
+        <v>9249804.18</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -9292,10 +9799,10 @@
         </is>
       </c>
       <c r="B22" s="29" t="n">
-        <v>354866.8</v>
+        <v>354879.56</v>
       </c>
       <c r="C22" s="29" t="n">
-        <v>9249823.4</v>
+        <v>9249805.51</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
@@ -9311,14 +9818,14 @@
         </is>
       </c>
       <c r="B23" s="29" t="n">
-        <v>354896.84</v>
+        <v>354863.11</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249812.4</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>R-06, R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -9330,14 +9837,14 @@
         </is>
       </c>
       <c r="B24" s="29" t="n">
-        <v>354896.84</v>
+        <v>354858.19</v>
       </c>
       <c r="C24" s="29" t="n">
-        <v>9249851.449999999</v>
+        <v>9249815.42</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -9352,11 +9859,11 @@
         <v>354896.84</v>
       </c>
       <c r="C25" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-08</t>
+          <t>R-06, R-07</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -9371,11 +9878,11 @@
         <v>354896.84</v>
       </c>
       <c r="C26" s="29" t="n">
-        <v>9249822.09</v>
+        <v>9249851.449999999</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-09</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -9387,14 +9894,14 @@
         </is>
       </c>
       <c r="B27" s="29" t="n">
-        <v>354919.61</v>
+        <v>354896.84</v>
       </c>
       <c r="C27" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-10</t>
+          <t>R-07, R-08</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -9406,14 +9913,14 @@
         </is>
       </c>
       <c r="B28" s="29" t="n">
-        <v>354919.61</v>
+        <v>354896.84</v>
       </c>
       <c r="C28" s="29" t="n">
-        <v>9249801.130000001</v>
+        <v>9249822.09</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-07, R-09</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -9425,14 +9932,14 @@
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>354927.57</v>
+        <v>354919.61</v>
       </c>
       <c r="C29" s="29" t="n">
-        <v>9249801.130000001</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-07, R-10</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -9444,14 +9951,14 @@
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>354927.57</v>
+        <v>354919.61</v>
       </c>
       <c r="C30" s="29" t="n">
-        <v>9249794.442</v>
+        <v>9249804.199999999</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-07, R-11</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -9463,14 +9970,14 @@
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>354935.617</v>
+        <v>354919.61</v>
       </c>
       <c r="C31" s="29" t="n">
-        <v>9249792.835999999</v>
+        <v>9249801.130000001</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-11</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -9482,14 +9989,14 @@
         </is>
       </c>
       <c r="B32" s="29" t="n">
-        <v>354932.64</v>
+        <v>354927.57</v>
       </c>
       <c r="C32" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249801.130000001</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>R-08, R-10</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -9501,14 +10008,14 @@
         </is>
       </c>
       <c r="B33" s="29" t="n">
-        <v>354932.64</v>
+        <v>354927.57</v>
       </c>
       <c r="C33" s="29" t="n">
-        <v>9249822.09</v>
+        <v>9249794.442</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>R-09, R-10</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -9520,14 +10027,14 @@
         </is>
       </c>
       <c r="B34" s="29" t="n">
-        <v>354918.7</v>
+        <v>354935.617</v>
       </c>
       <c r="C34" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249792.835999999</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -9542,11 +10049,11 @@
         <v>354936.52</v>
       </c>
       <c r="C35" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08, R-18</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -9558,14 +10065,14 @@
         </is>
       </c>
       <c r="B36" s="29" t="n">
-        <v>354936.52</v>
+        <v>354932.64</v>
       </c>
       <c r="C36" s="29" t="n">
         <v>9249839.939999999</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-08, R-10</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -9580,11 +10087,11 @@
         <v>354932.64</v>
       </c>
       <c r="C37" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249822.09</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-09, R-10</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -9596,14 +10103,14 @@
         </is>
       </c>
       <c r="B38" s="29" t="n">
-        <v>354937.26</v>
+        <v>354932.64</v>
       </c>
       <c r="C38" s="29" t="n">
         <v>9249815.970000001</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -9615,10 +10122,10 @@
         </is>
       </c>
       <c r="B39" s="29" t="n">
-        <v>354937.26</v>
+        <v>354949.97</v>
       </c>
       <c r="C39" s="29" t="n">
-        <v>9249804.4</v>
+        <v>9249804.09</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
@@ -9634,14 +10141,14 @@
         </is>
       </c>
       <c r="B40" s="29" t="n">
-        <v>354937.26</v>
+        <v>354953.1</v>
       </c>
       <c r="C40" s="29" t="n">
-        <v>9249795.1</v>
+        <v>9249811.689999999</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -9653,14 +10160,14 @@
         </is>
       </c>
       <c r="B41" s="29" t="n">
-        <v>354935.617</v>
+        <v>354953.2</v>
       </c>
       <c r="C41" s="29" t="n">
-        <v>9249795.1</v>
+        <v>9249796.029999999</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -9675,7 +10182,7 @@
         <v>354976.9</v>
       </c>
       <c r="C42" s="29" t="n">
-        <v>9249786.300000001</v>
+        <v>9249796</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
@@ -9694,7 +10201,7 @@
         <v>354976.9</v>
       </c>
       <c r="C43" s="29" t="n">
-        <v>9249796</v>
+        <v>9249831.279999999</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -9713,7 +10220,7 @@
         <v>354976.9</v>
       </c>
       <c r="C44" s="29" t="n">
-        <v>9249831.279999999</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
@@ -9793,7 +10300,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-12, R-16</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -9805,10 +10312,10 @@
         </is>
       </c>
       <c r="B49" s="29" t="n">
-        <v>354955.92</v>
+        <v>354952.52</v>
       </c>
       <c r="C49" s="29" t="n">
-        <v>9249796</v>
+        <v>9249831.279999999</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
@@ -9824,10 +10331,10 @@
         </is>
       </c>
       <c r="B50" s="29" t="n">
-        <v>354952.52</v>
+        <v>354935.26</v>
       </c>
       <c r="C50" s="29" t="n">
-        <v>9249831.279999999</v>
+        <v>9249815.970000001</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
@@ -9843,14 +10350,14 @@
         </is>
       </c>
       <c r="B51" s="29" t="n">
-        <v>354935.26</v>
+        <v>354952.32</v>
       </c>
       <c r="C51" s="29" t="n">
         <v>9249815.970000001</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -9865,11 +10372,11 @@
         <v>354952.32</v>
       </c>
       <c r="C52" s="29" t="n">
-        <v>9249815.970000001</v>
+        <v>9249838.82</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -9884,11 +10391,11 @@
         <v>354952.32</v>
       </c>
       <c r="C53" s="29" t="n">
-        <v>9249838.82</v>
+        <v>9249839.939999999</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>R-15, R-16</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -9900,14 +10407,14 @@
         </is>
       </c>
       <c r="B54" s="29" t="n">
-        <v>354952.32</v>
+        <v>354971.71</v>
       </c>
       <c r="C54" s="29" t="n">
         <v>9249839.939999999</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>R-14</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -9919,10 +10426,10 @@
         </is>
       </c>
       <c r="B55" s="29" t="n">
-        <v>354971.71</v>
+        <v>354948.13</v>
       </c>
       <c r="C55" s="29" t="n">
-        <v>9249839.939999999</v>
+        <v>9249838.82</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
@@ -9938,14 +10445,14 @@
         </is>
       </c>
       <c r="B56" s="29" t="n">
-        <v>354971.71</v>
+        <v>354948.13</v>
       </c>
       <c r="C56" s="29" t="n">
         <v>9249851.869999999</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>R-15, R-17</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -9957,14 +10464,14 @@
         </is>
       </c>
       <c r="B57" s="29" t="n">
-        <v>354948.13</v>
+        <v>354971.71</v>
       </c>
       <c r="C57" s="29" t="n">
-        <v>9249838.82</v>
+        <v>9249851.869999999</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>R-16, R-17</t>
+          <t>R-15</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -9976,14 +10483,14 @@
         </is>
       </c>
       <c r="B58" s="29" t="n">
-        <v>354948.13</v>
+        <v>354918.93</v>
       </c>
       <c r="C58" s="29" t="n">
-        <v>9249851.869999999</v>
+        <v>9249865.08</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>R-17, R-18</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -9995,14 +10502,14 @@
         </is>
       </c>
       <c r="B59" s="29" t="n">
-        <v>354941.39</v>
+        <v>354950.13</v>
       </c>
       <c r="C59" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249865.08</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -10014,14 +10521,14 @@
         </is>
       </c>
       <c r="B60" s="29" t="n">
-        <v>354948.13</v>
+        <v>354950.6</v>
       </c>
       <c r="C60" s="29" t="n">
-        <v>9249853.470000001</v>
+        <v>9249868.98</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>R-18, R-19</t>
+          <t>R-16</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -10040,77 +10547,195 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
+          <t>R-17</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>P-58</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="n">
+        <v>354911</v>
+      </c>
+      <c r="C62" s="29" t="n">
+        <v>9249853.6</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>R-17, R-18</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>P-59</t>
+        </is>
+      </c>
+      <c r="B63" s="29" t="n">
+        <v>354911</v>
+      </c>
+      <c r="C63" s="29" t="n">
+        <v>9249854.1</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>R-17</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>P-60</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="n">
+        <v>354936.47</v>
+      </c>
+      <c r="C64" s="29" t="n">
+        <v>9249851.689999999</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>R-18</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>P-61</t>
+        </is>
+      </c>
+      <c r="B65" s="29" t="n">
+        <v>354911</v>
+      </c>
+      <c r="C65" s="29" t="n">
+        <v>9249851.689999999</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>R-18, R-19</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>P-62</t>
+        </is>
+      </c>
+      <c r="B66" s="29" t="n">
+        <v>354897.16</v>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>9249851.689999999</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
           <t>R-19</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B62" s="31" t="n">
-        <v>354820.629</v>
-      </c>
-      <c r="C62" s="31" t="n">
-        <v>9249848.939999999</v>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
+      <c r="B67" s="31" t="n">
+        <v>354820.121</v>
+      </c>
+      <c r="C67" s="31" t="n">
+        <v>9249849.426000001</v>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>Cerco sur-oeste (lado C22-C1, x = 820.7): al talud natural que baja a la quebrada del oeste</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="30" t="inlineStr">
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>Cerco sur-oeste (lado C22-C1, x = 820.1): al talud natural que baja a la quebrada del oeste</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B63" s="31" t="n">
+      <c r="B68" s="31" t="n">
         <v>354965.5</v>
       </c>
-      <c r="C63" s="31" t="n">
+      <c r="C68" s="31" t="n">
         <v>9249869.58</v>
       </c>
-      <c r="D63" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>R-12</t>
         </is>
       </c>
-      <c r="E63" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>Cerco norte (x = 965.5): poza de salida que rebalsa a nivel del fondo de la hondonada natural (baja a la quebrada del norte)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B64" s="31" t="n">
+      <c r="B69" s="31" t="n">
         <v>354935.5</v>
       </c>
-      <c r="C64" s="31" t="n">
+      <c r="C69" s="31" t="n">
         <v>9249792.248</v>
       </c>
-      <c r="D64" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>Cerco sur junto a C14 (x = 935.5): al terreno exterior que baja al Jr. Alfonso Ugarte (183.00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>354911</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>9249854.699999999</v>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>R-17</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>Cerco norte (lado C3-C4, x = 911.0): al talud natural que baja a la quebrada del norte</t>
         </is>
       </c>
     </row>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -631,7 +631,7 @@
         <v/>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.832</v>
+        <v>0.894</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.853</v>
+        <v>0.922</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -685,11 +685,11 @@
         <v/>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.734</v>
+        <v>0.796</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>D2: Cerco norte (x = 965.5): poza de salida que rebalsa a nivel del fondo de la hondonada natural (baja a la quebrada del norte)</t>
+          <t>D2: Cerco norte (x = 965.5): pase en el cimiento del cerco al terreno exterior que baja a la quebrada del norte</t>
         </is>
       </c>
     </row>
@@ -770,14 +770,14 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>4. Rasante: NTN +184.50 en la plataforma; en el resto del area dentro del cerco, el terreno de las curvas recortado a +184.50.</t>
+          <t>4. Interior del cerco nivelado: pisos y pasadizos NPT +184.65; borde de cuneta +184.60; areas verdes +184.55; patio de maniobra +184.50 (cuneta al ras, con rejilla). Fuera del cerco, el terreno natural.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>5. D1, D3 y D4 salen por un pase en el cimiento del cerco; D2 por una poza de salida (0.80 x 0.80 m) que rebalsa a nivel del terreno. Fuera del cerco no hay obra.</t>
+          <t>5. D1, D2, D3 y D4 salen por un pase en el cimiento del cerco. Fuera del cerco no hay obra.</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>minima 0.50 % (R-02 P-04-P-05); maxima 47.52 %</t>
+          <t>minima 0.50 % (R-01 P-01-P-02); maxima 20.16 %</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>inicio 0.30 a 0.30; minima 0.25 (R-01); maxima 0.85 (R-07, prog 82.5)</t>
+          <t>inicio 0.30 a 0.30; minima 0.25 (R-01); maxima 0.92 (R-07, prog 96.2)</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>15 empalmes; caida maxima 0.34 m (R-11 en P-26)</t>
+          <t>15 empalmes; caida maxima 0.34 m (R-16 en P-44)</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>D1 C.F. 183.465: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.8 m del cerco; D2 C.F. 180.154: poza de salida: rebalsa a 180.62 (fondo de la hondonada); afuera el fondo no sube y baja 0.25 m a 11.8 m; D3 C.F. 183.482: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 1.8 m del cerco; D4 C.F. 183.999: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.8 m del cerco</t>
+          <t>D1 C.F. 183.660: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.5 m del cerco; D2 C.F. 183.704: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.2 m del cerco; D3 C.F. 183.576: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 1.0 m del cerco; D4 C.F. 184.099: pase en el cimiento del cerco; el terreno exterior queda bajo la C.F. a 0.5 m del cerco</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Borde de la cuneta por debajo del NPT de los bloques vecinos</t>
+          <t>Borde de la cuneta 0.05 m bajo el NPT (+184.65) y 0.05 m sobre el area verde (+184.55)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>41 rotulos NPT revisados (bloques a menos de 5 m de una cuneta); NPT de 183.50 a 184.65; borde de cuneta &lt;= NPT en todos</t>
+          <t>borde de cuneta +184.60 en la red dentro del cerco (NPT +184.65, area verde +184.55); junto al patio de maniobra (NTN +184.50) borde al ras +184.50 en 292 puntos</t>
         </is>
       </c>
     </row>
@@ -1012,11 +1012,11 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.072 m en R-12 P-43-P-44 (Q 134.8 l/s, y 0.185, h 0.26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.115 m en R-01 P-03-D1 (Q 190.8 l/s, y 0.135, h 0.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="11" t="n">
         <v>9</v>
       </c>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-03-D1 (S 19.1 %, V 5.28), R-12 P-40-P-41 (S 18.7 %, V 4.25), R-12 P-42-P-43 (S 6.9 %, V 3.33), R-15 P-53-P-41 (S 47.5 %, V 3.43) -&gt; gradas (escalones) de concreto</t>
+          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-03-D1 (S 8.0 %, V 3.91), R-07 P-30-D3 (S 17.2 %, V 4.37) -&gt; gradas (escalones) de concreto</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>ningun borde de cuneta pasa el cerco; solo las 3 salidas lo atraviesan</t>
+          <t>ningun borde de cuneta pasa el cerco; solo las 4 salidas lo atraviesan</t>
         </is>
       </c>
     </row>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>183.465</v>
+        <v>183.66</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.8 m (perfilado maximo 0.30 m, sin obra)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.5 m (perfilado maximo 0.11 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1125,11 +1125,11 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>180.154</v>
+        <v>183.704</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>poza de salida: rebalsa a 180.62; el fondo exterior no sube y baja 0.25 m a 11.8 m</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.2 m (perfilado maximo 0.00 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>183.482</v>
+        <v>183.576</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 1.8 m (perfilado maximo 0.26 m, sin obra)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 1.0 m (perfilado maximo 0.16 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>183.999</v>
+        <v>184.099</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.8 m (perfilado maximo 0.25 m, sin obra)</t>
+          <t>pase en el cimiento del cerco: el terreno exterior queda bajo la C.F. a 0.5 m (perfilado maximo 0.15 m, sin obra)</t>
         </is>
       </c>
     </row>
@@ -1350,11 +1350,11 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>NTN de la plataforma de los bloques</t>
+          <t>Borde superior de la cuneta (rasante)</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Rotulos NTN del plano de arquitectura</t>
+          <t>Indicacion del usuario: NPT +184.65 (pisos y pasadizos), area verde +184.55</t>
         </is>
       </c>
     </row>
@@ -1596,20 +1596,20 @@
         <v/>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.93</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.077</v>
+        <v>0.095</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="20">
         <f>H11-G11</f>
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="K11" s="21">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1645,20 +1645,20 @@
         <v/>
       </c>
       <c r="F12" s="18" t="n">
-        <v>15.15</v>
+        <v>20.16</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="I12" s="20">
         <f>H12-G12</f>
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="K12" s="21">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1694,20 +1694,20 @@
         <v/>
       </c>
       <c r="F13" s="18" t="n">
-        <v>19.13</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.1</v>
+        <v>0.135</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="20">
         <f>H13-G13</f>
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>5.28</v>
+        <v>3.91</v>
       </c>
       <c r="K13" s="21">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1949,7 +1949,7 @@
         <v>0.339</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="I18" s="20">
         <f>H18-G18</f>
@@ -2880,7 +2880,7 @@
         <v>0.256</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="I37" s="20">
         <f>H37-G37</f>
@@ -2929,7 +2929,7 @@
         <v>0.258</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I38" s="20">
         <f>H38-G38</f>
@@ -2972,20 +2972,20 @@
         <v/>
       </c>
       <c r="F39" s="18" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0.27</v>
+        <v>0.85</v>
       </c>
       <c r="I39" s="20">
         <f>H39-G39</f>
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="K39" s="21">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3021,20 +3021,20 @@
         <v/>
       </c>
       <c r="F40" s="18" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="G40" s="19" t="n">
-        <v>0.195</v>
+        <v>0.266</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>0.27</v>
+        <v>0.88</v>
       </c>
       <c r="I40" s="20">
         <f>H40-G40</f>
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="K40" s="21">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3070,20 +3070,20 @@
         <v/>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.5</v>
+        <v>17.21</v>
       </c>
       <c r="G41" s="19" t="n">
-        <v>0.266</v>
+        <v>0.075</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="I41" s="20">
         <f>H41-G41</f>
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.24</v>
+        <v>4.37</v>
       </c>
       <c r="K41" s="21">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3093,7 +3093,11 @@
         <f>IF(J41&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M41" s="22" t="inlineStr"/>
+      <c r="M41" s="22" t="inlineStr">
+        <is>
+          <t>gradas de concreto (escalones) en este tramo</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
@@ -3615,7 +3619,7 @@
         <v>0.161</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="I52" s="20">
         <f>H52-G52</f>
@@ -3658,20 +3662,20 @@
         <v/>
       </c>
       <c r="F53" s="18" t="n">
-        <v>18.72</v>
+        <v>0.5</v>
       </c>
       <c r="G53" s="19" t="n">
-        <v>0.065</v>
+        <v>0.235</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="I53" s="20">
         <f>H53-G53</f>
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>4.25</v>
+        <v>1.19</v>
       </c>
       <c r="K53" s="21">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3681,11 +3685,7 @@
         <f>IF(J53&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M53" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M53" s="22" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
@@ -3711,20 +3711,20 @@
         <v/>
       </c>
       <c r="F54" s="18" t="n">
-        <v>5.03</v>
+        <v>0.5</v>
       </c>
       <c r="G54" s="19" t="n">
-        <v>0.12</v>
+        <v>0.282</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>0.25</v>
+        <v>0.68</v>
       </c>
       <c r="I54" s="20">
         <f>H54-G54</f>
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>2.94</v>
+        <v>1.26</v>
       </c>
       <c r="K54" s="21">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3760,20 +3760,20 @@
         <v/>
       </c>
       <c r="F55" s="18" t="n">
-        <v>6.92</v>
+        <v>0.5</v>
       </c>
       <c r="G55" s="19" t="n">
-        <v>0.111</v>
+        <v>0.294</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>0.26</v>
+        <v>0.72</v>
       </c>
       <c r="I55" s="20">
         <f>H55-G55</f>
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>3.33</v>
+        <v>1.28</v>
       </c>
       <c r="K55" s="21">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3783,11 +3783,7 @@
         <f>IF(J55&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M55" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M55" s="22" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
@@ -3813,20 +3809,20 @@
         <v/>
       </c>
       <c r="F56" s="18" t="n">
-        <v>1.69</v>
+        <v>0.5</v>
       </c>
       <c r="G56" s="19" t="n">
-        <v>0.185</v>
+        <v>0.295</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>0.26</v>
+        <v>0.78</v>
       </c>
       <c r="I56" s="20">
         <f>H56-G56</f>
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="K56" s="21">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3862,20 +3858,20 @@
         <v/>
       </c>
       <c r="F57" s="18" t="n">
-        <v>11.71</v>
+        <v>0.5</v>
       </c>
       <c r="G57" s="19" t="n">
-        <v>0.106</v>
+        <v>0.344</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>0.4</v>
+        <v>0.79</v>
       </c>
       <c r="I57" s="20">
         <f>H57-G57</f>
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>4.25</v>
+        <v>1.33</v>
       </c>
       <c r="K57" s="21">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4064,7 +4060,7 @@
         <v>0.089</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I61" s="20">
         <f>H61-G61</f>
@@ -4113,7 +4109,7 @@
         <v>0.112</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="I62" s="20">
         <f>H62-G62</f>
@@ -4162,7 +4158,7 @@
         <v>0.114</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I63" s="20">
         <f>H63-G63</f>
@@ -4303,20 +4299,20 @@
         <v/>
       </c>
       <c r="F66" s="18" t="n">
-        <v>47.52</v>
+        <v>0.5</v>
       </c>
       <c r="G66" s="19" t="n">
-        <v>0.02</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="I66" s="20">
         <f>H66-G66</f>
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>3.43</v>
+        <v>0.79</v>
       </c>
       <c r="K66" s="21">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4326,11 +4322,7 @@
         <f>IF(J66&lt;=$B$7,"CUMPLE","GRADAS")</f>
         <v/>
       </c>
-      <c r="M66" s="22" t="inlineStr">
-        <is>
-          <t>gradas de concreto (escalones) en este tramo</t>
-        </is>
-      </c>
+      <c r="M66" s="22" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
@@ -4405,20 +4397,20 @@
         <v/>
       </c>
       <c r="F68" s="18" t="n">
-        <v>11.05</v>
+        <v>0.5</v>
       </c>
       <c r="G68" s="19" t="n">
-        <v>0.029</v>
+        <v>0.081</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="I68" s="20">
         <f>H68-G68</f>
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>2.11</v>
+        <v>0.77</v>
       </c>
       <c r="K68" s="21">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4454,20 +4446,20 @@
         <v/>
       </c>
       <c r="F69" s="18" t="n">
-        <v>21.72</v>
+        <v>0.5</v>
       </c>
       <c r="G69" s="19" t="n">
-        <v>0.027</v>
+        <v>0.094</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="I69" s="20">
         <f>H69-G69</f>
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>2.84</v>
+        <v>0.83</v>
       </c>
       <c r="K69" s="21">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4984,16 +4976,16 @@
         <v>31.9</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>184.155</v>
+        <v>184.6</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>183.905</v>
+        <v>184.141</v>
       </c>
       <c r="J5" s="26">
         <f>F5-H5</f>
@@ -5051,16 +5043,16 @@
         <v>2.15</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>184.155</v>
+        <v>184.6</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>184.024</v>
+        <v>184.6</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>183.905</v>
+        <v>184.141</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>183.579</v>
+        <v>183.708</v>
       </c>
       <c r="J6" s="26">
         <f>F6-H6</f>
@@ -5118,16 +5110,16 @@
         <v>0.6</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>184.024</v>
+        <v>184.6</v>
       </c>
       <c r="G7" s="24" t="n">
         <v>183.91</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>183.579</v>
+        <v>183.708</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>183.465</v>
+        <v>183.66</v>
       </c>
       <c r="J7" s="26">
         <f>F7-H7</f>
@@ -5185,16 +5177,16 @@
         <v>32.42</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>184.038</v>
+        <v>184.138</v>
       </c>
       <c r="J8" s="26">
         <f>F8-H8</f>
@@ -5252,16 +5244,16 @@
         <v>11.53</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>184.038</v>
+        <v>184.138</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>183.98</v>
+        <v>184.08</v>
       </c>
       <c r="J9" s="26">
         <f>F9-H9</f>
@@ -5319,16 +5311,16 @@
         <v>8.68</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>183.98</v>
+        <v>184.08</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>183.726</v>
+        <v>183.826</v>
       </c>
       <c r="J10" s="26">
         <f>F10-H10</f>
@@ -5386,16 +5378,16 @@
         <v>11.47</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>183.726</v>
+        <v>183.826</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>183.668</v>
+        <v>183.768</v>
       </c>
       <c r="J11" s="26">
         <f>F11-H11</f>
@@ -5453,16 +5445,16 @@
         <v>12.1</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>184.024</v>
+        <v>184.6</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>183.668</v>
+        <v>183.768</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>183.608</v>
+        <v>183.708</v>
       </c>
       <c r="J12" s="26">
         <f>F12-H12</f>
@@ -5520,16 +5512,16 @@
         <v>32.31</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>184.038</v>
+        <v>184.138</v>
       </c>
       <c r="J13" s="26">
         <f>F13-H13</f>
@@ -5587,16 +5579,16 @@
         <v>26.1</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>184.07</v>
+        <v>184.17</v>
       </c>
       <c r="J14" s="26">
         <f>F14-H14</f>
@@ -5654,16 +5646,16 @@
         <v>9.43</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>184.07</v>
+        <v>184.17</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>184.022</v>
+        <v>184.122</v>
       </c>
       <c r="J15" s="26">
         <f>F15-H15</f>
@@ -5721,16 +5713,16 @@
         <v>3.78</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>184.022</v>
+        <v>184.122</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>184.003</v>
+        <v>184.103</v>
       </c>
       <c r="J16" s="26">
         <f>F16-H16</f>
@@ -5788,16 +5780,16 @@
         <v>15.97</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>184.003</v>
+        <v>184.103</v>
       </c>
       <c r="I17" s="25" t="n">
-        <v>183.924</v>
+        <v>184.024</v>
       </c>
       <c r="J17" s="26">
         <f>F17-H17</f>
@@ -5855,16 +5847,16 @@
         <v>6.79</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>183.924</v>
+        <v>184.024</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>183.89</v>
+        <v>183.99</v>
       </c>
       <c r="J18" s="26">
         <f>F18-H18</f>
@@ -5922,16 +5914,16 @@
         <v>32.81</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>183.89</v>
+        <v>183.99</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>183.726</v>
+        <v>183.826</v>
       </c>
       <c r="J19" s="26">
         <f>F19-H19</f>
@@ -5989,16 +5981,16 @@
         <v>21.32</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>184.093</v>
+        <v>184.193</v>
       </c>
       <c r="J20" s="26">
         <f>F20-H20</f>
@@ -6056,16 +6048,16 @@
         <v>5.89</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>184.093</v>
+        <v>184.193</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>184.064</v>
+        <v>184.164</v>
       </c>
       <c r="J21" s="26">
         <f>F21-H21</f>
@@ -6123,16 +6115,16 @@
         <v>17.83</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>184.064</v>
+        <v>184.164</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>183.975</v>
+        <v>184.075</v>
       </c>
       <c r="J22" s="26">
         <f>F22-H22</f>
@@ -6190,16 +6182,16 @@
         <v>5.77</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G23" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>183.975</v>
+        <v>184.075</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>183.946</v>
+        <v>184.046</v>
       </c>
       <c r="J23" s="26">
         <f>F23-H23</f>
@@ -6257,16 +6249,16 @@
         <v>39.15</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G24" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>183.946</v>
+        <v>184.046</v>
       </c>
       <c r="I24" s="25" t="n">
-        <v>183.75</v>
+        <v>183.85</v>
       </c>
       <c r="J24" s="26">
         <f>F24-H24</f>
@@ -6324,16 +6316,16 @@
         <v>11.74</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G25" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I25" s="25" t="n">
-        <v>184.141</v>
+        <v>184.241</v>
       </c>
       <c r="J25" s="26">
         <f>F25-H25</f>
@@ -6391,16 +6383,16 @@
         <v>11.51</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G26" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>184.002</v>
+        <v>184.102</v>
       </c>
       <c r="J26" s="26">
         <f>F26-H26</f>
@@ -6458,16 +6450,16 @@
         <v>17.85</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G27" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>184.002</v>
+        <v>184.102</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>183.912</v>
+        <v>184.012</v>
       </c>
       <c r="J27" s="26">
         <f>F27-H27</f>
@@ -6525,16 +6517,16 @@
         <v>6.12</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G28" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>183.912</v>
+        <v>184.012</v>
       </c>
       <c r="I28" s="25" t="n">
-        <v>183.882</v>
+        <v>183.982</v>
       </c>
       <c r="J28" s="26">
         <f>F28-H28</f>
@@ -6592,16 +6584,16 @@
         <v>22.77</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G29" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>183.882</v>
+        <v>183.982</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>183.768</v>
+        <v>183.868</v>
       </c>
       <c r="J29" s="26">
         <f>F29-H29</f>
@@ -6659,16 +6651,16 @@
         <v>11.77</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G30" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>183.768</v>
+        <v>183.868</v>
       </c>
       <c r="I30" s="25" t="n">
-        <v>183.709</v>
+        <v>183.809</v>
       </c>
       <c r="J30" s="26">
         <f>F30-H30</f>
@@ -6726,16 +6718,16 @@
         <v>3.07</v>
       </c>
       <c r="F31" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>184.412</v>
+        <v>184.6</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>183.709</v>
+        <v>183.809</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>183.694</v>
+        <v>183.794</v>
       </c>
       <c r="J31" s="26">
         <f>F31-H31</f>
@@ -6793,16 +6785,16 @@
         <v>7.96</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>184.412</v>
+        <v>184.6</v>
       </c>
       <c r="G32" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>183.694</v>
+        <v>183.794</v>
       </c>
       <c r="I32" s="25" t="n">
-        <v>183.654</v>
+        <v>183.754</v>
       </c>
       <c r="J32" s="26">
         <f>F32-H32</f>
@@ -6860,16 +6852,16 @@
         <v>6.69</v>
       </c>
       <c r="F33" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G33" s="24" t="n">
-        <v>183.852</v>
+        <v>184.6</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>183.654</v>
+        <v>183.754</v>
       </c>
       <c r="I33" s="25" t="n">
-        <v>183.578</v>
+        <v>183.72</v>
       </c>
       <c r="J33" s="26">
         <f>F33-H33</f>
@@ -6927,16 +6919,16 @@
         <v>8.210000000000001</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>183.852</v>
+        <v>184.6</v>
       </c>
       <c r="G34" s="24" t="n">
-        <v>184.023</v>
+        <v>184.6</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>183.578</v>
+        <v>183.72</v>
       </c>
       <c r="I34" s="25" t="n">
-        <v>183.485</v>
+        <v>183.679</v>
       </c>
       <c r="J34" s="26">
         <f>F34-H34</f>
@@ -6994,16 +6986,16 @@
         <v>0.6</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>184.023</v>
+        <v>184.6</v>
       </c>
       <c r="G35" s="24" t="n">
         <v>183.826</v>
       </c>
       <c r="H35" s="25" t="n">
-        <v>183.485</v>
+        <v>183.679</v>
       </c>
       <c r="I35" s="25" t="n">
-        <v>183.482</v>
+        <v>183.576</v>
       </c>
       <c r="J35" s="26">
         <f>F35-H35</f>
@@ -7061,16 +7053,16 @@
         <v>3.88</v>
       </c>
       <c r="F36" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G36" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H36" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I36" s="25" t="n">
-        <v>184.181</v>
+        <v>184.281</v>
       </c>
       <c r="J36" s="26">
         <f>F36-H36</f>
@@ -7128,16 +7120,16 @@
         <v>35.8</v>
       </c>
       <c r="F37" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G37" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>184.181</v>
+        <v>184.281</v>
       </c>
       <c r="I37" s="25" t="n">
-        <v>184.002</v>
+        <v>184.102</v>
       </c>
       <c r="J37" s="26">
         <f>F37-H37</f>
@@ -7195,16 +7187,16 @@
         <v>35.8</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I38" s="25" t="n">
-        <v>184.021</v>
+        <v>184.121</v>
       </c>
       <c r="J38" s="26">
         <f>F38-H38</f>
@@ -7262,16 +7254,16 @@
         <v>17.85</v>
       </c>
       <c r="F39" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G39" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I39" s="25" t="n">
-        <v>184.111</v>
+        <v>184.211</v>
       </c>
       <c r="J39" s="26">
         <f>F39-H39</f>
@@ -7329,16 +7321,16 @@
         <v>6.12</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G40" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>184.111</v>
+        <v>184.211</v>
       </c>
       <c r="I40" s="25" t="n">
-        <v>184.08</v>
+        <v>184.18</v>
       </c>
       <c r="J40" s="26">
         <f>F40-H40</f>
@@ -7396,16 +7388,16 @@
         <v>13.03</v>
       </c>
       <c r="F41" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G41" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>184.08</v>
+        <v>184.18</v>
       </c>
       <c r="I41" s="25" t="n">
-        <v>184.015</v>
+        <v>184.115</v>
       </c>
       <c r="J41" s="26">
         <f>F41-H41</f>
@@ -7463,16 +7455,16 @@
         <v>30.36</v>
       </c>
       <c r="F42" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G42" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H42" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I42" s="25" t="n">
-        <v>184.048</v>
+        <v>184.148</v>
       </c>
       <c r="J42" s="26">
         <f>F42-H42</f>
@@ -7530,16 +7522,16 @@
         <v>15.66</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H43" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I43" s="25" t="n">
-        <v>184.122</v>
+        <v>184.222</v>
       </c>
       <c r="J43" s="26">
         <f>F43-H43</f>
@@ -7597,16 +7589,16 @@
         <v>23.7</v>
       </c>
       <c r="F44" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G44" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H44" s="25" t="n">
-        <v>184.122</v>
+        <v>184.222</v>
       </c>
       <c r="I44" s="25" t="n">
-        <v>184.003</v>
+        <v>184.103</v>
       </c>
       <c r="J44" s="26">
         <f>F44-H44</f>
@@ -7664,16 +7656,16 @@
         <v>35.28</v>
       </c>
       <c r="F45" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G45" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="H45" s="25" t="n">
-        <v>184.003</v>
+        <v>184.103</v>
       </c>
       <c r="I45" s="25" t="n">
-        <v>183.827</v>
+        <v>183.927</v>
       </c>
       <c r="J45" s="26">
         <f>F45-H45</f>
@@ -7737,10 +7729,10 @@
         <v>184.5</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>183.827</v>
+        <v>183.927</v>
       </c>
       <c r="I46" s="25" t="n">
-        <v>183.783</v>
+        <v>183.883</v>
       </c>
       <c r="J46" s="26">
         <f>F46-H46</f>
@@ -7801,13 +7793,13 @@
         <v>184.5</v>
       </c>
       <c r="G47" s="24" t="n">
-        <v>181.8</v>
+        <v>184.5</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>183.783</v>
+        <v>183.883</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>181.55</v>
+        <v>183.824</v>
       </c>
       <c r="J47" s="26">
         <f>F47-H47</f>
@@ -7865,16 +7857,16 @@
         <v>8.630000000000001</v>
       </c>
       <c r="F48" s="24" t="n">
-        <v>181.8</v>
+        <v>184.5</v>
       </c>
       <c r="G48" s="24" t="n">
-        <v>181.418</v>
+        <v>184.5</v>
       </c>
       <c r="H48" s="25" t="n">
-        <v>181.55</v>
+        <v>183.824</v>
       </c>
       <c r="I48" s="25" t="n">
-        <v>181.117</v>
+        <v>183.781</v>
       </c>
       <c r="J48" s="26">
         <f>F48-H48</f>
@@ -7932,16 +7924,16 @@
         <v>12.29</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>181.418</v>
+        <v>184.5</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>180.523</v>
+        <v>184.5</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>181.117</v>
+        <v>183.781</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>180.266</v>
+        <v>183.719</v>
       </c>
       <c r="J49" s="26">
         <f>F49-H49</f>
@@ -7999,16 +7991,16 @@
         <v>2.5</v>
       </c>
       <c r="F50" s="24" t="n">
-        <v>180.523</v>
+        <v>184.5</v>
       </c>
       <c r="G50" s="24" t="n">
-        <v>180.623</v>
+        <v>184.5</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>180.266</v>
+        <v>183.719</v>
       </c>
       <c r="I50" s="25" t="n">
-        <v>180.224</v>
+        <v>183.707</v>
       </c>
       <c r="J50" s="26">
         <f>F50-H50</f>
@@ -8066,16 +8058,16 @@
         <v>0.6</v>
       </c>
       <c r="F51" s="24" t="n">
-        <v>180.623</v>
+        <v>184.5</v>
       </c>
       <c r="G51" s="24" t="n">
-        <v>180.553</v>
+        <v>184.5</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>180.224</v>
+        <v>183.707</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>180.154</v>
+        <v>183.704</v>
       </c>
       <c r="J51" s="26">
         <f>F51-H51</f>
@@ -8200,16 +8192,16 @@
         <v>17.06</v>
       </c>
       <c r="F53" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G53" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H53" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>184.115</v>
+        <v>184.215</v>
       </c>
       <c r="J53" s="26">
         <f>F53-H53</f>
@@ -8267,16 +8259,16 @@
         <v>22.85</v>
       </c>
       <c r="F54" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G54" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="H54" s="25" t="n">
-        <v>184.115</v>
+        <v>184.215</v>
       </c>
       <c r="I54" s="25" t="n">
-        <v>184</v>
+        <v>184.1</v>
       </c>
       <c r="J54" s="26">
         <f>F54-H54</f>
@@ -8340,10 +8332,10 @@
         <v>184.5</v>
       </c>
       <c r="H55" s="25" t="n">
-        <v>184</v>
+        <v>184.1</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>183.995</v>
+        <v>184.095</v>
       </c>
       <c r="J55" s="26">
         <f>F55-H55</f>
@@ -8407,10 +8399,10 @@
         <v>184.5</v>
       </c>
       <c r="H56" s="25" t="n">
-        <v>183.995</v>
+        <v>184.095</v>
       </c>
       <c r="I56" s="25" t="n">
-        <v>183.898</v>
+        <v>183.998</v>
       </c>
       <c r="J56" s="26">
         <f>F56-H56</f>
@@ -8474,10 +8466,10 @@
         <v>184.5</v>
       </c>
       <c r="H57" s="25" t="n">
-        <v>183.898</v>
+        <v>183.998</v>
       </c>
       <c r="I57" s="25" t="n">
-        <v>183.872</v>
+        <v>183.972</v>
       </c>
       <c r="J57" s="26">
         <f>F57-H57</f>
@@ -8535,16 +8527,16 @@
         <v>13.05</v>
       </c>
       <c r="F58" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G58" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H58" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I58" s="25" t="n">
-        <v>184.135</v>
+        <v>184.235</v>
       </c>
       <c r="J58" s="26">
         <f>F58-H58</f>
@@ -8602,16 +8594,16 @@
         <v>23.58</v>
       </c>
       <c r="F59" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G59" s="24" t="n">
         <v>184.5</v>
       </c>
       <c r="H59" s="25" t="n">
-        <v>184.135</v>
+        <v>184.235</v>
       </c>
       <c r="I59" s="25" t="n">
-        <v>184.017</v>
+        <v>184.117</v>
       </c>
       <c r="J59" s="26">
         <f>F59-H59</f>
@@ -8672,13 +8664,13 @@
         <v>184.5</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>181.8</v>
+        <v>184.5</v>
       </c>
       <c r="H60" s="25" t="n">
-        <v>184.017</v>
+        <v>184.117</v>
       </c>
       <c r="I60" s="25" t="n">
-        <v>181.55</v>
+        <v>184.091</v>
       </c>
       <c r="J60" s="26">
         <f>F60-H60</f>
@@ -8736,16 +8728,16 @@
         <v>31.2</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G61" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H61" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I61" s="25" t="n">
-        <v>184.044</v>
+        <v>184.144</v>
       </c>
       <c r="J61" s="26">
         <f>F61-H61</f>
@@ -8803,16 +8795,16 @@
         <v>3.93</v>
       </c>
       <c r="F62" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G62" s="24" t="n">
-        <v>183.86</v>
+        <v>184.6</v>
       </c>
       <c r="H62" s="25" t="n">
-        <v>184.044</v>
+        <v>184.144</v>
       </c>
       <c r="I62" s="25" t="n">
-        <v>183.61</v>
+        <v>184.124</v>
       </c>
       <c r="J62" s="26">
         <f>F62-H62</f>
@@ -8870,16 +8862,16 @@
         <v>14.9</v>
       </c>
       <c r="F63" s="24" t="n">
-        <v>183.86</v>
+        <v>184.6</v>
       </c>
       <c r="G63" s="24" t="n">
-        <v>180.623</v>
+        <v>184.5</v>
       </c>
       <c r="H63" s="25" t="n">
-        <v>183.61</v>
+        <v>184.124</v>
       </c>
       <c r="I63" s="25" t="n">
-        <v>180.373</v>
+        <v>184.05</v>
       </c>
       <c r="J63" s="26">
         <f>F63-H63</f>
@@ -8937,16 +8929,16 @@
         <v>39.03</v>
       </c>
       <c r="F64" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G64" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H64" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I64" s="25" t="n">
-        <v>184.004</v>
+        <v>184.104</v>
       </c>
       <c r="J64" s="26">
         <f>F64-H64</f>
@@ -9004,16 +8996,16 @@
         <v>0.5</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G65" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H65" s="25" t="n">
-        <v>184.004</v>
+        <v>184.104</v>
       </c>
       <c r="I65" s="25" t="n">
-        <v>184.002</v>
+        <v>184.102</v>
       </c>
       <c r="J65" s="26">
         <f>F65-H65</f>
@@ -9071,16 +9063,16 @@
         <v>0.6</v>
       </c>
       <c r="F66" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G66" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H66" s="25" t="n">
-        <v>184.002</v>
+        <v>184.102</v>
       </c>
       <c r="I66" s="25" t="n">
-        <v>183.999</v>
+        <v>184.099</v>
       </c>
       <c r="J66" s="26">
         <f>F66-H66</f>
@@ -9138,16 +9130,16 @@
         <v>11.75</v>
       </c>
       <c r="F67" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G67" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H67" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I67" s="25" t="n">
-        <v>184.141</v>
+        <v>184.241</v>
       </c>
       <c r="J67" s="26">
         <f>F67-H67</f>
@@ -9205,16 +9197,16 @@
         <v>25.47</v>
       </c>
       <c r="F68" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G68" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H68" s="25" t="n">
-        <v>184.141</v>
+        <v>184.241</v>
       </c>
       <c r="I68" s="25" t="n">
-        <v>184.014</v>
+        <v>184.114</v>
       </c>
       <c r="J68" s="26">
         <f>F68-H68</f>
@@ -9272,16 +9264,16 @@
         <v>1.91</v>
       </c>
       <c r="F69" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G69" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H69" s="25" t="n">
-        <v>184.014</v>
+        <v>184.114</v>
       </c>
       <c r="I69" s="25" t="n">
-        <v>184.004</v>
+        <v>184.104</v>
       </c>
       <c r="J69" s="26">
         <f>F69-H69</f>
@@ -9339,16 +9331,16 @@
         <v>13.84</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="G70" s="24" t="n">
-        <v>184.5</v>
+        <v>184.6</v>
       </c>
       <c r="H70" s="25" t="n">
-        <v>184.2</v>
+        <v>184.3</v>
       </c>
       <c r="I70" s="25" t="n">
-        <v>184.131</v>
+        <v>184.231</v>
       </c>
       <c r="J70" s="26">
         <f>F70-H70</f>
@@ -10689,7 +10681,7 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>Cerco norte (x = 965.5): poza de salida que rebalsa a nivel del fondo de la hondonada natural (baja a la quebrada del norte)</t>
+          <t>Cerco norte (x = 965.5): pase en el cimiento del cerco al terreno exterior que baja a la quebrada del norte</t>
         </is>
       </c>
     </row>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIDRAULICA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRAMOS" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NUDOS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECCIONES" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -119,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -190,6 +191,8 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -791,7 +794,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta, DC-02 cuadro y secciones, DC-03 a DC-06 perfiles, DC-07 y DC-08 isometricos, DC-09 y DC-10 cortes, DC-11 detalle de descargas.</t>
+          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta general de cunetas - planteamiento preliminar; DC-02 cuadro de tramos y secciones tipicas de cuneta; DC-03 a DC-11 perfiles longitudinales de cunetas por eje; DC-12 a DC-15 secciones transversales de cunetas; DC-16 isometrico de la red - vista desde el sur; DC-17 isometrico de la red - vista desde el norte; DC-18 cortes por las descargas d1, d2, d3 y d4; DC-19 cortes generales del terreno y la red; DC-20 detalle isometrico de las descargas por el cerco.</t>
         </is>
       </c>
     </row>
@@ -872,7 +875,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>19 ramales: R-01-&gt;D1, R-02-&gt;D1, R-03-&gt;D1, R-04-&gt;D1, R-05-&gt;D1, R-06-&gt;D1, R-07-&gt;D3, R-08-&gt;D3, R-09-&gt;D3, R-10-&gt;D3, R-11-&gt;D3, R-12-&gt;D2, R-13-&gt;D2, R-14-&gt;D2, R-15-&gt;D2, R-16-&gt;D2, R-17-&gt;D4, R-18-&gt;D4, R-19-&gt;D4</t>
+          <t>19 ramales: EJE-01-&gt;D1, EJE-02-&gt;D1, EJE-03-&gt;D1, EJE-04-&gt;D1, EJE-05-&gt;D1, EJE-06-&gt;D1, EJE-07-&gt;D3, EJE-08-&gt;D3, EJE-09-&gt;D3, EJE-10-&gt;D3, EJE-11-&gt;D3, EJE-12-&gt;D2, EJE-13-&gt;D2, EJE-14-&gt;D2, EJE-15-&gt;D2, EJE-16-&gt;D2, EJE-17-&gt;D4, EJE-18-&gt;D4, EJE-19-&gt;D4</t>
         </is>
       </c>
     </row>
@@ -912,7 +915,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>minima 0.50 % (R-01 P-01-P-02); maxima 20.16 %</t>
+          <t>minima 0.50 % (EJE-01 P-01-P-02); maxima 20.16 %</t>
         </is>
       </c>
     </row>
@@ -932,7 +935,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>inicio 0.30 a 0.30; minima 0.25 (R-01); maxima 0.92 (R-07, prog 96.2)</t>
+          <t>inicio 0.30 a 0.30; minima 0.25 (EJE-01); maxima 0.92 (EJE-07, prog 96.2)</t>
         </is>
       </c>
     </row>
@@ -952,7 +955,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>15 empalmes; caida maxima 0.34 m (R-16 en P-44)</t>
+          <t>15 empalmes; caida maxima 0.34 m (EJE-16 en P-44)</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1015,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.115 m en R-01 P-03-D1 (Q 190.8 l/s, y 0.135, h 0.25)</t>
+          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.115 m en EJE-01 P-03-D1 (Q 190.8 l/s, y 0.135, h 0.25)</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1035,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: R-01 P-03-D1 (S 8.0 %, V 3.91), R-07 P-30-D3 (S 17.2 %, V 4.37) -&gt; gradas (escalones) de concreto</t>
+          <t>tramos de fuerte pendiente con V &gt; 3.0 m/s: EJE-01 P-03-D1 (S 8.0 %, V 3.91), EJE-07 P-30-D3 (S 17.2 %, V 4.37) -&gt; gradas (escalones) de concreto</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1511,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>RAMAL</t>
+          <t>EJE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1575,7 +1578,7 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
@@ -1624,7 +1627,7 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
@@ -1673,7 +1676,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
@@ -1726,7 +1729,7 @@
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
@@ -1775,7 +1778,7 @@
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
@@ -1824,7 +1827,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -1873,7 +1876,7 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
@@ -1922,7 +1925,7 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -1971,7 +1974,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>EJE-03</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -2020,7 +2023,7 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
@@ -2069,7 +2072,7 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -2118,7 +2121,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -2167,7 +2170,7 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
@@ -2216,7 +2219,7 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -2265,7 +2268,7 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -2314,7 +2317,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -2363,7 +2366,7 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -2412,7 +2415,7 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -2461,7 +2464,7 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -2510,7 +2513,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -2559,7 +2562,7 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>EJE-06</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -2608,7 +2611,7 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
@@ -2657,7 +2660,7 @@
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -2706,7 +2709,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
@@ -2755,7 +2758,7 @@
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -2804,7 +2807,7 @@
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
@@ -2853,7 +2856,7 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -2902,7 +2905,7 @@
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
@@ -2951,7 +2954,7 @@
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B39" s="18" t="inlineStr">
@@ -3000,7 +3003,7 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
@@ -3049,7 +3052,7 @@
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
@@ -3102,7 +3105,7 @@
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>EJE-08</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -3151,7 +3154,7 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>EJE-08</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
@@ -3200,7 +3203,7 @@
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>EJE-09</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -3249,7 +3252,7 @@
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -3298,7 +3301,7 @@
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -3347,7 +3350,7 @@
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -3396,7 +3399,7 @@
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>EJE-11</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -3445,7 +3448,7 @@
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
@@ -3494,7 +3497,7 @@
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
@@ -3543,7 +3546,7 @@
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B51" s="18" t="inlineStr">
@@ -3592,7 +3595,7 @@
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
@@ -3641,7 +3644,7 @@
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B53" s="18" t="inlineStr">
@@ -3690,7 +3693,7 @@
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
@@ -3739,7 +3742,7 @@
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B55" s="18" t="inlineStr">
@@ -3788,7 +3791,7 @@
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B56" s="18" t="inlineStr">
@@ -3837,7 +3840,7 @@
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="B57" s="18" t="inlineStr">
@@ -3886,7 +3889,7 @@
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>EJE-13</t>
         </is>
       </c>
       <c r="B58" s="18" t="inlineStr">
@@ -3935,7 +3938,7 @@
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="B59" s="18" t="inlineStr">
@@ -3984,7 +3987,7 @@
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="B60" s="18" t="inlineStr">
@@ -4033,7 +4036,7 @@
     <row r="61">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="B61" s="18" t="inlineStr">
@@ -4082,7 +4085,7 @@
     <row r="62">
       <c r="A62" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="B62" s="18" t="inlineStr">
@@ -4131,7 +4134,7 @@
     <row r="63">
       <c r="A63" s="18" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="B63" s="18" t="inlineStr">
@@ -4180,7 +4183,7 @@
     <row r="64">
       <c r="A64" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="B64" s="18" t="inlineStr">
@@ -4229,7 +4232,7 @@
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="B65" s="18" t="inlineStr">
@@ -4278,7 +4281,7 @@
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="B66" s="18" t="inlineStr">
@@ -4327,7 +4330,7 @@
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="B67" s="18" t="inlineStr">
@@ -4376,7 +4379,7 @@
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
@@ -4425,7 +4428,7 @@
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
@@ -4474,7 +4477,7 @@
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
@@ -4523,7 +4526,7 @@
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
@@ -4572,7 +4575,7 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
@@ -4621,7 +4624,7 @@
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
@@ -4670,7 +4673,7 @@
     <row r="74">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
@@ -4719,7 +4722,7 @@
     <row r="75">
       <c r="A75" s="18" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="B75" s="18" t="inlineStr">
@@ -4768,7 +4771,7 @@
     <row r="76">
       <c r="A76" s="18" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>EJE-19</t>
         </is>
       </c>
       <c r="B76" s="18" t="inlineStr">
@@ -4874,7 +4877,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>RAMAL</t>
+          <t>EJE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4949,7 +4952,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>DESCRIPCION DEL RAMAL</t>
+          <t>DESCRIPCION DEL EJE</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4962,7 @@
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -5026,7 +5029,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -5093,7 +5096,7 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -5160,7 +5163,7 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -5227,7 +5230,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -5294,7 +5297,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -5361,7 +5364,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -5428,7 +5431,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -5495,7 +5498,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>EJE-03</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -5562,7 +5565,7 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -5629,7 +5632,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -5696,7 +5699,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -5763,7 +5766,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -5830,7 +5833,7 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -5897,7 +5900,7 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -5964,7 +5967,7 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -6031,7 +6034,7 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -6098,7 +6101,7 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -6165,7 +6168,7 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -6232,7 +6235,7 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -6299,7 +6302,7 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>EJE-06</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -6366,7 +6369,7 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -6433,7 +6436,7 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -6500,7 +6503,7 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -6567,7 +6570,7 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -6634,7 +6637,7 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -6701,7 +6704,7 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -6768,7 +6771,7 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -6835,7 +6838,7 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
@@ -6902,7 +6905,7 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -6969,7 +6972,7 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
@@ -7036,7 +7039,7 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>EJE-08</t>
         </is>
       </c>
       <c r="C36" s="23" t="inlineStr">
@@ -7103,7 +7106,7 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>EJE-08</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
@@ -7170,7 +7173,7 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>EJE-09</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
@@ -7237,7 +7240,7 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="C39" s="23" t="inlineStr">
@@ -7304,7 +7307,7 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
@@ -7371,7 +7374,7 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
@@ -7438,7 +7441,7 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>EJE-11</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
@@ -7505,7 +7508,7 @@
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
@@ -7572,7 +7575,7 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C44" s="23" t="inlineStr">
@@ -7639,7 +7642,7 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
@@ -7706,7 +7709,7 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr">
@@ -7773,7 +7776,7 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
@@ -7840,7 +7843,7 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr">
@@ -7907,7 +7910,7 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
@@ -7974,7 +7977,7 @@
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr">
@@ -8041,7 +8044,7 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -8108,7 +8111,7 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>EJE-13</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
@@ -8175,7 +8178,7 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
@@ -8242,7 +8245,7 @@
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="C54" s="23" t="inlineStr">
@@ -8309,7 +8312,7 @@
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
@@ -8376,7 +8379,7 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr">
@@ -8443,7 +8446,7 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
@@ -8510,7 +8513,7 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr">
@@ -8577,7 +8580,7 @@
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
@@ -8644,7 +8647,7 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="C60" s="23" t="inlineStr">
@@ -8711,7 +8714,7 @@
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
@@ -8778,7 +8781,7 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="C62" s="23" t="inlineStr">
@@ -8845,7 +8848,7 @@
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
@@ -8912,7 +8915,7 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="C64" s="23" t="inlineStr">
@@ -8979,7 +8982,7 @@
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
@@ -9046,7 +9049,7 @@
       </c>
       <c r="B66" s="23" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="C66" s="23" t="inlineStr">
@@ -9113,7 +9116,7 @@
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="C67" s="23" t="inlineStr">
@@ -9180,7 +9183,7 @@
       </c>
       <c r="B68" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="C68" s="23" t="inlineStr">
@@ -9247,7 +9250,7 @@
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
@@ -9314,7 +9317,7 @@
       </c>
       <c r="B70" s="23" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>EJE-19</t>
         </is>
       </c>
       <c r="C70" s="23" t="inlineStr">
@@ -9452,7 +9455,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>RAMALES QUE PASAN</t>
+          <t>EJES QUE PASAN</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -9475,7 +9478,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -9494,7 +9497,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -9513,7 +9516,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>R-01, R-02</t>
+          <t>EJE-01, EJE-02</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -9532,7 +9535,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -9551,7 +9554,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>EJE-02</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -9570,7 +9573,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-03</t>
+          <t>EJE-02, EJE-03</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -9589,7 +9592,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-04</t>
+          <t>EJE-02, EJE-04</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -9608,7 +9611,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>R-02, R-05</t>
+          <t>EJE-02, EJE-05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -9627,7 +9630,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>EJE-03</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -9646,7 +9649,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -9665,7 +9668,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -9684,7 +9687,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>R-04, R-06</t>
+          <t>EJE-04, EJE-06</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -9703,7 +9706,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -9722,7 +9725,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -9741,7 +9744,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>EJE-04</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -9760,7 +9763,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -9779,7 +9782,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -9798,7 +9801,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -9817,7 +9820,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -9836,7 +9839,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>EJE-05</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -9855,7 +9858,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>R-06, R-07</t>
+          <t>EJE-06, EJE-07</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -9874,7 +9877,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -9893,7 +9896,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-08</t>
+          <t>EJE-07, EJE-08</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -9912,7 +9915,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-09</t>
+          <t>EJE-07, EJE-09</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -9931,7 +9934,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-10</t>
+          <t>EJE-07, EJE-10</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -9950,7 +9953,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>R-07, R-11</t>
+          <t>EJE-07, EJE-11</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -9969,7 +9972,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -9988,7 +9991,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -10007,7 +10010,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -10026,7 +10029,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -10045,7 +10048,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>R-08, R-18</t>
+          <t>EJE-08, EJE-18</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -10064,7 +10067,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>R-08, R-10</t>
+          <t>EJE-08, EJE-10</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -10083,7 +10086,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>R-09, R-10</t>
+          <t>EJE-09, EJE-10</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -10102,7 +10105,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>EJE-10</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -10121,7 +10124,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>EJE-11</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -10140,7 +10143,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -10159,7 +10162,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -10178,7 +10181,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -10197,7 +10200,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>R-12, R-13</t>
+          <t>EJE-12, EJE-13</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -10216,7 +10219,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>R-12, R-14</t>
+          <t>EJE-12, EJE-14</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -10235,7 +10238,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>R-12, R-15</t>
+          <t>EJE-12, EJE-15</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -10254,7 +10257,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -10273,7 +10276,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -10292,7 +10295,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>R-12, R-16</t>
+          <t>EJE-12, EJE-16</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -10311,7 +10314,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>EJE-13</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -10330,7 +10333,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
@@ -10349,7 +10352,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -10368,7 +10371,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -10387,7 +10390,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -10406,7 +10409,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>R-14</t>
+          <t>EJE-14</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -10425,7 +10428,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -10444,7 +10447,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -10463,7 +10466,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>R-15</t>
+          <t>EJE-15</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
@@ -10482,7 +10485,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -10501,7 +10504,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -10520,7 +10523,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>R-16</t>
+          <t>EJE-16</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -10539,7 +10542,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
@@ -10558,7 +10561,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>R-17, R-18</t>
+          <t>EJE-17, EJE-18</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -10577,7 +10580,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
@@ -10596,7 +10599,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>R-18</t>
+          <t>EJE-18</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -10615,7 +10618,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>R-18, R-19</t>
+          <t>EJE-18, EJE-19</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -10634,7 +10637,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>R-19</t>
+          <t>EJE-19</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -10653,7 +10656,7 @@
       </c>
       <c r="D67" s="30" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>EJE-01</t>
         </is>
       </c>
       <c r="E67" s="30" t="inlineStr">
@@ -10676,7 +10679,7 @@
       </c>
       <c r="D68" s="30" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>EJE-12</t>
         </is>
       </c>
       <c r="E68" s="30" t="inlineStr">
@@ -10699,7 +10702,7 @@
       </c>
       <c r="D69" s="30" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>EJE-07</t>
         </is>
       </c>
       <c r="E69" s="30" t="inlineStr">
@@ -10722,7 +10725,7 @@
       </c>
       <c r="D70" s="30" t="inlineStr">
         <is>
-          <t>R-17</t>
+          <t>EJE-17</t>
         </is>
       </c>
       <c r="E70" s="30" t="inlineStr">
@@ -10739,4 +10742,3908 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECCIONES DE LOS PERFILES LONGITUDINALES POR EJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO Y AMPLIACION DEL SERVICIO DE EDUCACION PRIMARIA EN LA I.E. N.° 0590, DISTRITO DE BARRANQUITA, PROVINCIA DE LAMAS, DEPARTAMENTO DE SAN MARTIN - C.I. N.° 468901</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SECCION</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EJE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PROGRESIVA (m)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NCF</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>H (m)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>EL (m)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>EM (m)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>EJE-01</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F5" s="33">
+        <f>D5-E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>S-02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>EJE-01</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>184.141</v>
+      </c>
+      <c r="F6" s="33">
+        <f>D6-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>S-03</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>EJE-01</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>183.708</v>
+      </c>
+      <c r="F7" s="33">
+        <f>D7-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>S-04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>EJE-01</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>183.91</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>183.66</v>
+      </c>
+      <c r="F8" s="33">
+        <f>D8-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Descarga D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F9" s="33">
+        <f>D9-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>S-06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>184.138</v>
+      </c>
+      <c r="F10" s="33">
+        <f>D10-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>S-07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="F11" s="33">
+        <f>D11-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>S-08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>183.826</v>
+      </c>
+      <c r="F12" s="33">
+        <f>D12-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>S-09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>183.768</v>
+      </c>
+      <c r="F13" s="33">
+        <f>D13-E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>S-10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>183.708</v>
+      </c>
+      <c r="F14" s="33">
+        <f>D14-E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>S-11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>EJE-03</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F15" s="33">
+        <f>D15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>S-12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>EJE-03</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <v>184.138</v>
+      </c>
+      <c r="F16" s="33">
+        <f>D16-E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>S-13</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F17" s="33">
+        <f>D17-E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>S-14</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>184.17</v>
+      </c>
+      <c r="F18" s="33">
+        <f>D18-E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>S-15</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>184.122</v>
+      </c>
+      <c r="F19" s="33">
+        <f>D19-E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>S-16</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>184.103</v>
+      </c>
+      <c r="F20" s="33">
+        <f>D20-E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>S-17</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>184.024</v>
+      </c>
+      <c r="F21" s="33">
+        <f>D21-E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>S-18</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="D22" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E22" s="32" t="n">
+        <v>183.99</v>
+      </c>
+      <c r="F22" s="33">
+        <f>D22-E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>S-19</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>EJE-04</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>183.826</v>
+      </c>
+      <c r="F23" s="33">
+        <f>D23-E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>S-20</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>EJE-05</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E24" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F24" s="33">
+        <f>D24-E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>S-21</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>EJE-05</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E25" s="32" t="n">
+        <v>184.193</v>
+      </c>
+      <c r="F25" s="33">
+        <f>D25-E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>S-22</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>EJE-05</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E26" s="32" t="n">
+        <v>184.164</v>
+      </c>
+      <c r="F26" s="33">
+        <f>D26-E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>S-23</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>EJE-05</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E27" s="32" t="n">
+        <v>184.075</v>
+      </c>
+      <c r="F27" s="33">
+        <f>D27-E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>S-24</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>EJE-05</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="D28" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E28" s="32" t="n">
+        <v>184.046</v>
+      </c>
+      <c r="F28" s="33">
+        <f>D28-E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H28" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>S-25</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>EJE-05</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E29" s="32" t="n">
+        <v>183.85</v>
+      </c>
+      <c r="F29" s="33">
+        <f>D29-E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>S-26</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>EJE-06</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E30" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F30" s="33">
+        <f>D30-E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>S-27</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>EJE-06</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="D31" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E31" s="32" t="n">
+        <v>184.241</v>
+      </c>
+      <c r="F31" s="33">
+        <f>D31-E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>S-28</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E32" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F32" s="33">
+        <f>D32-E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H32" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>S-29</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="D33" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>184.102</v>
+      </c>
+      <c r="F33" s="33">
+        <f>D33-E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H33" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>S-30</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="D34" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>184.012</v>
+      </c>
+      <c r="F34" s="33">
+        <f>D34-E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H34" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>S-31</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="n">
+        <v>35.48</v>
+      </c>
+      <c r="D35" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E35" s="32" t="n">
+        <v>183.982</v>
+      </c>
+      <c r="F35" s="33">
+        <f>D35-E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>S-32</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E36" s="32" t="n">
+        <v>183.868</v>
+      </c>
+      <c r="F36" s="33">
+        <f>D36-E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>S-33</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="D37" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E37" s="32" t="n">
+        <v>183.809</v>
+      </c>
+      <c r="F37" s="33">
+        <f>D37-E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H37" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>S-34</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="n">
+        <v>73.09</v>
+      </c>
+      <c r="D38" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E38" s="32" t="n">
+        <v>183.794</v>
+      </c>
+      <c r="F38" s="33">
+        <f>D38-E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H38" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>S-35</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="D39" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E39" s="32" t="n">
+        <v>183.754</v>
+      </c>
+      <c r="F39" s="33">
+        <f>D39-E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H39" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>S-36</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E40" s="32" t="n">
+        <v>183.72</v>
+      </c>
+      <c r="F40" s="33">
+        <f>D40-E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H40" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>S-37</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E41" s="32" t="n">
+        <v>183.679</v>
+      </c>
+      <c r="F41" s="33">
+        <f>D41-E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H41" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>S-38</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>183.826</v>
+      </c>
+      <c r="E42" s="32" t="n">
+        <v>183.576</v>
+      </c>
+      <c r="F42" s="33">
+        <f>D42-E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H42" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Descarga D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>S-39</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>EJE-08</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E43" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F43" s="33">
+        <f>D43-E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H43" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>S-40</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>EJE-08</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E44" s="32" t="n">
+        <v>184.281</v>
+      </c>
+      <c r="F44" s="33">
+        <f>D44-E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H44" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>S-41</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>EJE-08</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E45" s="32" t="n">
+        <v>184.102</v>
+      </c>
+      <c r="F45" s="33">
+        <f>D45-E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H45" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>S-42</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>EJE-09</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E46" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F46" s="33">
+        <f>D46-E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H46" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>S-43</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>EJE-09</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D47" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E47" s="32" t="n">
+        <v>184.121</v>
+      </c>
+      <c r="F47" s="33">
+        <f>D47-E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H47" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>S-44</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>EJE-10</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E48" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F48" s="33">
+        <f>D48-E48</f>
+        <v/>
+      </c>
+      <c r="G48" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>S-45</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>EJE-10</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E49" s="32" t="n">
+        <v>184.211</v>
+      </c>
+      <c r="F49" s="33">
+        <f>D49-E49</f>
+        <v/>
+      </c>
+      <c r="G49" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H49" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>S-46</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>EJE-10</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="D50" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E50" s="32" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="F50" s="33">
+        <f>D50-E50</f>
+        <v/>
+      </c>
+      <c r="G50" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>S-47</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>EJE-10</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E51" s="32" t="n">
+        <v>184.115</v>
+      </c>
+      <c r="F51" s="33">
+        <f>D51-E51</f>
+        <v/>
+      </c>
+      <c r="G51" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H51" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>S-48</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>EJE-11</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E52" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F52" s="33">
+        <f>D52-E52</f>
+        <v/>
+      </c>
+      <c r="G52" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H52" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>S-49</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>EJE-11</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="D53" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E53" s="32" t="n">
+        <v>184.203</v>
+      </c>
+      <c r="F53" s="33">
+        <f>D53-E53</f>
+        <v/>
+      </c>
+      <c r="G53" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H53" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Inicio de tapado</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>S-50</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>EJE-11</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E54" s="32" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="F54" s="33">
+        <f>D54-E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H54" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Fin de tapado</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>S-51</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>EJE-11</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E55" s="32" t="n">
+        <v>184.148</v>
+      </c>
+      <c r="F55" s="33">
+        <f>D55-E55</f>
+        <v/>
+      </c>
+      <c r="G55" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H55" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>S-52</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E56" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F56" s="33">
+        <f>D56-E56</f>
+        <v/>
+      </c>
+      <c r="G56" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H56" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>S-53</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E57" s="32" t="n">
+        <v>184.222</v>
+      </c>
+      <c r="F57" s="33">
+        <f>D57-E57</f>
+        <v/>
+      </c>
+      <c r="G57" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H57" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>S-54</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E58" s="32" t="n">
+        <v>184.103</v>
+      </c>
+      <c r="F58" s="33">
+        <f>D58-E58</f>
+        <v/>
+      </c>
+      <c r="G58" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H58" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>S-55</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="n">
+        <v>74.14</v>
+      </c>
+      <c r="D59" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E59" s="32" t="n">
+        <v>183.929</v>
+      </c>
+      <c r="F59" s="33">
+        <f>D59-E59</f>
+        <v/>
+      </c>
+      <c r="G59" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H59" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>S-56</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E60" s="32" t="n">
+        <v>183.927</v>
+      </c>
+      <c r="F60" s="33">
+        <f>D60-E60</f>
+        <v/>
+      </c>
+      <c r="G60" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H60" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>S-57</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>183.883</v>
+      </c>
+      <c r="F61" s="33">
+        <f>D61-E61</f>
+        <v/>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H61" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>S-58</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E62" s="32" t="n">
+        <v>183.824</v>
+      </c>
+      <c r="F62" s="33">
+        <f>D62-E62</f>
+        <v/>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H62" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>S-59</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>103.86</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>183.781</v>
+      </c>
+      <c r="F63" s="33">
+        <f>D63-E63</f>
+        <v/>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H63" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>S-60</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>183.719</v>
+      </c>
+      <c r="F64" s="33">
+        <f>D64-E64</f>
+        <v/>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H64" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>S-61</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>183.707</v>
+      </c>
+      <c r="F65" s="33">
+        <f>D65-E65</f>
+        <v/>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H65" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>S-62</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>183.704</v>
+      </c>
+      <c r="F66" s="33">
+        <f>D66-E66</f>
+        <v/>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Descarga D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>S-63</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>EJE-13</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="F67" s="33">
+        <f>D67-E67</f>
+        <v/>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H67" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>S-64</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>EJE-13</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>184.078</v>
+      </c>
+      <c r="F68" s="33">
+        <f>D68-E68</f>
+        <v/>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H68" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>S-65</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F69" s="33">
+        <f>D69-E69</f>
+        <v/>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H69" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>S-66</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>184.215</v>
+      </c>
+      <c r="F70" s="33">
+        <f>D70-E70</f>
+        <v/>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H70" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>S-67</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>184.143</v>
+      </c>
+      <c r="F71" s="33">
+        <f>D71-E71</f>
+        <v/>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H71" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>S-68</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>31.96</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>184.14</v>
+      </c>
+      <c r="F72" s="33">
+        <f>D72-E72</f>
+        <v/>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H72" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>S-69</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F73" s="33">
+        <f>D73-E73</f>
+        <v/>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H73" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>S-70</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>184.095</v>
+      </c>
+      <c r="F74" s="33">
+        <f>D74-E74</f>
+        <v/>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H74" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>S-71</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>183.998</v>
+      </c>
+      <c r="F75" s="33">
+        <f>D75-E75</f>
+        <v/>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H75" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>S-72</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>EJE-14</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>183.972</v>
+      </c>
+      <c r="F76" s="33">
+        <f>D76-E76</f>
+        <v/>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H76" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>S-73</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>EJE-15</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F77" s="33">
+        <f>D77-E77</f>
+        <v/>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H77" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>S-74</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>EJE-15</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>184.235</v>
+      </c>
+      <c r="F78" s="33">
+        <f>D78-E78</f>
+        <v/>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H78" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>S-75</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>EJE-15</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>184.22</v>
+      </c>
+      <c r="F79" s="33">
+        <f>D79-E79</f>
+        <v/>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H79" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>S-76</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>EJE-15</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>184.218</v>
+      </c>
+      <c r="F80" s="33">
+        <f>D80-E80</f>
+        <v/>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H80" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>S-77</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>EJE-15</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>184.117</v>
+      </c>
+      <c r="F81" s="33">
+        <f>D81-E81</f>
+        <v/>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>S-78</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>EJE-15</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>184.091</v>
+      </c>
+      <c r="F82" s="33">
+        <f>D82-E82</f>
+        <v/>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H82" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>S-79</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>EJE-16</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E83" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F83" s="33">
+        <f>D83-E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H83" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>S-80</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>EJE-16</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D84" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E84" s="32" t="n">
+        <v>184.144</v>
+      </c>
+      <c r="F84" s="33">
+        <f>D84-E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H84" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>S-81</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>EJE-16</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="D85" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E85" s="32" t="n">
+        <v>184.124</v>
+      </c>
+      <c r="F85" s="33">
+        <f>D85-E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H85" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>S-82</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>EJE-16</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="D86" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E86" s="32" t="n">
+        <v>184.122</v>
+      </c>
+      <c r="F86" s="33">
+        <f>D86-E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H86" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>S-83</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>EJE-16</t>
+        </is>
+      </c>
+      <c r="C87" s="32" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="D87" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E87" s="32" t="n">
+        <v>184.119</v>
+      </c>
+      <c r="F87" s="33">
+        <f>D87-E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H87" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Cambio de borde</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>S-84</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>EJE-16</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="D88" s="32" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="E88" s="32" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="F88" s="33">
+        <f>D88-E88</f>
+        <v/>
+      </c>
+      <c r="G88" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H88" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>S-85</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C89" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E89" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F89" s="33">
+        <f>D89-E89</f>
+        <v/>
+      </c>
+      <c r="G89" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H89" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>S-86</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="D90" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E90" s="32" t="n">
+        <v>184.256</v>
+      </c>
+      <c r="F90" s="33">
+        <f>D90-E90</f>
+        <v/>
+      </c>
+      <c r="G90" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H90" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Inicio de tapado</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>S-87</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="D91" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E91" s="32" t="n">
+        <v>184.236</v>
+      </c>
+      <c r="F91" s="33">
+        <f>D91-E91</f>
+        <v/>
+      </c>
+      <c r="G91" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H91" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Fin de tapado</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>S-88</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="D92" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E92" s="32" t="n">
+        <v>184.104</v>
+      </c>
+      <c r="F92" s="33">
+        <f>D92-E92</f>
+        <v/>
+      </c>
+      <c r="G92" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H92" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>S-89</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="D93" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E93" s="32" t="n">
+        <v>184.102</v>
+      </c>
+      <c r="F93" s="33">
+        <f>D93-E93</f>
+        <v/>
+      </c>
+      <c r="G93" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H93" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>S-90</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="D94" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E94" s="32" t="n">
+        <v>184.099</v>
+      </c>
+      <c r="F94" s="33">
+        <f>D94-E94</f>
+        <v/>
+      </c>
+      <c r="G94" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H94" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>TAPADA</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Descarga D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>S-91</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>EJE-18</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E95" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F95" s="33">
+        <f>D95-E95</f>
+        <v/>
+      </c>
+      <c r="G95" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H95" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>S-92</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>EJE-18</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D96" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E96" s="32" t="n">
+        <v>184.241</v>
+      </c>
+      <c r="F96" s="33">
+        <f>D96-E96</f>
+        <v/>
+      </c>
+      <c r="G96" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H96" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>S-93</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>EJE-18</t>
+        </is>
+      </c>
+      <c r="C97" s="32" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="D97" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E97" s="32" t="n">
+        <v>184.114</v>
+      </c>
+      <c r="F97" s="33">
+        <f>D97-E97</f>
+        <v/>
+      </c>
+      <c r="G97" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H97" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>Llega EJE-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>S-94</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>EJE-18</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="D98" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E98" s="32" t="n">
+        <v>184.104</v>
+      </c>
+      <c r="F98" s="33">
+        <f>D98-E98</f>
+        <v/>
+      </c>
+      <c r="G98" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H98" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>S-95</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>EJE-19</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E99" s="32" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="F99" s="33">
+        <f>D99-E99</f>
+        <v/>
+      </c>
+      <c r="G99" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H99" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>Inicio del eje</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>S-96</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>EJE-19</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="D100" s="32" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="E100" s="32" t="n">
+        <v>184.231</v>
+      </c>
+      <c r="F100" s="33">
+        <f>D100-E100</f>
+        <v/>
+      </c>
+      <c r="G100" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H100" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>CON REJILLA</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>Entrega a EJE-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -10946,7 +10946,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Llega EJE-02</t>
+          <t>Inicio de tapado; Llega EJE-02</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12175,11 @@
           <t>TAPADA</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Inicio de tapado</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -13043,7 +13047,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Llega EJE-13</t>
+          <t>Llega EJE-13; Cambio de borde</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13168,11 @@
           <t>TAPADA</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Inicio de tapado</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -14354,7 +14362,11 @@
           <t>TAPADA</t>
         </is>
       </c>
-      <c r="J93" s="4" t="inlineStr"/>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>Inicio de tapado</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRAMOS" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NUDOS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECCIONES" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPAS INSPECCION" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -791,7 +792,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta general de cunetas - planteamiento preliminar; DC-02 cuadro de tramos y secciones tipicas de cuneta; DC-03 a DC-11 perfiles longitudinales de cunetas por eje; DC-12 a DC-14 secciones transversales de cunetas; DC-15 isometrico de la red - vista desde el sur; DC-16 isometrico de la red - vista desde el norte; DC-17 cortes generales del terreno y la red; DC-18 detalle de la descarga d1 por el cerco; DC-19 detalle de la descarga d2 por el cerco; DC-20 detalle de la descarga d3 por el cerco; DC-21 detalle de la descarga d4 por el cerco.</t>
+          <t>7. Ver planos PLANTEAMIENTO_CUNETAS_IE0590_BARRANQUITA.dxf: DC-01 planta general de cunetas - planteamiento preliminar; DC-02 cuadro de tramos y secciones tipicas de cuneta; DC-03 a DC-11 perfiles longitudinales de cunetas por eje; DC-12 a DC-14 secciones transversales de cunetas; DC-15 cortes generales del terreno y la red; DC-16 detalle de la descarga d1 por el cerco; DC-17 detalle de la descarga d2 por el cerco; DC-18 detalle de la descarga d3 por el cerco; DC-19 detalle de la descarga d4 por el cerco.</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6234,7 @@
       </c>
       <c r="Q5" s="27" t="inlineStr">
         <is>
-          <t>Pabellon oeste A: lado nor-oeste; entrega al EJE-02 junto al cerco (caida)</t>
+          <t>Pabellon oeste A: lado nor-oeste; entrega al EJE-02 junto al cerco</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6301,7 @@
       </c>
       <c r="Q6" s="27" t="inlineStr">
         <is>
-          <t>Pabellon oeste A: lado nor-oeste; entrega al EJE-02 junto al cerco (caida)</t>
+          <t>Pabellon oeste A: lado nor-oeste; entrega al EJE-02 junto al cerco</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7038,7 @@
       </c>
       <c r="Q17" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7105,7 @@
       </c>
       <c r="Q18" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7172,7 @@
       </c>
       <c r="Q19" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7239,7 @@
       </c>
       <c r="Q20" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7306,7 @@
       </c>
       <c r="Q21" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7373,7 @@
       </c>
       <c r="Q22" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7440,7 @@
       </c>
       <c r="Q23" s="27" t="inlineStr">
         <is>
-          <t>Bloque x=884.9 (lado oeste), bloque D (lado norte) y pabellon C (lado nor-este)</t>
+          <t>Bloque D (lado norte) y pabellon C (lado nor-este)</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7842,7 @@
       </c>
       <c r="Q29" s="27" t="inlineStr">
         <is>
-          <t>Bloque del ingreso: lado norte (y=815.97) al oeste de x=896.8</t>
+          <t>Bloque del ingreso: lado norte, tramo oeste</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7909,7 @@
       </c>
       <c r="Q30" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7976,7 @@
       </c>
       <c r="Q31" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8043,7 @@
       </c>
       <c r="Q32" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8110,7 @@
       </c>
       <c r="Q33" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8177,7 @@
       </c>
       <c r="Q34" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8244,7 @@
       </c>
       <c r="Q35" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8311,7 @@
       </c>
       <c r="Q36" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8377,7 +8378,7 @@
       </c>
       <c r="Q37" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8445,7 @@
       </c>
       <c r="Q38" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8512,7 @@
       </c>
       <c r="Q39" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8579,7 @@
       </c>
       <c r="Q40" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8646,7 @@
       </c>
       <c r="Q41" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8713,7 @@
       </c>
       <c r="Q42" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8780,7 @@
       </c>
       <c r="Q43" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8847,7 @@
       </c>
       <c r="Q44" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8914,7 @@
       </c>
       <c r="Q45" s="27" t="inlineStr">
         <is>
-          <t>Patio central (x=896.8), y=815.97, bajada x=919.6 y atrio de ingreso a D3</t>
+          <t>Patio central, bajada al atrio de ingreso y salida D3</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8981,7 @@
       </c>
       <c r="Q46" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado sur (y=839.94)</t>
+          <t>Bloque del centro: lado sur</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9048,7 @@
       </c>
       <c r="Q47" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado sur (y=839.94)</t>
+          <t>Bloque del centro: lado sur</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9115,7 @@
       </c>
       <c r="Q48" s="27" t="inlineStr">
         <is>
-          <t>Patio central: y=822.09</t>
+          <t>Patio central</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9182,7 @@
       </c>
       <c r="Q49" s="27" t="inlineStr">
         <is>
-          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
+          <t>Bloque del frente: lado norte</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9249,7 @@
       </c>
       <c r="Q50" s="27" t="inlineStr">
         <is>
-          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
+          <t>Bloque del frente: lado norte</t>
         </is>
       </c>
     </row>
@@ -9315,7 +9316,7 @@
       </c>
       <c r="Q51" s="27" t="inlineStr">
         <is>
-          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
+          <t>Bloque del frente: lado norte</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9383,7 @@
       </c>
       <c r="Q52" s="27" t="inlineStr">
         <is>
-          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
+          <t>Bloque del frente: lado norte</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9450,7 @@
       </c>
       <c r="Q53" s="27" t="inlineStr">
         <is>
-          <t>x=932.6 y bloque del frente: lado norte (y=815.97)</t>
+          <t>Bloque del frente: lado norte</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9517,7 @@
       </c>
       <c r="Q54" s="27" t="inlineStr">
         <is>
-          <t>Bloque del frente: lado sur (y=804.1)</t>
+          <t>Bloque del frente: lado sur</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10388,7 @@
       </c>
       <c r="Q67" s="27" t="inlineStr">
         <is>
-          <t>Losa: lado norte (y=831.3)</t>
+          <t>Losa: lado norte</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10455,7 @@
       </c>
       <c r="Q68" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10522,7 @@
       </c>
       <c r="Q69" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10589,7 @@
       </c>
       <c r="Q70" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10656,7 @@
       </c>
       <c r="Q71" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10723,7 @@
       </c>
       <c r="Q72" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10789,7 +10790,7 @@
       </c>
       <c r="Q73" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10857,7 @@
       </c>
       <c r="Q74" s="27" t="inlineStr">
         <is>
-          <t>y=815.97, x=952.3 y bloque nor-este: lado sur (y=839.9)</t>
+          <t>Bloque nor-este: lado sur</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10924,7 @@
       </c>
       <c r="Q75" s="27" t="inlineStr">
         <is>
-          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
+          <t>Bloque nor-este: lados oeste y norte</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10991,7 @@
       </c>
       <c r="Q76" s="27" t="inlineStr">
         <is>
-          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
+          <t>Bloque nor-este: lados oeste y norte</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11058,7 @@
       </c>
       <c r="Q77" s="27" t="inlineStr">
         <is>
-          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
+          <t>Bloque nor-este: lados oeste y norte</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11125,7 @@
       </c>
       <c r="Q78" s="27" t="inlineStr">
         <is>
-          <t>Bloque nor-este: lado oeste (x=948.1) y lado norte (y=851.9)</t>
+          <t>Bloque nor-este: lados oeste y norte</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11192,7 @@
       </c>
       <c r="Q79" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
+          <t>Bloque norte: lado norte y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11259,7 @@
       </c>
       <c r="Q80" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
+          <t>Bloque norte: lado norte y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -11325,7 +11326,7 @@
       </c>
       <c r="Q81" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
+          <t>Bloque norte: lado norte y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11393,7 @@
       </c>
       <c r="Q82" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
+          <t>Bloque norte: lado norte y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11460,7 @@
       </c>
       <c r="Q83" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
+          <t>Bloque norte: lado norte y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11527,7 @@
       </c>
       <c r="Q84" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado norte (y=865.1) y union a D2 por el norte de la planta de tratamiento</t>
+          <t>Bloque norte: lado norte y union a D2 por el norte de la planta de tratamiento</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11594,7 @@
       </c>
       <c r="Q85" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
+          <t>Bloque norte: lado sur y salida D4</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11661,7 @@
       </c>
       <c r="Q86" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
+          <t>Bloque norte: lado sur y salida D4</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11728,7 @@
       </c>
       <c r="Q87" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
+          <t>Bloque norte: lado sur y salida D4</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11795,7 @@
       </c>
       <c r="Q88" s="27" t="inlineStr">
         <is>
-          <t>Bloque norte: lado sur (y=853.5) y salida D4</t>
+          <t>Bloque norte: lado sur y salida D4</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11862,7 @@
       </c>
       <c r="Q89" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+          <t>Bloque del centro: lados este y norte, tramo este</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11929,7 @@
       </c>
       <c r="Q90" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+          <t>Bloque del centro: lados este y norte, tramo este</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11996,7 @@
       </c>
       <c r="Q91" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+          <t>Bloque del centro: lados este y norte, tramo este</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12063,7 @@
       </c>
       <c r="Q92" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+          <t>Bloque del centro: lados este y norte, tramo este</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12130,7 @@
       </c>
       <c r="Q93" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado este (x=936.5) y lado norte (y=851.7), tramo este</t>
+          <t>Bloque del centro: lados este y norte, tramo este</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12197,7 @@
       </c>
       <c r="Q94" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado norte (y=851.7), tramo oeste</t>
+          <t>Bloque del centro: lado norte, tramo oeste</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12264,7 @@
       </c>
       <c r="Q95" s="27" t="inlineStr">
         <is>
-          <t>Bloque del centro: lado norte (y=851.7), tramo oeste</t>
+          <t>Bloque del centro: lado norte, tramo oeste</t>
         </is>
       </c>
     </row>
@@ -17046,4 +17047,347 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TAPAS DE INSPECCION EN TRAMOS TAPADOS (0.60 x 0.60, CONCRETO REMOVIBLE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO Y AMPLIACION DEL SERVICIO DE EDUCACION PRIMARIA EN LA I.E. N.° 0590, DISTRITO DE BARRANQUITA, PROVINCIA DE LAMAS, DEPARTAMENTO DE SAN MARTIN - C.I. N.° 468901</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>N.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EJE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PROGRESIVA (m)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ESTE (m)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NORTE (m)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>UBICACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>T-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>EJE-02</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>354820.328</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>9249849.642999999</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>T-02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>354919.895</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>9249801.445</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>T-03</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>354926.978</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>9249801.122</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>T-04</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>86.62</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>354928.135</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>9249794.353</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>T-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>EJE-07</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>354935.2</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>9249792.92</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>T-06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>103.56</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>354976.611</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>9249860.776000001</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>T-07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>110.54</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>354971.554</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>9249865.593</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>T-08</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>EJE-12</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>117.53</v>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>354965.926</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>9249868.98</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>T-09</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="D13" s="28" t="n">
+        <v>354940.68</v>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>9249853.501</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>T-10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>EJE-17</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>354937.5</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>9249853.512</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Inicio / fin de tramo tapado, empalme o a 10 m como maximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C15" s="29">
+        <f>COUNTA(B5:B14)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 211 mm/h, C = 0.80, area total 9393 m2; menor borde libre 0.135 m en EJE-11 P-48-P-33 (Q 16.3 l/s, y 0.065, h 0.20)</t>
+          <t>I = 401 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.119 m en EJE-11 P-48-P-33 (Q 22.7 l/s, y 0.081, h 0.20)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>V max 1.84 m/s</t>
+          <t>V max 1.73 m/s</t>
         </is>
       </c>
     </row>
@@ -1462,31 +1462,31 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>C (escorrentia)</t>
+          <t>C ponderado (escorrentia)</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>I (mm/h)</t>
+          <t>I (mm/h), T = 25 anos, tc = 10 min</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>211</v>
+        <v>400.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Factor de seguridad</t>
+          <t>P max 24 h transpuesta (mm)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1.15</v>
+        <v>231.49</v>
       </c>
     </row>
     <row r="7">
@@ -1502,7 +1502,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>I: tc = 10 min, TR = 25 anos, P10 = 35.16 mm (estacion usada en el Hogar de Refugio - Morales); reemplazar por la del proyecto. Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
+          <t>I: tc = 10 min, TR = 25 anos, P10 = 66.83 mm (estacion usada en el Hogar de Refugio - Morales); reemplazar por la del proyecto. Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.095</v>
+        <v>0.083</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>0.3</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="K11" s="20">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1649,7 +1649,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.098</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>0.46</v>
@@ -1659,7 +1659,7 @@
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="K12" s="20">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1698,7 +1698,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>0.3</v>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="K13" s="20">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1747,7 +1747,7 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.083</v>
+        <v>0.073</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>0.46</v>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="K14" s="20">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1796,7 +1796,7 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>0.46</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="K15" s="20">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1845,7 +1845,7 @@
         <v>2.92</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.078</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>0.52</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="K16" s="20">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1894,7 +1894,7 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.269</v>
+        <v>0.253</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>0.77</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="K17" s="20">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1943,7 +1943,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.269</v>
+        <v>0.253</v>
       </c>
       <c r="H18" s="17" t="n">
         <v>0.83</v>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="K18" s="20">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1992,7 +1992,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.339</v>
+        <v>0.327</v>
       </c>
       <c r="H19" s="17" t="n">
         <v>0.83</v>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="K19" s="20">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2041,7 +2041,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.339</v>
+        <v>0.327</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>0.79</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="K20" s="20">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2090,7 +2090,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.39</v>
+        <v>0.369</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>0.79</v>
@@ -2100,7 +2100,7 @@
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="K21" s="20">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2139,7 +2139,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
       <c r="H22" s="17" t="n">
         <v>0.3</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="K22" s="20">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2188,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.076</v>
+        <v>0.083</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>0.3</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="K23" s="20">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2237,7 +2237,7 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>0.43</v>
@@ -2247,7 +2247,7 @@
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K24" s="20">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2286,7 +2286,7 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>0.47</v>
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K25" s="20">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2335,7 +2335,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.101</v>
+        <v>0.112</v>
       </c>
       <c r="H26" s="17" t="n">
         <v>0.48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K26" s="20">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2384,7 +2384,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.124</v>
+        <v>0.132</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>0.49</v>
@@ -2394,7 +2394,7 @@
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="K27" s="20">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2433,7 +2433,7 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.132</v>
+        <v>0.139</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>0.57</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="K28" s="20">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.166</v>
+        <v>0.167</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>0.61</v>
@@ -2531,7 +2531,7 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.047</v>
+        <v>0.067</v>
       </c>
       <c r="H30" s="17" t="n">
         <v>0.3</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="K30" s="20">
         <f>IF(I30&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2580,7 +2580,7 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.054</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H31" s="17" t="n">
         <v>0.41</v>
@@ -2590,7 +2590,7 @@
         <v/>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="K31" s="20">
         <f>IF(I31&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2629,7 +2629,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.074</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H32" s="17" t="n">
         <v>0.44</v>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="K32" s="20">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.079</v>
+        <v>0.092</v>
       </c>
       <c r="H33" s="17" t="n">
         <v>0.53</v>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="K33" s="20">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2727,7 +2727,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.115</v>
+        <v>0.12</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>0.55</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="K34" s="20">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.034</v>
+        <v>0.043</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>0.3</v>
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K35" s="20">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2825,7 +2825,7 @@
         <v>1.72</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="H36" s="17" t="n">
         <v>0.3</v>
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="K36" s="20">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2874,7 +2874,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.124</v>
+        <v>0.134</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>0.5</v>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="K37" s="20">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,7 +2923,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.164</v>
+        <v>0.175</v>
       </c>
       <c r="H38" s="17" t="n">
         <v>0.59</v>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K38" s="20">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2972,7 +2972,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.164</v>
+        <v>0.175</v>
       </c>
       <c r="H39" s="17" t="n">
         <v>0.61</v>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K39" s="20">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3021,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.183</v>
+        <v>0.207</v>
       </c>
       <c r="H40" s="17" t="n">
         <v>0.62</v>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="K40" s="20">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3070,7 +3070,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.183</v>
+        <v>0.207</v>
       </c>
       <c r="H41" s="17" t="n">
         <v>0.73</v>
@@ -3080,7 +3080,7 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="K41" s="20">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3119,7 +3119,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.226</v>
+        <v>0.271</v>
       </c>
       <c r="H42" s="17" t="n">
         <v>0.73</v>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="K42" s="20">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3168,7 +3168,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.256</v>
+        <v>0.312</v>
       </c>
       <c r="H43" s="17" t="n">
         <v>0.79</v>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="K43" s="20">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3217,7 +3217,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.256</v>
+        <v>0.312</v>
       </c>
       <c r="H44" s="17" t="n">
         <v>0.7</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="K44" s="20">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3266,7 +3266,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.257</v>
+        <v>0.313</v>
       </c>
       <c r="H45" s="17" t="n">
         <v>0.7</v>
@@ -3276,7 +3276,7 @@
         <v/>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="K45" s="20">
         <f>IF(I45&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3315,7 +3315,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.258</v>
+        <v>0.314</v>
       </c>
       <c r="H46" s="17" t="n">
         <v>0.74</v>
@@ -3325,7 +3325,7 @@
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="K46" s="20">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3364,7 +3364,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0.26</v>
+        <v>0.315</v>
       </c>
       <c r="H47" s="17" t="n">
         <v>0.74</v>
@@ -3374,7 +3374,7 @@
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="K47" s="20">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3413,7 +3413,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.26</v>
+        <v>0.315</v>
       </c>
       <c r="H48" s="17" t="n">
         <v>0.77</v>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="K48" s="20">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.265</v>
+        <v>0.319</v>
       </c>
       <c r="H49" s="17" t="n">
         <v>0.77</v>
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="K49" s="20">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3511,7 +3511,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0.266</v>
+        <v>0.32</v>
       </c>
       <c r="H50" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="K50" s="20">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.266</v>
+        <v>0.32</v>
       </c>
       <c r="H51" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="K51" s="20">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3609,7 +3609,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="H52" s="17" t="n">
         <v>0.3</v>
@@ -3619,7 +3619,7 @@
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="K52" s="20">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3658,7 +3658,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>0.32</v>
@@ -3668,7 +3668,7 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K53" s="20">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3707,7 +3707,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="H54" s="17" t="n">
         <v>0.3</v>
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="K54" s="20">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3756,7 +3756,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.05</v>
+        <v>0.062</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>0.3</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="K55" s="20">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3805,7 +3805,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.054</v>
+        <v>0.068</v>
       </c>
       <c r="H56" s="17" t="n">
         <v>0.39</v>
@@ -3815,7 +3815,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="K56" s="20">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3854,7 +3854,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.056</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H57" s="17" t="n">
         <v>0.42</v>
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="K57" s="20">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3903,7 +3903,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="H58" s="17" t="n">
         <v>0.42</v>
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="K58" s="20">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3952,7 +3952,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="H59" s="17" t="n">
         <v>0.48</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="K59" s="20">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4001,7 +4001,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.065</v>
+        <v>0.081</v>
       </c>
       <c r="H60" s="17" t="n">
         <v>0.2</v>
@@ -4011,7 +4011,7 @@
         <v/>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="K60" s="20">
         <f>IF(I60&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4050,7 +4050,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="H61" s="17" t="n">
         <v>0.3</v>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="K61" s="20">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4099,7 +4099,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>0.38</v>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K62" s="20">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4148,7 +4148,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.095</v>
+        <v>0.092</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>0.38</v>
@@ -4158,7 +4158,7 @@
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="K63" s="20">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4197,7 +4197,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.095</v>
+        <v>0.093</v>
       </c>
       <c r="H64" s="17" t="n">
         <v>0.49</v>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="K64" s="20">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4246,7 +4246,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.132</v>
+        <v>0.124</v>
       </c>
       <c r="H65" s="17" t="n">
         <v>0.5</v>
@@ -4256,7 +4256,7 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K65" s="20">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4295,7 +4295,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
       <c r="H66" s="17" t="n">
         <v>0.52</v>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K66" s="20">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4344,7 +4344,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.235</v>
+        <v>0.279</v>
       </c>
       <c r="H67" s="17" t="n">
         <v>0.5600000000000001</v>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="K67" s="20">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4393,7 +4393,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.282</v>
+        <v>0.36</v>
       </c>
       <c r="H68" s="17" t="n">
         <v>0.62</v>
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="K68" s="20">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4442,7 +4442,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.294</v>
+        <v>0.38</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>0.57</v>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="K69" s="20">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4491,7 +4491,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.295</v>
+        <v>0.382</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>0.63</v>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="K70" s="20">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4540,7 +4540,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.295</v>
+        <v>0.382</v>
       </c>
       <c r="H71" s="17" t="n">
         <v>0.64</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="K71" s="20">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4589,7 +4589,7 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.344</v>
+        <v>0.45</v>
       </c>
       <c r="H72" s="17" t="n">
         <v>0.64</v>
@@ -4599,7 +4599,7 @@
         <v/>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="K72" s="20">
         <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4638,7 +4638,7 @@
         <v>0.5</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.056</v>
+        <v>0.064</v>
       </c>
       <c r="H73" s="17" t="n">
         <v>0.3</v>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K73" s="20">
         <f>IF(I73&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4687,7 +4687,7 @@
         <v>0.5</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.049</v>
+        <v>0.073</v>
       </c>
       <c r="H74" s="17" t="n">
         <v>0.3</v>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="J74" s="6" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="K74" s="20">
         <f>IF(I74&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4736,7 +4736,7 @@
         <v>0.5</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.053</v>
+        <v>0.075</v>
       </c>
       <c r="H75" s="17" t="n">
         <v>0.38</v>
@@ -4746,7 +4746,7 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="K75" s="20">
         <f>IF(I75&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4785,7 +4785,7 @@
         <v>0.5</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>0.35</v>
@@ -4795,7 +4795,7 @@
         <v/>
       </c>
       <c r="J76" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="K76" s="20">
         <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4834,7 +4834,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>0.35</v>
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="K77" s="20">
         <f>IF(I77&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4883,7 +4883,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.089</v>
+        <v>0.122</v>
       </c>
       <c r="H78" s="17" t="n">
         <v>0.35</v>
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="J78" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="K78" s="20">
         <f>IF(I78&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4932,7 +4932,7 @@
         <v>0.5</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.111</v>
+        <v>0.158</v>
       </c>
       <c r="H79" s="17" t="n">
         <v>0.35</v>
@@ -4942,7 +4942,7 @@
         <v/>
       </c>
       <c r="J79" s="6" t="n">
-        <v>0.9</v>
+        <v>1.04</v>
       </c>
       <c r="K79" s="20">
         <f>IF(I79&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4981,7 +4981,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.114</v>
+        <v>0.161</v>
       </c>
       <c r="H80" s="17" t="n">
         <v>0.45</v>
@@ -4991,7 +4991,7 @@
         <v/>
       </c>
       <c r="J80" s="6" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="K80" s="20">
         <f>IF(I80&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5030,7 +5030,7 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.042</v>
+        <v>0.061</v>
       </c>
       <c r="H81" s="17" t="n">
         <v>0.3</v>
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J81" s="6" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="K81" s="20">
         <f>IF(I81&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5079,7 +5079,7 @@
         <v>0.5</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.042</v>
+        <v>0.062</v>
       </c>
       <c r="H82" s="17" t="n">
         <v>0.36</v>
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="J82" s="6" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="K82" s="20">
         <f>IF(I82&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5128,7 +5128,7 @@
         <v>0.58</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.078</v>
+        <v>0.117</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>0.35</v>
@@ -5138,7 +5138,7 @@
         <v/>
       </c>
       <c r="J83" s="6" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="K83" s="20">
         <f>IF(I83&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5177,7 +5177,7 @@
         <v>0.5</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>0.35</v>
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="J84" s="6" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="K84" s="20">
         <f>IF(I84&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5226,7 +5226,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.075</v>
+        <v>0.092</v>
       </c>
       <c r="H85" s="17" t="n">
         <v>0.3</v>
@@ -5236,7 +5236,7 @@
         <v/>
       </c>
       <c r="J85" s="6" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="K85" s="20">
         <f>IF(I85&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5275,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="H86" s="17" t="n">
         <v>0.45</v>
@@ -5285,7 +5285,7 @@
         <v/>
       </c>
       <c r="J86" s="6" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="K86" s="20">
         <f>IF(I86&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5324,7 +5324,7 @@
         <v>0.5</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.08</v>
+        <v>0.099</v>
       </c>
       <c r="H87" s="17" t="n">
         <v>0.46</v>
@@ -5334,7 +5334,7 @@
         <v/>
       </c>
       <c r="J87" s="6" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="K87" s="20">
         <f>IF(I87&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5373,7 +5373,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.08</v>
+        <v>0.099</v>
       </c>
       <c r="H88" s="17" t="n">
         <v>0.47</v>
@@ -5383,7 +5383,7 @@
         <v/>
       </c>
       <c r="J88" s="6" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="K88" s="20">
         <f>IF(I88&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5422,7 +5422,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.094</v>
+        <v>0.122</v>
       </c>
       <c r="H89" s="17" t="n">
         <v>0.4</v>
@@ -5432,7 +5432,7 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="K89" s="20">
         <f>IF(I89&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5471,7 +5471,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.094</v>
+        <v>0.122</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>0.4</v>
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J90" s="6" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="K90" s="20">
         <f>IF(I90&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5520,7 +5520,7 @@
         <v>0.51</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.059</v>
+        <v>0.08</v>
       </c>
       <c r="H91" s="17" t="n">
         <v>0.2</v>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="J91" s="6" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="K91" s="20">
         <f>IF(I91&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5569,7 +5569,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.059</v>
+        <v>0.08</v>
       </c>
       <c r="H92" s="17" t="n">
         <v>0.5</v>
@@ -5579,7 +5579,7 @@
         <v/>
       </c>
       <c r="J92" s="6" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="K92" s="20">
         <f>IF(I92&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5618,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.106</v>
+        <v>0.122</v>
       </c>
       <c r="H93" s="17" t="n">
         <v>0.5</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="K93" s="20">
         <f>IF(I93&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5667,7 +5667,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.107</v>
+        <v>0.123</v>
       </c>
       <c r="H94" s="17" t="n">
         <v>0.4</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="J94" s="6" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K94" s="20">
         <f>IF(I94&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5716,7 +5716,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="H95" s="17" t="n">
         <v>0.3</v>
@@ -5726,7 +5726,7 @@
         <v/>
       </c>
       <c r="J95" s="6" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="K95" s="20">
         <f>IF(I95&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5765,7 +5765,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="H96" s="17" t="n">
         <v>0.36</v>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="K96" s="20">
         <f>IF(I96&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5814,7 +5814,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>0.36</v>
@@ -5824,7 +5824,7 @@
         <v/>
       </c>
       <c r="J97" s="6" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K97" s="20">
         <f>IF(I97&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5863,7 +5863,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>0.48</v>
@@ -5873,7 +5873,7 @@
         <v/>
       </c>
       <c r="J98" s="6" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K98" s="20">
         <f>IF(I98&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5912,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.073</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H99" s="17" t="n">
         <v>0.49</v>
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="K99" s="20">
         <f>IF(I99&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5961,7 +5961,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="H100" s="17" t="n">
         <v>0.3</v>
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="J100" s="6" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="K100" s="20">
         <f>IF(I100&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -6010,7 +6010,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="H101" s="17" t="n">
         <v>0.37</v>
@@ -6020,7 +6020,7 @@
         <v/>
       </c>
       <c r="J101" s="6" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="K101" s="20">
         <f>IF(I101&gt;=0.05,"CUMPLE","NO CUMPLE")</f>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 401 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.119 m en EJE-11 P-48-P-33 (Q 22.7 l/s, y 0.081, h 0.20)</t>
+          <t>I = 467 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.110 m en EJE-11 P-48-P-33 (Q 26.4 l/s, y 0.090, h 0.20)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>V max 1.73 m/s</t>
+          <t>V max 1.82 m/s</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>400.96</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>231.49</v>
+        <v>269.62</v>
       </c>
     </row>
     <row r="7">
@@ -1502,7 +1502,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>I: tc = 10 min, TR = 25 anos, P10 = 66.83 mm (estacion usada en el Hogar de Refugio - Morales); reemplazar por la del proyecto. Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
+          <t>I: tc = 10 min, TR = 25 anos, P10 = 77.83 mm (estacion usada en el Hogar de Refugio - Morales); reemplazar por la del proyecto. Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.083</v>
+        <v>0.092</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>0.3</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="K11" s="20">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1649,7 +1649,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>0.46</v>
@@ -1659,7 +1659,7 @@
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="K12" s="20">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1698,7 +1698,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>0.3</v>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="K13" s="20">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1747,7 +1747,7 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.073</v>
+        <v>0.081</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>0.46</v>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="K14" s="20">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1796,7 +1796,7 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.083</v>
+        <v>0.092</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>0.46</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="K15" s="20">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1845,7 +1845,7 @@
         <v>2.92</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>0.52</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="K16" s="20">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1894,7 +1894,7 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.253</v>
+        <v>0.285</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>0.77</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K17" s="20">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1943,7 +1943,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.253</v>
+        <v>0.285</v>
       </c>
       <c r="H18" s="17" t="n">
         <v>0.83</v>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="K18" s="20">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1992,7 +1992,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.327</v>
+        <v>0.37</v>
       </c>
       <c r="H19" s="17" t="n">
         <v>0.83</v>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="K19" s="20">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2041,7 +2041,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.327</v>
+        <v>0.37</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>0.79</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="K20" s="20">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2090,7 +2090,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.369</v>
+        <v>0.418</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>0.79</v>
@@ -2100,7 +2100,7 @@
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="K21" s="20">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2139,7 +2139,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.065</v>
+        <v>0.073</v>
       </c>
       <c r="H22" s="17" t="n">
         <v>0.3</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="K22" s="20">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2188,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.083</v>
+        <v>0.092</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>0.3</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="K23" s="20">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2237,7 +2237,7 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.089</v>
+        <v>0.099</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>0.43</v>
@@ -2247,7 +2247,7 @@
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="K24" s="20">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2286,7 +2286,7 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>0.47</v>
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="K25" s="20">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2335,7 +2335,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.112</v>
+        <v>0.124</v>
       </c>
       <c r="H26" s="17" t="n">
         <v>0.48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K26" s="20">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2384,7 +2384,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.132</v>
+        <v>0.147</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>0.49</v>
@@ -2394,7 +2394,7 @@
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="K27" s="20">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2433,7 +2433,7 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.139</v>
+        <v>0.156</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>0.57</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K28" s="20">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.167</v>
+        <v>0.187</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>0.61</v>
@@ -2492,7 +2492,7 @@
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K29" s="20">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2531,7 +2531,7 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
       <c r="H30" s="17" t="n">
         <v>0.3</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="K30" s="20">
         <f>IF(I30&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2580,7 +2580,7 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="H31" s="17" t="n">
         <v>0.41</v>
@@ -2590,7 +2590,7 @@
         <v/>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="K31" s="20">
         <f>IF(I31&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2629,7 +2629,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="H32" s="17" t="n">
         <v>0.44</v>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="K32" s="20">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.092</v>
+        <v>0.102</v>
       </c>
       <c r="H33" s="17" t="n">
         <v>0.53</v>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K33" s="20">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2727,7 +2727,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.12</v>
+        <v>0.133</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>0.55</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="K34" s="20">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>0.3</v>
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="K35" s="20">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2825,7 +2825,7 @@
         <v>1.72</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="H36" s="17" t="n">
         <v>0.3</v>
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="K36" s="20">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2874,7 +2874,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.134</v>
+        <v>0.15</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>0.5</v>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="K37" s="20">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,7 +2923,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.175</v>
+        <v>0.196</v>
       </c>
       <c r="H38" s="17" t="n">
         <v>0.59</v>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K38" s="20">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2972,7 +2972,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.175</v>
+        <v>0.196</v>
       </c>
       <c r="H39" s="17" t="n">
         <v>0.61</v>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K39" s="20">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3021,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.207</v>
+        <v>0.233</v>
       </c>
       <c r="H40" s="17" t="n">
         <v>0.62</v>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="K40" s="20">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3070,7 +3070,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.207</v>
+        <v>0.233</v>
       </c>
       <c r="H41" s="17" t="n">
         <v>0.73</v>
@@ -3080,7 +3080,7 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="K41" s="20">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3119,7 +3119,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.271</v>
+        <v>0.305</v>
       </c>
       <c r="H42" s="17" t="n">
         <v>0.73</v>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="K42" s="20">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3168,7 +3168,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.312</v>
+        <v>0.353</v>
       </c>
       <c r="H43" s="17" t="n">
         <v>0.79</v>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K43" s="20">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3217,7 +3217,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.312</v>
+        <v>0.353</v>
       </c>
       <c r="H44" s="17" t="n">
         <v>0.7</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K44" s="20">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3266,7 +3266,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.313</v>
+        <v>0.354</v>
       </c>
       <c r="H45" s="17" t="n">
         <v>0.7</v>
@@ -3276,7 +3276,7 @@
         <v/>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K45" s="20">
         <f>IF(I45&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3315,7 +3315,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.314</v>
+        <v>0.354</v>
       </c>
       <c r="H46" s="17" t="n">
         <v>0.74</v>
@@ -3325,7 +3325,7 @@
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K46" s="20">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3364,7 +3364,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0.315</v>
+        <v>0.356</v>
       </c>
       <c r="H47" s="17" t="n">
         <v>0.74</v>
@@ -3374,7 +3374,7 @@
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K47" s="20">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3413,7 +3413,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.315</v>
+        <v>0.356</v>
       </c>
       <c r="H48" s="17" t="n">
         <v>0.77</v>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K48" s="20">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.319</v>
+        <v>0.361</v>
       </c>
       <c r="H49" s="17" t="n">
         <v>0.77</v>
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="K49" s="20">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3511,7 +3511,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0.32</v>
+        <v>0.362</v>
       </c>
       <c r="H50" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="K50" s="20">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.32</v>
+        <v>0.362</v>
       </c>
       <c r="H51" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="K51" s="20">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3609,7 +3609,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="H52" s="17" t="n">
         <v>0.3</v>
@@ -3619,7 +3619,7 @@
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="K52" s="20">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3658,7 +3658,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>0.32</v>
@@ -3668,7 +3668,7 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="K53" s="20">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3707,7 +3707,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.073</v>
+        <v>0.081</v>
       </c>
       <c r="H54" s="17" t="n">
         <v>0.3</v>
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="K54" s="20">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3756,7 +3756,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.062</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>0.3</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="K55" s="20">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3805,7 +3805,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.068</v>
+        <v>0.075</v>
       </c>
       <c r="H56" s="17" t="n">
         <v>0.39</v>
@@ -3815,7 +3815,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="K56" s="20">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3854,7 +3854,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="H57" s="17" t="n">
         <v>0.42</v>
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="K57" s="20">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3903,7 +3903,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.091</v>
+        <v>0.101</v>
       </c>
       <c r="H58" s="17" t="n">
         <v>0.42</v>
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K58" s="20">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3952,7 +3952,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.091</v>
+        <v>0.101</v>
       </c>
       <c r="H59" s="17" t="n">
         <v>0.48</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K59" s="20">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4001,7 +4001,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="H60" s="17" t="n">
         <v>0.2</v>
@@ -4011,7 +4011,7 @@
         <v/>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K60" s="20">
         <f>IF(I60&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4050,7 +4050,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="H61" s="17" t="n">
         <v>0.3</v>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.65</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K61" s="20">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4099,7 +4099,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>0.38</v>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="K62" s="20">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4148,7 +4148,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.092</v>
+        <v>0.103</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>0.38</v>
@@ -4158,7 +4158,7 @@
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="K63" s="20">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4197,7 +4197,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.093</v>
+        <v>0.103</v>
       </c>
       <c r="H64" s="17" t="n">
         <v>0.49</v>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="K64" s="20">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4246,7 +4246,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.124</v>
+        <v>0.138</v>
       </c>
       <c r="H65" s="17" t="n">
         <v>0.5</v>
@@ -4256,7 +4256,7 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="K65" s="20">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4295,7 +4295,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.161</v>
+        <v>0.18</v>
       </c>
       <c r="H66" s="17" t="n">
         <v>0.52</v>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K66" s="20">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4344,7 +4344,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.279</v>
+        <v>0.315</v>
       </c>
       <c r="H67" s="17" t="n">
         <v>0.5600000000000001</v>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="K67" s="20">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4393,7 +4393,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.36</v>
+        <v>0.407</v>
       </c>
       <c r="H68" s="17" t="n">
         <v>0.62</v>
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K68" s="20">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4442,7 +4442,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>0.57</v>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="K69" s="20">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4491,7 +4491,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.382</v>
+        <v>0.433</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>0.63</v>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="K70" s="20">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4540,7 +4540,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.382</v>
+        <v>0.433</v>
       </c>
       <c r="H71" s="17" t="n">
         <v>0.64</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="K71" s="20">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4589,7 +4589,7 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.45</v>
+        <v>0.512</v>
       </c>
       <c r="H72" s="17" t="n">
         <v>0.64</v>
@@ -4599,7 +4599,7 @@
         <v/>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="K72" s="20">
         <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4638,7 +4638,7 @@
         <v>0.5</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.064</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H73" s="17" t="n">
         <v>0.3</v>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="K73" s="20">
         <f>IF(I73&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4687,7 +4687,7 @@
         <v>0.5</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.073</v>
+        <v>0.081</v>
       </c>
       <c r="H74" s="17" t="n">
         <v>0.3</v>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="J74" s="6" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="K74" s="20">
         <f>IF(I74&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4736,7 +4736,7 @@
         <v>0.5</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.075</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H75" s="17" t="n">
         <v>0.38</v>
@@ -4746,7 +4746,7 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="K75" s="20">
         <f>IF(I75&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4785,7 +4785,7 @@
         <v>0.5</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.12</v>
+        <v>0.133</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>0.35</v>
@@ -4795,7 +4795,7 @@
         <v/>
       </c>
       <c r="J76" s="6" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="K76" s="20">
         <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4834,7 +4834,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.12</v>
+        <v>0.134</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>0.35</v>
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="K77" s="20">
         <f>IF(I77&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4883,7 +4883,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.122</v>
+        <v>0.136</v>
       </c>
       <c r="H78" s="17" t="n">
         <v>0.35</v>
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="J78" s="6" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="K78" s="20">
         <f>IF(I78&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4932,7 +4932,7 @@
         <v>0.5</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.158</v>
+        <v>0.176</v>
       </c>
       <c r="H79" s="17" t="n">
         <v>0.35</v>
@@ -4942,7 +4942,7 @@
         <v/>
       </c>
       <c r="J79" s="6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K79" s="20">
         <f>IF(I79&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4981,7 +4981,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.161</v>
+        <v>0.181</v>
       </c>
       <c r="H80" s="17" t="n">
         <v>0.45</v>
@@ -4991,7 +4991,7 @@
         <v/>
       </c>
       <c r="J80" s="6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K80" s="20">
         <f>IF(I80&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5030,7 +5030,7 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.061</v>
+        <v>0.068</v>
       </c>
       <c r="H81" s="17" t="n">
         <v>0.3</v>
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J81" s="6" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="K81" s="20">
         <f>IF(I81&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5079,7 +5079,7 @@
         <v>0.5</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.062</v>
+        <v>0.068</v>
       </c>
       <c r="H82" s="17" t="n">
         <v>0.36</v>
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="J82" s="6" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="K82" s="20">
         <f>IF(I82&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5128,7 +5128,7 @@
         <v>0.58</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.117</v>
+        <v>0.13</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>0.35</v>
@@ -5138,7 +5138,7 @@
         <v/>
       </c>
       <c r="J83" s="6" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="K83" s="20">
         <f>IF(I83&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5177,7 +5177,7 @@
         <v>0.5</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.128</v>
+        <v>0.143</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>0.35</v>
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="J84" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="K84" s="20">
         <f>IF(I84&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5226,7 +5226,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.092</v>
+        <v>0.102</v>
       </c>
       <c r="H85" s="17" t="n">
         <v>0.3</v>
@@ -5236,7 +5236,7 @@
         <v/>
       </c>
       <c r="J85" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K85" s="20">
         <f>IF(I85&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5275,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.097</v>
+        <v>0.107</v>
       </c>
       <c r="H86" s="17" t="n">
         <v>0.45</v>
@@ -5285,7 +5285,7 @@
         <v/>
       </c>
       <c r="J86" s="6" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="K86" s="20">
         <f>IF(I86&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5324,7 +5324,7 @@
         <v>0.5</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.099</v>
+        <v>0.11</v>
       </c>
       <c r="H87" s="17" t="n">
         <v>0.46</v>
@@ -5334,7 +5334,7 @@
         <v/>
       </c>
       <c r="J87" s="6" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="K87" s="20">
         <f>IF(I87&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5373,7 +5373,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.099</v>
+        <v>0.11</v>
       </c>
       <c r="H88" s="17" t="n">
         <v>0.47</v>
@@ -5383,7 +5383,7 @@
         <v/>
       </c>
       <c r="J88" s="6" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="K88" s="20">
         <f>IF(I88&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5422,7 +5422,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.122</v>
+        <v>0.136</v>
       </c>
       <c r="H89" s="17" t="n">
         <v>0.4</v>
@@ -5432,7 +5432,7 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="K89" s="20">
         <f>IF(I89&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5471,7 +5471,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.122</v>
+        <v>0.136</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>0.4</v>
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J90" s="6" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="K90" s="20">
         <f>IF(I90&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5520,7 +5520,7 @@
         <v>0.51</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.08</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H91" s="17" t="n">
         <v>0.2</v>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="J91" s="6" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="K91" s="20">
         <f>IF(I91&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5569,7 +5569,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="H92" s="17" t="n">
         <v>0.5</v>
@@ -5579,7 +5579,7 @@
         <v/>
       </c>
       <c r="J92" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K92" s="20">
         <f>IF(I92&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5618,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.122</v>
+        <v>0.136</v>
       </c>
       <c r="H93" s="17" t="n">
         <v>0.5</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="K93" s="20">
         <f>IF(I93&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5667,7 +5667,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.123</v>
+        <v>0.137</v>
       </c>
       <c r="H94" s="17" t="n">
         <v>0.4</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="J94" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="K94" s="20">
         <f>IF(I94&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5716,7 +5716,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="H95" s="17" t="n">
         <v>0.3</v>
@@ -5726,7 +5726,7 @@
         <v/>
       </c>
       <c r="J95" s="6" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="K95" s="20">
         <f>IF(I95&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5765,7 +5765,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="H96" s="17" t="n">
         <v>0.36</v>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="K96" s="20">
         <f>IF(I96&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5814,7 +5814,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.058</v>
+        <v>0.064</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>0.36</v>
@@ -5824,7 +5824,7 @@
         <v/>
       </c>
       <c r="J97" s="6" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K97" s="20">
         <f>IF(I97&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5863,7 +5863,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.058</v>
+        <v>0.064</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>0.48</v>
@@ -5873,7 +5873,7 @@
         <v/>
       </c>
       <c r="J98" s="6" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K98" s="20">
         <f>IF(I98&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5912,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="H99" s="17" t="n">
         <v>0.49</v>
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="K99" s="20">
         <f>IF(I99&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5961,7 +5961,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="H100" s="17" t="n">
         <v>0.3</v>
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="J100" s="6" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="K100" s="20">
         <f>IF(I100&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -6010,7 +6010,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="H101" s="17" t="n">
         <v>0.37</v>
@@ -6020,7 +6020,7 @@
         <v/>
       </c>
       <c r="J101" s="6" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="K101" s="20">
         <f>IF(I101&gt;=0.05,"CUMPLE","NO CUMPLE")</f>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 467 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.110 m en EJE-11 P-48-P-33 (Q 26.4 l/s, y 0.090, h 0.20)</t>
+          <t>I = 467 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.064 m en EJE-12 P-60-D2 (Q 304.4 l/s, y 0.576, h 0.64)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>V max 1.82 m/s</t>
+          <t>V max 1.90 m/s</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.092</v>
+        <v>0.102</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>0.3</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K11" s="20">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1649,7 +1649,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.096</v>
+        <v>0.105</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>0.46</v>
@@ -1659,7 +1659,7 @@
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="K12" s="20">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1698,7 +1698,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.078</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>0.3</v>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="K13" s="20">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1747,7 +1747,7 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>0.46</v>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K14" s="20">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1796,7 +1796,7 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.092</v>
+        <v>0.101</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>0.46</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K15" s="20">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1845,7 +1845,7 @@
         <v>2.92</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.076</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>0.52</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="K16" s="20">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1894,7 +1894,7 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.285</v>
+        <v>0.319</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>0.77</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="K17" s="20">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1943,7 +1943,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.285</v>
+        <v>0.319</v>
       </c>
       <c r="H18" s="17" t="n">
         <v>0.83</v>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="K18" s="20">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1992,7 +1992,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.37</v>
+        <v>0.414</v>
       </c>
       <c r="H19" s="17" t="n">
         <v>0.83</v>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="K19" s="20">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2041,7 +2041,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.37</v>
+        <v>0.414</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>0.79</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="K20" s="20">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2090,7 +2090,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.418</v>
+        <v>0.469</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>0.79</v>
@@ -2100,7 +2100,7 @@
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="K21" s="20">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2139,7 +2139,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.073</v>
+        <v>0.08</v>
       </c>
       <c r="H22" s="17" t="n">
         <v>0.3</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="K22" s="20">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2188,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.092</v>
+        <v>0.101</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>0.3</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K23" s="20">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2237,7 +2237,7 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.099</v>
+        <v>0.109</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>0.43</v>
@@ -2247,7 +2247,7 @@
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="K24" s="20">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2286,7 +2286,7 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>0.47</v>
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="K25" s="20">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2335,7 +2335,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.124</v>
+        <v>0.138</v>
       </c>
       <c r="H26" s="17" t="n">
         <v>0.48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="K26" s="20">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2384,7 +2384,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.147</v>
+        <v>0.162</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>0.49</v>
@@ -2394,7 +2394,7 @@
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K27" s="20">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2433,7 +2433,7 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.156</v>
+        <v>0.172</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>0.57</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="K28" s="20">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.187</v>
+        <v>0.207</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>0.61</v>
@@ -2492,7 +2492,7 @@
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="K29" s="20">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2531,7 +2531,7 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.074</v>
+        <v>0.081</v>
       </c>
       <c r="H30" s="17" t="n">
         <v>0.3</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="K30" s="20">
         <f>IF(I30&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2580,7 +2580,7 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.08</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H31" s="17" t="n">
         <v>0.41</v>
@@ -2590,7 +2590,7 @@
         <v/>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K31" s="20">
         <f>IF(I31&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2629,7 +2629,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.097</v>
+        <v>0.106</v>
       </c>
       <c r="H32" s="17" t="n">
         <v>0.44</v>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="K32" s="20">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.102</v>
+        <v>0.112</v>
       </c>
       <c r="H33" s="17" t="n">
         <v>0.53</v>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K33" s="20">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2727,7 +2727,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.133</v>
+        <v>0.148</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>0.55</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="K34" s="20">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>0.3</v>
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="K35" s="20">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2825,7 +2825,7 @@
         <v>1.72</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="H36" s="17" t="n">
         <v>0.3</v>
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="K36" s="20">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2874,7 +2874,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.15</v>
+        <v>0.166</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>0.5</v>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K37" s="20">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,7 +2923,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.196</v>
+        <v>0.218</v>
       </c>
       <c r="H38" s="17" t="n">
         <v>0.59</v>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="K38" s="20">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2972,7 +2972,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.196</v>
+        <v>0.218</v>
       </c>
       <c r="H39" s="17" t="n">
         <v>0.61</v>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="K39" s="20">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3021,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.233</v>
+        <v>0.259</v>
       </c>
       <c r="H40" s="17" t="n">
         <v>0.62</v>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="K40" s="20">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3070,7 +3070,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.233</v>
+        <v>0.259</v>
       </c>
       <c r="H41" s="17" t="n">
         <v>0.73</v>
@@ -3080,7 +3080,7 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="K41" s="20">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3119,7 +3119,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.305</v>
+        <v>0.341</v>
       </c>
       <c r="H42" s="17" t="n">
         <v>0.73</v>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="K42" s="20">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3168,7 +3168,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.353</v>
+        <v>0.395</v>
       </c>
       <c r="H43" s="17" t="n">
         <v>0.79</v>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K43" s="20">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3217,7 +3217,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.353</v>
+        <v>0.395</v>
       </c>
       <c r="H44" s="17" t="n">
         <v>0.7</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K44" s="20">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3266,7 +3266,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.354</v>
+        <v>0.396</v>
       </c>
       <c r="H45" s="17" t="n">
         <v>0.7</v>
@@ -3276,7 +3276,7 @@
         <v/>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K45" s="20">
         <f>IF(I45&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3315,7 +3315,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.354</v>
+        <v>0.397</v>
       </c>
       <c r="H46" s="17" t="n">
         <v>0.74</v>
@@ -3325,7 +3325,7 @@
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K46" s="20">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3364,7 +3364,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0.356</v>
+        <v>0.399</v>
       </c>
       <c r="H47" s="17" t="n">
         <v>0.74</v>
@@ -3374,7 +3374,7 @@
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K47" s="20">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3413,7 +3413,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.356</v>
+        <v>0.399</v>
       </c>
       <c r="H48" s="17" t="n">
         <v>0.77</v>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K48" s="20">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.361</v>
+        <v>0.404</v>
       </c>
       <c r="H49" s="17" t="n">
         <v>0.77</v>
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K49" s="20">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3511,7 +3511,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0.362</v>
+        <v>0.406</v>
       </c>
       <c r="H50" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K50" s="20">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.362</v>
+        <v>0.406</v>
       </c>
       <c r="H51" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K51" s="20">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3609,7 +3609,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="H52" s="17" t="n">
         <v>0.3</v>
@@ -3619,7 +3619,7 @@
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="K52" s="20">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3658,7 +3658,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.095</v>
+        <v>0.105</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>0.32</v>
@@ -3668,7 +3668,7 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="K53" s="20">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3707,7 +3707,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="H54" s="17" t="n">
         <v>0.3</v>
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K54" s="20">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3756,7 +3756,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>0.3</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="K55" s="20">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3805,7 +3805,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.075</v>
+        <v>0.082</v>
       </c>
       <c r="H56" s="17" t="n">
         <v>0.39</v>
@@ -3815,7 +3815,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="K56" s="20">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3854,7 +3854,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.078</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H57" s="17" t="n">
         <v>0.42</v>
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="K57" s="20">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3903,7 +3903,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.101</v>
+        <v>0.111</v>
       </c>
       <c r="H58" s="17" t="n">
         <v>0.42</v>
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K58" s="20">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3952,7 +3952,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.101</v>
+        <v>0.111</v>
       </c>
       <c r="H59" s="17" t="n">
         <v>0.48</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K59" s="20">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4001,7 +4001,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.09</v>
+        <v>0.099</v>
       </c>
       <c r="H60" s="17" t="n">
         <v>0.2</v>
@@ -4011,7 +4011,7 @@
         <v/>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="K60" s="20">
         <f>IF(I60&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4050,7 +4050,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H61" s="17" t="n">
         <v>0.3</v>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="K61" s="20">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4099,7 +4099,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.066</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>0.38</v>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="K62" s="20">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4148,7 +4148,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.103</v>
+        <v>0.113</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>0.38</v>
@@ -4158,7 +4158,7 @@
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="K63" s="20">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4197,7 +4197,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.103</v>
+        <v>0.113</v>
       </c>
       <c r="H64" s="17" t="n">
         <v>0.49</v>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="K64" s="20">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4246,7 +4246,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.138</v>
+        <v>0.153</v>
       </c>
       <c r="H65" s="17" t="n">
         <v>0.5</v>
@@ -4256,7 +4256,7 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="K65" s="20">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4295,7 +4295,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H66" s="17" t="n">
         <v>0.52</v>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="K66" s="20">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4344,7 +4344,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.315</v>
+        <v>0.352</v>
       </c>
       <c r="H67" s="17" t="n">
         <v>0.5600000000000001</v>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K67" s="20">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4393,7 +4393,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.407</v>
+        <v>0.457</v>
       </c>
       <c r="H68" s="17" t="n">
         <v>0.62</v>
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="K68" s="20">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4442,7 +4442,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.43</v>
+        <v>0.483</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>0.57</v>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="K69" s="20">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4491,7 +4491,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.433</v>
+        <v>0.486</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>0.63</v>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="K70" s="20">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4540,7 +4540,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.433</v>
+        <v>0.486</v>
       </c>
       <c r="H71" s="17" t="n">
         <v>0.64</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="K71" s="20">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4589,7 +4589,7 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.512</v>
+        <v>0.576</v>
       </c>
       <c r="H72" s="17" t="n">
         <v>0.64</v>
@@ -4599,7 +4599,7 @@
         <v/>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="K72" s="20">
         <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4638,7 +4638,7 @@
         <v>0.5</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="H73" s="17" t="n">
         <v>0.3</v>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="K73" s="20">
         <f>IF(I73&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4687,7 +4687,7 @@
         <v>0.5</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="H74" s="17" t="n">
         <v>0.3</v>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="J74" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K74" s="20">
         <f>IF(I74&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4736,7 +4736,7 @@
         <v>0.5</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="H75" s="17" t="n">
         <v>0.38</v>
@@ -4746,7 +4746,7 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="K75" s="20">
         <f>IF(I75&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4785,7 +4785,7 @@
         <v>0.5</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.133</v>
+        <v>0.147</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>0.35</v>
@@ -4795,7 +4795,7 @@
         <v/>
       </c>
       <c r="J76" s="6" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="K76" s="20">
         <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4834,7 +4834,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.134</v>
+        <v>0.148</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>0.35</v>
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="K77" s="20">
         <f>IF(I77&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4883,7 +4883,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.136</v>
+        <v>0.15</v>
       </c>
       <c r="H78" s="17" t="n">
         <v>0.35</v>
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="J78" s="6" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="K78" s="20">
         <f>IF(I78&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4932,7 +4932,7 @@
         <v>0.5</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.176</v>
+        <v>0.196</v>
       </c>
       <c r="H79" s="17" t="n">
         <v>0.35</v>
@@ -4942,7 +4942,7 @@
         <v/>
       </c>
       <c r="J79" s="6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K79" s="20">
         <f>IF(I79&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4981,7 +4981,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.181</v>
+        <v>0.2</v>
       </c>
       <c r="H80" s="17" t="n">
         <v>0.45</v>
@@ -4991,7 +4991,7 @@
         <v/>
       </c>
       <c r="J80" s="6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="K80" s="20">
         <f>IF(I80&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5030,7 +5030,7 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.068</v>
+        <v>0.075</v>
       </c>
       <c r="H81" s="17" t="n">
         <v>0.3</v>
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J81" s="6" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="K81" s="20">
         <f>IF(I81&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5079,7 +5079,7 @@
         <v>0.5</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.068</v>
+        <v>0.075</v>
       </c>
       <c r="H82" s="17" t="n">
         <v>0.36</v>
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="J82" s="6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="K82" s="20">
         <f>IF(I82&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5128,7 +5128,7 @@
         <v>0.58</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.13</v>
+        <v>0.144</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>0.35</v>
@@ -5138,7 +5138,7 @@
         <v/>
       </c>
       <c r="J83" s="6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="K83" s="20">
         <f>IF(I83&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5177,7 +5177,7 @@
         <v>0.5</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.143</v>
+        <v>0.158</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>0.35</v>
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="J84" s="6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="K84" s="20">
         <f>IF(I84&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5226,7 +5226,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
       <c r="H85" s="17" t="n">
         <v>0.3</v>
@@ -5236,7 +5236,7 @@
         <v/>
       </c>
       <c r="J85" s="6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="K85" s="20">
         <f>IF(I85&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5275,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.107</v>
+        <v>0.119</v>
       </c>
       <c r="H86" s="17" t="n">
         <v>0.45</v>
@@ -5285,7 +5285,7 @@
         <v/>
       </c>
       <c r="J86" s="6" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="K86" s="20">
         <f>IF(I86&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5324,7 +5324,7 @@
         <v>0.5</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.11</v>
+        <v>0.121</v>
       </c>
       <c r="H87" s="17" t="n">
         <v>0.46</v>
@@ -5334,7 +5334,7 @@
         <v/>
       </c>
       <c r="J87" s="6" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="K87" s="20">
         <f>IF(I87&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5373,7 +5373,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.11</v>
+        <v>0.121</v>
       </c>
       <c r="H88" s="17" t="n">
         <v>0.47</v>
@@ -5383,7 +5383,7 @@
         <v/>
       </c>
       <c r="J88" s="6" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="K88" s="20">
         <f>IF(I88&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5422,7 +5422,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.136</v>
+        <v>0.15</v>
       </c>
       <c r="H89" s="17" t="n">
         <v>0.4</v>
@@ -5432,7 +5432,7 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="K89" s="20">
         <f>IF(I89&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5471,7 +5471,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.136</v>
+        <v>0.15</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>0.4</v>
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J90" s="6" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="K90" s="20">
         <f>IF(I90&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5520,7 +5520,7 @@
         <v>0.51</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="H91" s="17" t="n">
         <v>0.2</v>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="J91" s="6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="K91" s="20">
         <f>IF(I91&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5569,7 +5569,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="H92" s="17" t="n">
         <v>0.5</v>
@@ -5579,7 +5579,7 @@
         <v/>
       </c>
       <c r="J92" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="K92" s="20">
         <f>IF(I92&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5618,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.136</v>
+        <v>0.151</v>
       </c>
       <c r="H93" s="17" t="n">
         <v>0.5</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="K93" s="20">
         <f>IF(I93&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5667,7 +5667,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.137</v>
+        <v>0.151</v>
       </c>
       <c r="H94" s="17" t="n">
         <v>0.4</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="J94" s="6" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="K94" s="20">
         <f>IF(I94&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5716,7 +5716,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="H95" s="17" t="n">
         <v>0.3</v>
@@ -5726,7 +5726,7 @@
         <v/>
       </c>
       <c r="J95" s="6" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K95" s="20">
         <f>IF(I95&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5765,7 +5765,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="H96" s="17" t="n">
         <v>0.36</v>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K96" s="20">
         <f>IF(I96&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5814,7 +5814,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.064</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>0.36</v>
@@ -5824,7 +5824,7 @@
         <v/>
       </c>
       <c r="J97" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="K97" s="20">
         <f>IF(I97&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5863,7 +5863,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.064</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>0.48</v>
@@ -5873,7 +5873,7 @@
         <v/>
       </c>
       <c r="J98" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="K98" s="20">
         <f>IF(I98&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5912,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.079</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H99" s="17" t="n">
         <v>0.49</v>
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="K99" s="20">
         <f>IF(I99&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5961,7 +5961,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="H100" s="17" t="n">
         <v>0.3</v>
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="J100" s="6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="K100" s="20">
         <f>IF(I100&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -6010,7 +6010,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="H101" s="17" t="n">
         <v>0.37</v>
@@ -6020,7 +6020,7 @@
         <v/>
       </c>
       <c r="J101" s="6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="K101" s="20">
         <f>IF(I101&gt;=0.05,"CUMPLE","NO CUMPLE")</f>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 467 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.064 m en EJE-12 P-60-D2 (Q 304.4 l/s, y 0.576, h 0.64)</t>
+          <t>I = 289 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.129 m en EJE-11 P-48-P-33 (Q 18.8 l/s, y 0.071, h 0.20)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>V max 1.90 m/s</t>
+          <t>V max 1.62 m/s</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>467</v>
+        <v>288.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>P max 24 h transpuesta (mm)</t>
+          <t>P max 24 h, T = 25 anos, Pongo de Caynarachi (mm)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>269.62</v>
+        <v>166.64</v>
       </c>
     </row>
     <row r="7">
@@ -1502,7 +1502,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>I: tc = 10 min, TR = 25 anos, P10 = 77.83 mm (estacion usada en el Hogar de Refugio - Morales); reemplazar por la del proyecto. Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
+          <t>I: tc = 10 min, TR = 25 anos, P10 = 48.11 mm (estacion Pongo de Caynarachi, SENAMHI 003317, 1989-2013; Dick y Peschke). Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.102</v>
+        <v>0.073</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>0.3</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="K11" s="20">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1649,7 +1649,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.105</v>
+        <v>0.076</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>0.46</v>
@@ -1659,7 +1659,7 @@
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="K12" s="20">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1698,7 +1698,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>0.3</v>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="K13" s="20">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1747,7 +1747,7 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.089</v>
+        <v>0.065</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>0.46</v>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K14" s="20">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1796,7 +1796,7 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.101</v>
+        <v>0.073</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>0.46</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="K15" s="20">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1845,7 +1845,7 @@
         <v>2.92</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.061</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>0.52</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="K16" s="20">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1894,7 +1894,7 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.319</v>
+        <v>0.219</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>0.77</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="K17" s="20">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1943,7 +1943,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.319</v>
+        <v>0.219</v>
       </c>
       <c r="H18" s="17" t="n">
         <v>0.83</v>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="K18" s="20">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1992,7 +1992,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.414</v>
+        <v>0.282</v>
       </c>
       <c r="H19" s="17" t="n">
         <v>0.83</v>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="K19" s="20">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2041,7 +2041,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.414</v>
+        <v>0.282</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>0.79</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="K20" s="20">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2090,7 +2090,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.469</v>
+        <v>0.317</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>0.79</v>
@@ -2100,7 +2100,7 @@
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="K21" s="20">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2139,7 +2139,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.08</v>
+        <v>0.058</v>
       </c>
       <c r="H22" s="17" t="n">
         <v>0.3</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="K22" s="20">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2188,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.101</v>
+        <v>0.073</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>0.3</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="K23" s="20">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2237,7 +2237,7 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.109</v>
+        <v>0.078</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>0.43</v>
@@ -2247,7 +2247,7 @@
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
       <c r="K24" s="20">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2286,7 +2286,7 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.11</v>
+        <v>0.079</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>0.47</v>
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="K25" s="20">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2335,7 +2335,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.138</v>
+        <v>0.098</v>
       </c>
       <c r="H26" s="17" t="n">
         <v>0.48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="K26" s="20">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2384,7 +2384,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.162</v>
+        <v>0.115</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>0.49</v>
@@ -2394,7 +2394,7 @@
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="K27" s="20">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2433,7 +2433,7 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.172</v>
+        <v>0.122</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>0.57</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="K28" s="20">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.207</v>
+        <v>0.145</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>0.61</v>
@@ -2492,7 +2492,7 @@
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="K29" s="20">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2531,7 +2531,7 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.081</v>
+        <v>0.059</v>
       </c>
       <c r="H30" s="17" t="n">
         <v>0.3</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="K30" s="20">
         <f>IF(I30&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2580,7 +2580,7 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="H31" s="17" t="n">
         <v>0.41</v>
@@ -2590,7 +2590,7 @@
         <v/>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K31" s="20">
         <f>IF(I31&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2629,7 +2629,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.106</v>
+        <v>0.077</v>
       </c>
       <c r="H32" s="17" t="n">
         <v>0.44</v>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="K32" s="20">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.112</v>
+        <v>0.081</v>
       </c>
       <c r="H33" s="17" t="n">
         <v>0.53</v>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="K33" s="20">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2727,7 +2727,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.148</v>
+        <v>0.105</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>0.55</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="K34" s="20">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.052</v>
+        <v>0.038</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>0.3</v>
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="K35" s="20">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2825,7 +2825,7 @@
         <v>1.72</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="H36" s="17" t="n">
         <v>0.3</v>
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.93</v>
+        <v>0.78</v>
       </c>
       <c r="K36" s="20">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2874,7 +2874,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.166</v>
+        <v>0.118</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>0.5</v>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="K37" s="20">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,7 +2923,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.218</v>
+        <v>0.153</v>
       </c>
       <c r="H38" s="17" t="n">
         <v>0.59</v>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="K38" s="20">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2972,7 +2972,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.218</v>
+        <v>0.153</v>
       </c>
       <c r="H39" s="17" t="n">
         <v>0.61</v>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="K39" s="20">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3021,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.259</v>
+        <v>0.18</v>
       </c>
       <c r="H40" s="17" t="n">
         <v>0.62</v>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="K40" s="20">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3070,7 +3070,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.259</v>
+        <v>0.18</v>
       </c>
       <c r="H41" s="17" t="n">
         <v>0.73</v>
@@ -3080,7 +3080,7 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="K41" s="20">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3119,7 +3119,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.341</v>
+        <v>0.234</v>
       </c>
       <c r="H42" s="17" t="n">
         <v>0.73</v>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="K42" s="20">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3168,7 +3168,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.395</v>
+        <v>0.269</v>
       </c>
       <c r="H43" s="17" t="n">
         <v>0.79</v>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="K43" s="20">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3217,7 +3217,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.395</v>
+        <v>0.269</v>
       </c>
       <c r="H44" s="17" t="n">
         <v>0.7</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="K44" s="20">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3266,7 +3266,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.396</v>
+        <v>0.27</v>
       </c>
       <c r="H45" s="17" t="n">
         <v>0.7</v>
@@ -3276,7 +3276,7 @@
         <v/>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="K45" s="20">
         <f>IF(I45&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3315,7 +3315,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.397</v>
+        <v>0.27</v>
       </c>
       <c r="H46" s="17" t="n">
         <v>0.74</v>
@@ -3325,7 +3325,7 @@
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="K46" s="20">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3364,7 +3364,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0.399</v>
+        <v>0.272</v>
       </c>
       <c r="H47" s="17" t="n">
         <v>0.74</v>
@@ -3374,7 +3374,7 @@
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="K47" s="20">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3413,7 +3413,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.399</v>
+        <v>0.272</v>
       </c>
       <c r="H48" s="17" t="n">
         <v>0.77</v>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="K48" s="20">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.404</v>
+        <v>0.275</v>
       </c>
       <c r="H49" s="17" t="n">
         <v>0.77</v>
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="K49" s="20">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3511,7 +3511,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0.406</v>
+        <v>0.276</v>
       </c>
       <c r="H50" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="K50" s="20">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.406</v>
+        <v>0.276</v>
       </c>
       <c r="H51" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="K51" s="20">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3609,7 +3609,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="H52" s="17" t="n">
         <v>0.3</v>
@@ -3619,7 +3619,7 @@
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="K52" s="20">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3658,7 +3658,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.105</v>
+        <v>0.075</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>0.32</v>
@@ -3668,7 +3668,7 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="K53" s="20">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3707,7 +3707,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.089</v>
+        <v>0.064</v>
       </c>
       <c r="H54" s="17" t="n">
         <v>0.3</v>
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K54" s="20">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3756,7 +3756,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>0.3</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="K55" s="20">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3805,7 +3805,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.082</v>
+        <v>0.06</v>
       </c>
       <c r="H56" s="17" t="n">
         <v>0.39</v>
@@ -3815,7 +3815,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="K56" s="20">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3854,7 +3854,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="H57" s="17" t="n">
         <v>0.42</v>
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="K57" s="20">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3903,7 +3903,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.111</v>
+        <v>0.08</v>
       </c>
       <c r="H58" s="17" t="n">
         <v>0.42</v>
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="K58" s="20">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3952,7 +3952,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.111</v>
+        <v>0.08</v>
       </c>
       <c r="H59" s="17" t="n">
         <v>0.48</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="K59" s="20">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4001,7 +4001,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.099</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H60" s="17" t="n">
         <v>0.2</v>
@@ -4011,7 +4011,7 @@
         <v/>
       </c>
       <c r="J60" s="6" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="K60" s="20">
         <f>IF(I60&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4050,7 +4050,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="H61" s="17" t="n">
         <v>0.3</v>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="K61" s="20">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4099,7 +4099,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>0.38</v>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="K62" s="20">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4148,7 +4148,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>0.38</v>
@@ -4158,7 +4158,7 @@
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="K63" s="20">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4197,7 +4197,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="H64" s="17" t="n">
         <v>0.49</v>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="K64" s="20">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4246,7 +4246,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.153</v>
+        <v>0.108</v>
       </c>
       <c r="H65" s="17" t="n">
         <v>0.5</v>
@@ -4256,7 +4256,7 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="K65" s="20">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4295,7 +4295,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H66" s="17" t="n">
         <v>0.52</v>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="K66" s="20">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4344,7 +4344,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.352</v>
+        <v>0.241</v>
       </c>
       <c r="H67" s="17" t="n">
         <v>0.5600000000000001</v>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="K67" s="20">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4393,7 +4393,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.457</v>
+        <v>0.309</v>
       </c>
       <c r="H68" s="17" t="n">
         <v>0.62</v>
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="K68" s="20">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4442,7 +4442,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.483</v>
+        <v>0.326</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>0.57</v>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="K69" s="20">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4491,7 +4491,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.486</v>
+        <v>0.328</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>0.63</v>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="K70" s="20">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4540,7 +4540,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.486</v>
+        <v>0.328</v>
       </c>
       <c r="H71" s="17" t="n">
         <v>0.64</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="K71" s="20">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4589,7 +4589,7 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.576</v>
+        <v>0.385</v>
       </c>
       <c r="H72" s="17" t="n">
         <v>0.64</v>
@@ -4599,7 +4599,7 @@
         <v/>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="K72" s="20">
         <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4638,7 +4638,7 @@
         <v>0.5</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.078</v>
+        <v>0.057</v>
       </c>
       <c r="H73" s="17" t="n">
         <v>0.3</v>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="K73" s="20">
         <f>IF(I73&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4687,7 +4687,7 @@
         <v>0.5</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.089</v>
+        <v>0.064</v>
       </c>
       <c r="H74" s="17" t="n">
         <v>0.3</v>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="J74" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K74" s="20">
         <f>IF(I74&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4736,7 +4736,7 @@
         <v>0.5</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.092</v>
+        <v>0.066</v>
       </c>
       <c r="H75" s="17" t="n">
         <v>0.38</v>
@@ -4746,7 +4746,7 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="K75" s="20">
         <f>IF(I75&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4785,7 +4785,7 @@
         <v>0.5</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.147</v>
+        <v>0.105</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>0.35</v>
@@ -4795,7 +4795,7 @@
         <v/>
       </c>
       <c r="J76" s="6" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="K76" s="20">
         <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4834,7 +4834,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.148</v>
+        <v>0.105</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>0.35</v>
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="K77" s="20">
         <f>IF(I77&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4883,7 +4883,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.15</v>
+        <v>0.107</v>
       </c>
       <c r="H78" s="17" t="n">
         <v>0.35</v>
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="J78" s="6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="K78" s="20">
         <f>IF(I78&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4932,7 +4932,7 @@
         <v>0.5</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.196</v>
+        <v>0.138</v>
       </c>
       <c r="H79" s="17" t="n">
         <v>0.35</v>
@@ -4942,7 +4942,7 @@
         <v/>
       </c>
       <c r="J79" s="6" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="K79" s="20">
         <f>IF(I79&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4981,7 +4981,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.2</v>
+        <v>0.141</v>
       </c>
       <c r="H80" s="17" t="n">
         <v>0.45</v>
@@ -4991,7 +4991,7 @@
         <v/>
       </c>
       <c r="J80" s="6" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="K80" s="20">
         <f>IF(I80&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5030,7 +5030,7 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.075</v>
+        <v>0.054</v>
       </c>
       <c r="H81" s="17" t="n">
         <v>0.3</v>
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J81" s="6" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="K81" s="20">
         <f>IF(I81&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5079,7 +5079,7 @@
         <v>0.5</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="H82" s="17" t="n">
         <v>0.36</v>
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="J82" s="6" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="K82" s="20">
         <f>IF(I82&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5128,7 +5128,7 @@
         <v>0.58</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.144</v>
+        <v>0.102</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>0.35</v>
@@ -5138,7 +5138,7 @@
         <v/>
       </c>
       <c r="J83" s="6" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="K83" s="20">
         <f>IF(I83&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5177,7 +5177,7 @@
         <v>0.5</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.158</v>
+        <v>0.112</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>0.35</v>
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="J84" s="6" t="n">
-        <v>1.04</v>
+        <v>0.9</v>
       </c>
       <c r="K84" s="20">
         <f>IF(I84&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5226,7 +5226,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="H85" s="17" t="n">
         <v>0.3</v>
@@ -5236,7 +5236,7 @@
         <v/>
       </c>
       <c r="J85" s="6" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="K85" s="20">
         <f>IF(I85&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5275,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.119</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H86" s="17" t="n">
         <v>0.45</v>
@@ -5285,7 +5285,7 @@
         <v/>
       </c>
       <c r="J86" s="6" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="K86" s="20">
         <f>IF(I86&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5324,7 +5324,7 @@
         <v>0.5</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.121</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H87" s="17" t="n">
         <v>0.46</v>
@@ -5334,7 +5334,7 @@
         <v/>
       </c>
       <c r="J87" s="6" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="K87" s="20">
         <f>IF(I87&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5373,7 +5373,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.121</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H88" s="17" t="n">
         <v>0.47</v>
@@ -5383,7 +5383,7 @@
         <v/>
       </c>
       <c r="J88" s="6" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="K88" s="20">
         <f>IF(I88&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5422,7 +5422,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.15</v>
+        <v>0.107</v>
       </c>
       <c r="H89" s="17" t="n">
         <v>0.4</v>
@@ -5432,7 +5432,7 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="K89" s="20">
         <f>IF(I89&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5471,7 +5471,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.15</v>
+        <v>0.107</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>0.4</v>
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J90" s="6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="K90" s="20">
         <f>IF(I90&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5520,7 +5520,7 @@
         <v>0.51</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.097</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H91" s="17" t="n">
         <v>0.2</v>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="J91" s="6" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="K91" s="20">
         <f>IF(I91&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5569,7 +5569,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="18" t="n">
-        <v>0.098</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H92" s="17" t="n">
         <v>0.5</v>
@@ -5579,7 +5579,7 @@
         <v/>
       </c>
       <c r="J92" s="6" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="K92" s="20">
         <f>IF(I92&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5618,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.151</v>
+        <v>0.107</v>
       </c>
       <c r="H93" s="17" t="n">
         <v>0.5</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="K93" s="20">
         <f>IF(I93&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5667,7 +5667,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.151</v>
+        <v>0.108</v>
       </c>
       <c r="H94" s="17" t="n">
         <v>0.4</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="J94" s="6" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="K94" s="20">
         <f>IF(I94&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5716,7 +5716,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.044</v>
+        <v>0.032</v>
       </c>
       <c r="H95" s="17" t="n">
         <v>0.3</v>
@@ -5726,7 +5726,7 @@
         <v/>
       </c>
       <c r="J95" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="K95" s="20">
         <f>IF(I95&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5765,7 +5765,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.044</v>
+        <v>0.032</v>
       </c>
       <c r="H96" s="17" t="n">
         <v>0.36</v>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="K96" s="20">
         <f>IF(I96&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5814,7 +5814,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>0.36</v>
@@ -5824,7 +5824,7 @@
         <v/>
       </c>
       <c r="J97" s="6" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="K97" s="20">
         <f>IF(I97&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5863,7 +5863,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>0.48</v>
@@ -5873,7 +5873,7 @@
         <v/>
       </c>
       <c r="J98" s="6" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="K98" s="20">
         <f>IF(I98&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5912,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="H99" s="17" t="n">
         <v>0.49</v>
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="K99" s="20">
         <f>IF(I99&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5961,7 +5961,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="H100" s="17" t="n">
         <v>0.3</v>
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="J100" s="6" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="K100" s="20">
         <f>IF(I100&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -6010,7 +6010,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="H101" s="17" t="n">
         <v>0.37</v>
@@ -6020,7 +6020,7 @@
         <v/>
       </c>
       <c r="J101" s="6" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="K101" s="20">
         <f>IF(I101&gt;=0.05,"CUMPLE","NO CUMPLE")</f>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 289 mm/h, C ponderado = 0.57, area total 9393 m2; menor borde libre 0.129 m en EJE-11 P-48-P-33 (Q 18.8 l/s, y 0.071, h 0.20)</t>
+          <t>I = 289 mm/h, C ponderado = 0.76, area total 9393 m2; menor borde libre 0.129 m en EJE-11 P-48-P-33 (Q 18.8 l/s, y 0.071, h 0.20)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>V max 1.62 m/s</t>
+          <t>V max 1.97 m/s</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.57</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="5">
@@ -1600,7 +1600,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.073</v>
+        <v>0.094</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>0.3</v>
@@ -1610,7 +1610,7 @@
         <v/>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="K11" s="20">
         <f>IF(I11&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1649,7 +1649,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.076</v>
+        <v>0.096</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>0.46</v>
@@ -1659,7 +1659,7 @@
         <v/>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="K12" s="20">
         <f>IF(I12&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1698,7 +1698,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.062</v>
+        <v>0.083</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>0.3</v>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="K13" s="20">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1747,7 +1747,7 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.065</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>0.46</v>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="K14" s="20">
         <f>IF(I14&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1796,7 +1796,7 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.073</v>
+        <v>0.103</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>0.46</v>
@@ -1806,7 +1806,7 @@
         <v/>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="K15" s="20">
         <f>IF(I15&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1845,7 +1845,7 @@
         <v>2.92</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.061</v>
+        <v>0.09</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>0.52</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="K16" s="20">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1894,7 +1894,7 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.219</v>
+        <v>0.314</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>0.77</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="J17" s="6" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="K17" s="20">
         <f>IF(I17&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1943,7 +1943,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.219</v>
+        <v>0.314</v>
       </c>
       <c r="H18" s="17" t="n">
         <v>0.83</v>
@@ -1953,7 +1953,7 @@
         <v/>
       </c>
       <c r="J18" s="6" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="K18" s="20">
         <f>IF(I18&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1992,7 +1992,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.282</v>
+        <v>0.399</v>
       </c>
       <c r="H19" s="17" t="n">
         <v>0.83</v>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="K19" s="20">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2041,7 +2041,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.282</v>
+        <v>0.399</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>0.79</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="K20" s="20">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2090,7 +2090,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.317</v>
+        <v>0.448</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>0.79</v>
@@ -2100,7 +2100,7 @@
         <v/>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="K21" s="20">
         <f>IF(I21&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2139,7 +2139,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.058</v>
+        <v>0.091</v>
       </c>
       <c r="H22" s="17" t="n">
         <v>0.3</v>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="K22" s="20">
         <f>IF(I22&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2188,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.073</v>
+        <v>0.077</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>0.3</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K23" s="20">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2237,7 +2237,7 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0.078</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H24" s="17" t="n">
         <v>0.43</v>
@@ -2247,7 +2247,7 @@
         <v/>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="K24" s="20">
         <f>IF(I24&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2286,7 +2286,7 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.079</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>0.47</v>
@@ -2296,7 +2296,7 @@
         <v/>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="K25" s="20">
         <f>IF(I25&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2335,7 +2335,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.098</v>
+        <v>0.104</v>
       </c>
       <c r="H26" s="17" t="n">
         <v>0.48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="K26" s="20">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2384,7 +2384,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.115</v>
+        <v>0.129</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>0.49</v>
@@ -2394,7 +2394,7 @@
         <v/>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="K27" s="20">
         <f>IF(I27&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2433,7 +2433,7 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.122</v>
+        <v>0.139</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>0.57</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="K28" s="20">
         <f>IF(I28&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.145</v>
+        <v>0.186</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>0.61</v>
@@ -2492,7 +2492,7 @@
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K29" s="20">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2629,7 +2629,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.077</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H32" s="17" t="n">
         <v>0.44</v>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K32" s="20">
         <f>IF(I32&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.081</v>
+        <v>0.093</v>
       </c>
       <c r="H33" s="17" t="n">
         <v>0.53</v>
@@ -2688,7 +2688,7 @@
         <v/>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="K33" s="20">
         <f>IF(I33&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2727,7 +2727,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.105</v>
+        <v>0.135</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>0.55</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="K34" s="20">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2825,7 +2825,7 @@
         <v>1.72</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="H36" s="17" t="n">
         <v>0.3</v>
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="K36" s="20">
         <f>IF(I36&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2874,7 +2874,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.118</v>
+        <v>0.165</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>0.5</v>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>0.92</v>
+        <v>1.05</v>
       </c>
       <c r="K37" s="20">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,7 +2923,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.153</v>
+        <v>0.219</v>
       </c>
       <c r="H38" s="17" t="n">
         <v>0.59</v>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="K38" s="20">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2972,7 +2972,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.153</v>
+        <v>0.219</v>
       </c>
       <c r="H39" s="17" t="n">
         <v>0.61</v>
@@ -2982,7 +2982,7 @@
         <v/>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="K39" s="20">
         <f>IF(I39&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3021,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.18</v>
+        <v>0.246</v>
       </c>
       <c r="H40" s="17" t="n">
         <v>0.62</v>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="K40" s="20">
         <f>IF(I40&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3070,7 +3070,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.18</v>
+        <v>0.246</v>
       </c>
       <c r="H41" s="17" t="n">
         <v>0.73</v>
@@ -3080,7 +3080,7 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="K41" s="20">
         <f>IF(I41&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3119,7 +3119,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.234</v>
+        <v>0.304</v>
       </c>
       <c r="H42" s="17" t="n">
         <v>0.73</v>
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="K42" s="20">
         <f>IF(I42&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3168,7 +3168,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.269</v>
+        <v>0.338</v>
       </c>
       <c r="H43" s="17" t="n">
         <v>0.79</v>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="K43" s="20">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3217,7 +3217,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.269</v>
+        <v>0.338</v>
       </c>
       <c r="H44" s="17" t="n">
         <v>0.7</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="K44" s="20">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3266,7 +3266,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.27</v>
+        <v>0.338</v>
       </c>
       <c r="H45" s="17" t="n">
         <v>0.7</v>
@@ -3276,7 +3276,7 @@
         <v/>
       </c>
       <c r="J45" s="6" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="K45" s="20">
         <f>IF(I45&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3315,7 +3315,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.27</v>
+        <v>0.339</v>
       </c>
       <c r="H46" s="17" t="n">
         <v>0.74</v>
@@ -3325,7 +3325,7 @@
         <v/>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="K46" s="20">
         <f>IF(I46&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3364,7 +3364,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0.272</v>
+        <v>0.34</v>
       </c>
       <c r="H47" s="17" t="n">
         <v>0.74</v>
@@ -3374,7 +3374,7 @@
         <v/>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K47" s="20">
         <f>IF(I47&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3413,7 +3413,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.272</v>
+        <v>0.34</v>
       </c>
       <c r="H48" s="17" t="n">
         <v>0.77</v>
@@ -3423,7 +3423,7 @@
         <v/>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K48" s="20">
         <f>IF(I48&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.275</v>
+        <v>0.343</v>
       </c>
       <c r="H49" s="17" t="n">
         <v>0.77</v>
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K49" s="20">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3511,7 +3511,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0.276</v>
+        <v>0.344</v>
       </c>
       <c r="H50" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K50" s="20">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.276</v>
+        <v>0.344</v>
       </c>
       <c r="H51" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="K51" s="20">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3609,7 +3609,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="H52" s="17" t="n">
         <v>0.3</v>
@@ -3619,7 +3619,7 @@
         <v/>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="K52" s="20">
         <f>IF(I52&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3658,7 +3658,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.075</v>
+        <v>0.119</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>0.32</v>
@@ -3668,7 +3668,7 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="K53" s="20">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3707,7 +3707,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.064</v>
+        <v>0.093</v>
       </c>
       <c r="H54" s="17" t="n">
         <v>0.3</v>
@@ -3717,7 +3717,7 @@
         <v/>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="K54" s="20">
         <f>IF(I54&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3756,7 +3756,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.055</v>
+        <v>0.063</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>0.3</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K55" s="20">
         <f>IF(I55&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3805,7 +3805,7 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0.06</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H56" s="17" t="n">
         <v>0.39</v>
@@ -3815,7 +3815,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="K56" s="20">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3854,7 +3854,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.062</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H57" s="17" t="n">
         <v>0.42</v>
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="K57" s="20">
         <f>IF(I57&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3903,7 +3903,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="H58" s="17" t="n">
         <v>0.42</v>
@@ -3913,7 +3913,7 @@
         <v/>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K58" s="20">
         <f>IF(I58&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3952,7 +3952,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="H59" s="17" t="n">
         <v>0.48</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K59" s="20">
         <f>IF(I59&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4050,7 +4050,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.051</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H61" s="17" t="n">
         <v>0.3</v>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="K61" s="20">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4099,7 +4099,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.053</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>0.38</v>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="K62" s="20">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4148,7 +4148,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.081</v>
+        <v>0.111</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>0.38</v>
@@ -4158,7 +4158,7 @@
         <v/>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="K63" s="20">
         <f>IF(I63&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4197,7 +4197,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.081</v>
+        <v>0.111</v>
       </c>
       <c r="H64" s="17" t="n">
         <v>0.49</v>
@@ -4207,7 +4207,7 @@
         <v/>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="K64" s="20">
         <f>IF(I64&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4246,7 +4246,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.108</v>
+        <v>0.161</v>
       </c>
       <c r="H65" s="17" t="n">
         <v>0.5</v>
@@ -4256,7 +4256,7 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>0.89</v>
+        <v>1.04</v>
       </c>
       <c r="K65" s="20">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4295,7 +4295,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.14</v>
+        <v>0.202</v>
       </c>
       <c r="H66" s="17" t="n">
         <v>0.52</v>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="K66" s="20">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4344,7 +4344,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.241</v>
+        <v>0.306</v>
       </c>
       <c r="H67" s="17" t="n">
         <v>0.5600000000000001</v>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="K67" s="20">
         <f>IF(I67&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4393,7 +4393,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.309</v>
+        <v>0.372</v>
       </c>
       <c r="H68" s="17" t="n">
         <v>0.62</v>
@@ -4403,7 +4403,7 @@
         <v/>
       </c>
       <c r="J68" s="6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="K68" s="20">
         <f>IF(I68&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4442,7 +4442,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.326</v>
+        <v>0.389</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>0.57</v>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="K69" s="20">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4491,7 +4491,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.328</v>
+        <v>0.39</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>0.63</v>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="K70" s="20">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4540,7 +4540,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.328</v>
+        <v>0.39</v>
       </c>
       <c r="H71" s="17" t="n">
         <v>0.64</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="K71" s="20">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4589,7 +4589,7 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.385</v>
+        <v>0.447</v>
       </c>
       <c r="H72" s="17" t="n">
         <v>0.64</v>
@@ -4599,7 +4599,7 @@
         <v/>
       </c>
       <c r="J72" s="6" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="K72" s="20">
         <f>IF(I72&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4638,7 +4638,7 @@
         <v>0.5</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>0.057</v>
+        <v>0.074</v>
       </c>
       <c r="H73" s="17" t="n">
         <v>0.3</v>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="J73" s="6" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="K73" s="20">
         <f>IF(I73&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4736,7 +4736,7 @@
         <v>0.5</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.066</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H75" s="17" t="n">
         <v>0.38</v>
@@ -4746,7 +4746,7 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="K75" s="20">
         <f>IF(I75&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4785,7 +4785,7 @@
         <v>0.5</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.105</v>
+        <v>0.116</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>0.35</v>
@@ -4795,7 +4795,7 @@
         <v/>
       </c>
       <c r="J76" s="6" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="K76" s="20">
         <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4834,7 +4834,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.105</v>
+        <v>0.116</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>0.35</v>
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="K77" s="20">
         <f>IF(I77&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4883,7 +4883,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.107</v>
+        <v>0.117</v>
       </c>
       <c r="H78" s="17" t="n">
         <v>0.35</v>
@@ -4893,7 +4893,7 @@
         <v/>
       </c>
       <c r="J78" s="6" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="K78" s="20">
         <f>IF(I78&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4932,7 +4932,7 @@
         <v>0.5</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.138</v>
+        <v>0.147</v>
       </c>
       <c r="H79" s="17" t="n">
         <v>0.35</v>
@@ -4942,7 +4942,7 @@
         <v/>
       </c>
       <c r="J79" s="6" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="K79" s="20">
         <f>IF(I79&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4981,7 +4981,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.141</v>
+        <v>0.151</v>
       </c>
       <c r="H80" s="17" t="n">
         <v>0.45</v>
@@ -4991,7 +4991,7 @@
         <v/>
       </c>
       <c r="J80" s="6" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="K80" s="20">
         <f>IF(I80&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5618,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.107</v>
+        <v>0.129</v>
       </c>
       <c r="H93" s="17" t="n">
         <v>0.5</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="K93" s="20">
         <f>IF(I93&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5667,7 +5667,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.108</v>
+        <v>0.129</v>
       </c>
       <c r="H94" s="17" t="n">
         <v>0.4</v>
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="J94" s="6" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="K94" s="20">
         <f>IF(I94&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5716,7 +5716,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="18" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="H95" s="17" t="n">
         <v>0.3</v>
@@ -5726,7 +5726,7 @@
         <v/>
       </c>
       <c r="J95" s="6" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="K95" s="20">
         <f>IF(I95&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5765,7 +5765,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="H96" s="17" t="n">
         <v>0.36</v>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="K96" s="20">
         <f>IF(I96&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5814,7 +5814,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.051</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>0.36</v>
@@ -5824,7 +5824,7 @@
         <v/>
       </c>
       <c r="J97" s="6" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="K97" s="20">
         <f>IF(I97&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5863,7 +5863,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.051</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>0.48</v>
@@ -5873,7 +5873,7 @@
         <v/>
       </c>
       <c r="J98" s="6" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="K98" s="20">
         <f>IF(I98&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5912,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.063</v>
+        <v>0.089</v>
       </c>
       <c r="H99" s="17" t="n">
         <v>0.49</v>
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K99" s="20">
         <f>IF(I99&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5961,7 +5961,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="18" t="n">
-        <v>0.026</v>
+        <v>0.038</v>
       </c>
       <c r="H100" s="17" t="n">
         <v>0.3</v>
@@ -5971,7 +5971,7 @@
         <v/>
       </c>
       <c r="J100" s="6" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="K100" s="20">
         <f>IF(I100&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -6010,7 +6010,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="18" t="n">
-        <v>0.026</v>
+        <v>0.038</v>
       </c>
       <c r="H101" s="17" t="n">
         <v>0.37</v>
@@ -6020,7 +6020,7 @@
         <v/>
       </c>
       <c r="J101" s="6" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="K101" s="20">
         <f>IF(I101&gt;=0.05,"CUMPLE","NO CUMPLE")</f>

--- a/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/CUADRO_TRAMOS_CUNETAS_IE0590_BARRANQUITA.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>I = 289 mm/h, C ponderado = 0.76, area total 9393 m2; menor borde libre 0.129 m en EJE-11 P-48-P-33 (Q 18.8 l/s, y 0.071, h 0.20)</t>
+          <t>I = 293 mm/h, C ponderado = 0.76, area total 9393 m2; menor borde libre 0.128 m en EJE-11 P-48-P-33 (Q 19.1 l/s, y 0.072, h 0.20)</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>V max 1.97 m/s</t>
+          <t>V max 1.98 m/s</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>288.63</v>
+        <v>293.18</v>
       </c>
     </row>
     <row r="6">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>166.64</v>
+        <v>169.27</v>
       </c>
     </row>
     <row r="7">
@@ -1502,7 +1502,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>I: tc = 10 min, TR = 25 anos, P10 = 48.11 mm (estacion Pongo de Caynarachi, SENAMHI 003317, 1989-2013; Dick y Peschke). Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
+          <t>I: tc = 10 min, TR = 25 anos, P10 = 48.86 mm (estacion Pongo de Caynarachi, SENAMHI 003317, 1989-2013; Dick y Peschke). Area tributaria: cada m2 dentro del cerco a la cuneta mas cercana.</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.094</v>
+        <v>0.095</v>
       </c>
       <c r="H11" s="17" t="n">
         <v>0.3</v>
@@ -1649,7 +1649,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="H12" s="17" t="n">
         <v>0.46</v>
@@ -1698,7 +1698,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.083</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>0.3</v>
@@ -1708,7 +1708,7 @@
         <v/>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="K13" s="20">
         <f>IF(I13&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1747,7 +1747,7 @@
         <v>0.5</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>0.46</v>
@@ -1796,7 +1796,7 @@
         <v>0.5</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="H15" s="17" t="n">
         <v>0.46</v>
@@ -1845,7 +1845,7 @@
         <v>2.92</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="H16" s="17" t="n">
         <v>0.52</v>
@@ -1855,7 +1855,7 @@
         <v/>
       </c>
       <c r="J16" s="6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="K16" s="20">
         <f>IF(I16&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -1894,7 +1894,7 @@
         <v>0.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.314</v>
+        <v>0.318</v>
       </c>
       <c r="H17" s="17" t="n">
         <v>0.77</v>
@@ -1943,7 +1943,7 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0.314</v>
+        <v>0.318</v>
       </c>
       <c r="H18" s="17" t="n">
         <v>0.83</v>
@@ -1992,7 +1992,7 @@
         <v>0.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0.399</v>
+        <v>0.404</v>
       </c>
       <c r="H19" s="17" t="n">
         <v>0.83</v>
@@ -2002,7 +2002,7 @@
         <v/>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="K19" s="20">
         <f>IF(I19&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2041,7 +2041,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.399</v>
+        <v>0.405</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>0.79</v>
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="K20" s="20">
         <f>IF(I20&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2090,7 +2090,7 @@
         <v>0.5</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>0.448</v>
+        <v>0.453</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>0.79</v>
@@ -2139,7 +2139,7 @@
         <v>0.5</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
       <c r="H22" s="17" t="n">
         <v>0.3</v>
@@ -2188,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="H23" s="17" t="n">
         <v>0.3</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="K23" s="20">
         <f>IF(I23&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2286,7 +2286,7 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H25" s="17" t="n">
         <v>0.47</v>
@@ -2335,7 +2335,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="H26" s="17" t="n">
         <v>0.48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="K26" s="20">
         <f>IF(I26&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2384,7 +2384,7 @@
         <v>0.5</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>0.49</v>
@@ -2433,7 +2433,7 @@
         <v>0.5</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>0.57</v>
@@ -2482,7 +2482,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>0.186</v>
+        <v>0.188</v>
       </c>
       <c r="H29" s="17" t="n">
         <v>0.61</v>
@@ -2492,7 +2492,7 @@
         <v/>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K29" s="20">
         <f>IF(I29&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2531,7 +2531,7 @@
         <v>0.5</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="H30" s="17" t="n">
         <v>0.3</v>
@@ -2580,7 +2580,7 @@
         <v>0.5</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="H31" s="17" t="n">
         <v>0.41</v>
@@ -2629,7 +2629,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="H32" s="17" t="n">
         <v>0.44</v>
@@ -2678,7 +2678,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="H33" s="17" t="n">
         <v>0.53</v>
@@ -2727,7 +2727,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>0.55</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="K34" s="20">
         <f>IF(I34&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2776,7 +2776,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>0.3</v>
@@ -2786,7 +2786,7 @@
         <v/>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="K35" s="20">
         <f>IF(I35&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2874,7 +2874,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>0.165</v>
+        <v>0.167</v>
       </c>
       <c r="H37" s="17" t="n">
         <v>0.5</v>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K37" s="20">
         <f>IF(I37&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2923,7 +2923,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>0.219</v>
+        <v>0.221</v>
       </c>
       <c r="H38" s="17" t="n">
         <v>0.59</v>
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="K38" s="20">
         <f>IF(I38&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -2972,7 +2972,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="H39" s="17" t="n">
         <v>0.61</v>
@@ -3021,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>0.246</v>
+        <v>0.249</v>
       </c>
       <c r="H40" s="17" t="n">
         <v>0.62</v>
@@ -3070,7 +3070,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.246</v>
+        <v>0.249</v>
       </c>
       <c r="H41" s="17" t="n">
         <v>0.73</v>
@@ -3119,7 +3119,7 @@
         <v>0.5</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0.304</v>
+        <v>0.308</v>
       </c>
       <c r="H42" s="17" t="n">
         <v>0.73</v>
@@ -3168,7 +3168,7 @@
         <v>0.5</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0.338</v>
+        <v>0.342</v>
       </c>
       <c r="H43" s="17" t="n">
         <v>0.79</v>
@@ -3178,7 +3178,7 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="K43" s="20">
         <f>IF(I43&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3217,7 +3217,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0.338</v>
+        <v>0.342</v>
       </c>
       <c r="H44" s="17" t="n">
         <v>0.7</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="K44" s="20">
         <f>IF(I44&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3266,7 +3266,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0.338</v>
+        <v>0.343</v>
       </c>
       <c r="H45" s="17" t="n">
         <v>0.7</v>
@@ -3315,7 +3315,7 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>0.339</v>
+        <v>0.343</v>
       </c>
       <c r="H46" s="17" t="n">
         <v>0.74</v>
@@ -3364,7 +3364,7 @@
         <v>0.5</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0.34</v>
+        <v>0.344</v>
       </c>
       <c r="H47" s="17" t="n">
         <v>0.74</v>
@@ -3413,7 +3413,7 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H48" s="17" t="n">
         <v>0.77</v>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="H49" s="17" t="n">
         <v>0.77</v>
@@ -3472,7 +3472,7 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="K49" s="20">
         <f>IF(I49&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3511,7 +3511,7 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H50" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3521,7 +3521,7 @@
         <v/>
       </c>
       <c r="J50" s="6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="K50" s="20">
         <f>IF(I50&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="H51" s="17" t="n">
         <v>0.8100000000000001</v>
@@ -3570,7 +3570,7 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="K51" s="20">
         <f>IF(I51&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3609,7 +3609,7 @@
         <v>0.5</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="H52" s="17" t="n">
         <v>0.3</v>
@@ -3658,7 +3658,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="H53" s="17" t="n">
         <v>0.32</v>
@@ -3668,7 +3668,7 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="K53" s="20">
         <f>IF(I53&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3707,7 +3707,7 @@
         <v>0.5</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="H54" s="17" t="n">
         <v>0.3</v>
@@ -3756,7 +3756,7 @@
         <v>0.5</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>0.3</v>
@@ -3815,7 +3815,7 @@
         <v/>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="K56" s="20">
         <f>IF(I56&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -3854,7 +3854,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H57" s="17" t="n">
         <v>0.42</v>
@@ -3903,7 +3903,7 @@
         <v>0.5</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="H58" s="17" t="n">
         <v>0.42</v>
@@ -3952,7 +3952,7 @@
         <v>0.5</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="H59" s="17" t="n">
         <v>0.48</v>
@@ -4001,7 +4001,7 @@
         <v>0.5</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H60" s="17" t="n">
         <v>0.2</v>
@@ -4050,7 +4050,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H61" s="17" t="n">
         <v>0.3</v>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="K61" s="20">
         <f>IF(I61&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4099,7 +4099,7 @@
         <v>0.5</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>0.38</v>
@@ -4109,7 +4109,7 @@
         <v/>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="K62" s="20">
         <f>IF(I62&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4148,7 +4148,7 @@
         <v>0.5</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.111</v>
+        <v>0.112</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>0.38</v>
@@ -4197,7 +4197,7 @@
         <v>0.5</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0.111</v>
+        <v>0.112</v>
       </c>
       <c r="H64" s="17" t="n">
         <v>0.49</v>
@@ -4246,7 +4246,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0.161</v>
+        <v>0.163</v>
       </c>
       <c r="H65" s="17" t="n">
         <v>0.5</v>
@@ -4256,7 +4256,7 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K65" s="20">
         <f>IF(I65&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4295,7 +4295,7 @@
         <v>0.5</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0.202</v>
+        <v>0.204</v>
       </c>
       <c r="H66" s="17" t="n">
         <v>0.52</v>
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="J66" s="6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="K66" s="20">
         <f>IF(I66&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4344,7 +4344,7 @@
         <v>0.5</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0.306</v>
+        <v>0.31</v>
       </c>
       <c r="H67" s="17" t="n">
         <v>0.5600000000000001</v>
@@ -4393,7 +4393,7 @@
         <v>0.5</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>0.372</v>
+        <v>0.377</v>
       </c>
       <c r="H68" s="17" t="n">
         <v>0.62</v>
@@ -4442,7 +4442,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="18" t="n">
-        <v>0.389</v>
+        <v>0.394</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>0.57</v>
@@ -4452,7 +4452,7 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="K69" s="20">
         <f>IF(I69&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4491,7 +4491,7 @@
         <v>0.5</v>
       </c>
       <c r="G70" s="18" t="n">
-        <v>0.39</v>
+        <v>0.395</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>0.63</v>
@@ -4501,7 +4501,7 @@
         <v/>
       </c>
       <c r="J70" s="6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="K70" s="20">
         <f>IF(I70&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4540,7 +4540,7 @@
         <v>0.5</v>
       </c>
       <c r="G71" s="18" t="n">
-        <v>0.39</v>
+        <v>0.395</v>
       </c>
       <c r="H71" s="17" t="n">
         <v>0.64</v>
@@ -4550,7 +4550,7 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="K71" s="20">
         <f>IF(I71&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4589,7 +4589,7 @@
         <v>0.5</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0.447</v>
+        <v>0.453</v>
       </c>
       <c r="H72" s="17" t="n">
         <v>0.64</v>
@@ -4687,7 +4687,7 @@
         <v>0.5</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="H74" s="17" t="n">
         <v>0.3</v>
@@ -4736,7 +4736,7 @@
         <v>0.5</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H75" s="17" t="n">
         <v>0.38</v>
@@ -4785,7 +4785,7 @@
         <v>0.5</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>0.35</v>
@@ -4795,7 +4795,7 @@
         <v/>
       </c>
       <c r="J76" s="6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K76" s="20">
         <f>IF(I76&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4834,7 +4834,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>0.35</v>
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K77" s="20">
         <f>IF(I77&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -4883,7 +4883,7 @@
         <v>0.5</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="H78" s="17" t="n">
         <v>0.35</v>
@@ -4932,7 +4932,7 @@
         <v>0.5</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="H79" s="17" t="n">
         <v>0.35</v>
@@ -4981,7 +4981,7 @@
         <v>0.5</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="H80" s="17" t="n">
         <v>0.45</v>
@@ -5030,7 +5030,7 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="H81" s="17" t="n">
         <v>0.3</v>
@@ -5040,7 +5040,7 @@
         <v/>
       </c>
       <c r="J81" s="6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="K81" s="20">
         <f>IF(I81&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5089,7 +5089,7 @@
         <v/>
       </c>
       <c r="J82" s="6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="K82" s="20">
         <f>IF(I82&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5128,7 +5128,7 @@
         <v>0.58</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>0.35</v>
@@ -5138,7 +5138,7 @@
         <v/>
       </c>
       <c r="J83" s="6" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K83" s="20">
         <f>IF(I83&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5177,7 +5177,7 @@
         <v>0.5</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>0.35</v>
@@ -5226,7 +5226,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="H85" s="17" t="n">
         <v>0.3</v>
@@ -5275,7 +5275,7 @@
         <v>0.5</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H86" s="17" t="n">
         <v>0.45</v>
@@ -5285,7 +5285,7 @@
         <v/>
       </c>
       <c r="J86" s="6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="K86" s="20">
         <f>IF(I86&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5324,7 +5324,7 @@
         <v>0.5</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H87" s="17" t="n">
         <v>0.46</v>
@@ -5373,7 +5373,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H88" s="17" t="n">
         <v>0.47</v>
@@ -5383,7 +5383,7 @@
         <v/>
       </c>
       <c r="J88" s="6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K88" s="20">
         <f>IF(I88&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5422,7 +5422,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="H89" s="17" t="n">
         <v>0.4</v>
@@ -5432,7 +5432,7 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="K89" s="20">
         <f>IF(I89&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5471,7 +5471,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>0.4</v>
@@ -5481,7 +5481,7 @@
         <v/>
       </c>
       <c r="J90" s="6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="K90" s="20">
         <f>IF(I90&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5520,7 +5520,7 @@
         <v>0.51</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H91" s="17" t="n">
         <v>0.2</v>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="J91" s="6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="K91" s="20">
         <f>IF(I91&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5579,7 +5579,7 @@
         <v/>
       </c>
       <c r="J92" s="6" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="K92" s="20">
         <f>IF(I92&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5618,7 +5618,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="H93" s="17" t="n">
         <v>0.5</v>
@@ -5667,7 +5667,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0.129</v>
+        <v>0.131</v>
       </c>
       <c r="H94" s="17" t="n">
         <v>0.4</v>
@@ -5775,7 +5775,7 @@
         <v/>
       </c>
       <c r="J96" s="6" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="K96" s="20">
         <f>IF(I96&gt;=0.05,"CUMPLE","NO CUMPLE")</f>
@@ -5814,7 +5814,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>0.36</v>
@@ -5863,7 +5863,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>0.48</v>
@@ -5912,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="18" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="H99" s="17" t="n">
         <v>0.49</v>
